--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="368" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F430E9A-0B19-4A13-B70B-E851EBFE5A29}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{518ACB2F-0356-4DC5-93E2-AE6AB317B5F0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="2400" windowWidth="29040" windowHeight="18480" tabRatio="883" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="1137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="1155">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -983,9 +983,6 @@
     <t>레터럴 레이즈</t>
   </si>
   <si>
-    <t>덤벨은 아래 구간에 저항이 안 걸린다 — 원암 케이블(7일차)이 그 구간을 메운다</t>
-  </si>
-  <si>
     <t>케이블 레터럴 레이즈 (전 구간 장력) / 레터럴 레이즈 머신 / 라잉 레터럴</t>
   </si>
   <si>
@@ -1148,9 +1145,6 @@
     <t>25~30</t>
   </si>
   <si>
-    <t>[2026-09-04 신설] 프레싱 두 종목을 끝내고 고립으로 마무리하는 자리. 팔꿈치 각도를 고정한 채 어깨 수평 내전만 — 굽혔다 펴면 프레스가 된다. 첫날은 25kg으로 10~12회가 실패 2~3회 안에 들어오는지 보고 맞춘다. 이 종목을 넣어 흉근 합산이 주당 환산 24.1이 됐다(천장 20 초과) — 사용자가 알고 선택한 것이며, 세트 질이 떨어지면 2일차 디클라인 케이블 플라이 3세트를 먼저 뺀다.</t>
-  </si>
-  <si>
     <t>케이블 크로스오버 / 플랫 벤치 덤벨 플라이 (가동범위 ↑) / 머신 체스트 플라이</t>
   </si>
   <si>
@@ -1250,9 +1244,6 @@
     <t>프리쳐 컬</t>
   </si>
   <si>
-    <t>반동이 차단되는 종목. 인클라인(9일차)과 각도를 나눈다</t>
-  </si>
-  <si>
     <t>EZ바 프리처 컬 / 머신 프리처 컬 / 컨센트레이션 컬</t>
   </si>
   <si>
@@ -1442,18 +1433,6 @@
     <t>레그 익스텐션</t>
   </si>
   <si>
-    <t>대퇴사두 사이클당 2회를 만들기 위한 배치. 3일차 스쿼트 볼륨과 5일 간격</t>
-  </si>
-  <si>
-    <t>싱글 레그 익스텐션 / 시시 스쿼트 / 레그 프레스 발판 높게</t>
-  </si>
-  <si>
-    <t>수/토 3+3 분할. 데드·힙 이후라 대퇴가 예열된 상태에서 궤도 고정으로 확실히 간다</t>
-  </si>
-  <si>
-    <t>핵 스쿼트 / 레그 익스텐션 / 프론트 스쿼트 / 45도 레그 프레스</t>
-  </si>
-  <si>
     <t>무릎 굽힘 — 가자미근 주도. 3일차 스탠딩(비복근)과 역할이 다르다</t>
   </si>
   <si>
@@ -3270,10 +3249,6 @@
   </si>
   <si>
     <t>· 햄스트링 8.0 · 전완 8.0 · 내전근 5.0 — 하한 근처다. 유지는 되나 성장 여지는 없는 자리다.</t>
-  </si>
-  <si>
-    <t>[2026-09-05 4일차 → 2일차 이동] 벤치·딥스·플라이·레이즈를 다 마친 뒤 마지막에 — 프레스에서 이미 지친 삼두를 고립으로 마무리하는 자리다. 4일차에 있을 때의 근거였던 '삼두가 안 쓰인 날의 신선함'은 포기했고, 대신 밀기 날에 삼두가 같이 끝난다. 로프로 마지막에 손등을 바깥으로 벌리면 외측두가 끝까지 수축한다. 팔꿈치는 옆구리에 고정 — 어깨로 누르면 광배 종목이 된다. 9일차 라잉 익스텐션이 늘어난 구간(장두)이라 여기는 짧아진 구간(외측두·내측두)으로 축을 나눈다. 삼두 직접은 2일차 4 · 9일차 4로 사이클당 2회 그대로. [2026-08-28 — 원래 1일차 인클라인 덤벨 컬 자리에 들어왔던 종목]</t>
-    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>[2026-09-05 2일차 → 4일차 이동] 이 날 유일한 프레스라 벤치·딥스 뒤 세 번째로 치던 때보다 신선하다 — 중량을 2일차 시절보다 올려 잡아도 된다. 레이즈 6세트 뒤에 두는 이유는 9일차 머신 숄더 프레스와 같다: 앞에 두면 프레스 피로로 레이즈 중량이 눌린다. 복합관절이라 뒤의 플라이 두 종목 앞이다. [2026-09-04 신설 당시] 흉근 상부 7세트를 플라이 하나로 채우던 것을 프레스 3 + 플라이 4로 나눴다. 플라이는 늘어난 구간에서 벌리는 자극, 프레스는 중량을 실을 수 있는 축 — 상부 흉근을 한 종류로만 때리지 않는다. 2일차 인클라인 플라이 · 7일차 인클라인 머신과 함께 흉근 상부 사이클당 3회.</t>
@@ -3332,10 +3307,6 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>[2026-09-05 4일차 → 7일차 이동 — 사용자 요청] 흉근 중하부 고립. 헤머 체스트·인클라인 머신 두 프레스 뒤 마무리 자리다. 위에서 아래로 내리는 궤적이라 하부 섬유 비중이 크고, 케이블이라 수축 지점에서도 장력이 유지된다. 흉근 합산이 천장(20)을 넘어 있어 세트 질이 떨어지면 먼저 빼는 후보가 이 3세트다. [이력] 이 행은 v18 전 삼두 종목 자리였고, 2026-09-04 2일차 → 4일차, 오늘 7일차로 왔다.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>케이블 크로스오버 (위→아래) / 디클라인 덤벨 플라이 / 펙덱 플라이 (시트를 높여 하부 각)</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
@@ -3383,10 +3354,6 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>오버헤드 프레싱 · 흉근 상부 · 어깨 측면/후면. 벤치(2일차)와 5일 간격이라 무게가 온전히 나온다. [2026-09-05] 4일차 디클라인 케이블 플라이 3세트가 왔다 — 흉근 9세트(헤머 · 인클라인 머신 · 디클라인). 6일차 중량 크런치 3세트도 마지막에 왔다 — 약 72분.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>· 6일차 스탠딩 카프 4세트가 시티드 카프 앞으로 왔다 — 6일차 자리를 힙 외전에 내준 것. 35세트 · 약 70분.</t>
   </si>
   <si>
@@ -3414,14 +3381,6 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>측면·후면 삼각근 + 승모 하부 + 흉근(인클라인 스미스 · 펙덱) + 이두 · 전완 + 종아리. 약 71분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B. [2026-09-05] 이너·아우터 타이·리스트 컬은 9일차로, 디클라인 플라이는 7일차로, 시티드 카프는 6일차로 갔고, 9일차의 리버스 리스트 컬·리버스컬과 6일차 스탠딩 카프·오버헤드 슈러그가 왔다.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
-    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다. [2026-09-05] 스탠딩 카프는 4일차로, 중량 크런치는 7일차로 갔고 9일차 케이블 힙 외전이 왔다. 약 72분. 오버헤드 슈러그는 4일차로 가고 4일차 시티드 카프 2세트가 왔다 — 약 71분.</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>· 6일차 오버헤드 슈러그 3세트가 5번(인클라인 스미스 앞, 같은 스미스 머신)으로 왔고 시티드 카프 2세트는 6일차로 갔다. 승모 하부 4·7·9일차. 36세트 · 약 71분.</t>
   </si>
   <si>
@@ -3449,9 +3408,6 @@
     <t>8~12 (좌우)</t>
   </si>
   <si>
-    <t>[2026-09-05 신설] 랫풀다운 4세트를 양팔 2 + 원암 2로 나눴다 (사용자 요청). 하이 풀리에 D핸들을 걸고 뉴트럴 그립으로 한 팔씩 — 좌우를 따로 세니 약한 쪽이 강한 쪽에 묻히지 않고, 당기는 쪽으로 몸통을 살짝 기울여 광배를 더 늘린 자리에서 시작할 수 있다. 팔꿈치를 옆구리 쪽으로 끌어내리고 맨 아래에서 1초 정지. 세트 수는 좌우 한 번씩을 1세트로 센다(수행 80초 = 40초 × 2). 무게는 양팔의 절반에서 시작해 약한 쪽 기준으로 올린다. 광배 직접 세트는 이 날 8 그대로.</t>
-  </si>
-  <si>
     <t>원암 케이블 풀다운 (다른 하이 풀리) / 원암 덤벨 로우 (풀다운 기구가 찼을 때) / 뉴트럴 그립 랫풀다운 4세트로 합치기</t>
   </si>
   <si>
@@ -3465,9 +3421,6 @@
     <t>원암 케이블 로우</t>
   </si>
   <si>
-    <t>[2026-09-05 신설] 시티드 케이블 로우 5세트를 양팔 3 + 원암 2로 나눴다 (사용자 요청). 같은 로우 스테이션에서 바를 D핸들로 바꿔 한 팔씩 — 팔꿈치를 몸통에 붙이고, 당기는 쪽으로 몸통을 살짝 돌려 광배 수축을 끝까지 가져간다(반대 손은 기구를 잡아 몸통을 고정). 좌우를 따로 세니 약한 쪽이 강한 쪽에 묻히지 않는다. 세트 수는 좌우 한 번씩을 1세트로 센다(수행 80초 = 40초 × 2). 무게는 양팔의 절반에서 시작해 약한 쪽 기준으로 올린다. 광배 직접 세트는 이 날 5 그대로. 4번 스캡 슈러그는 이 뒤에 바를 다시 걸고 이어서 한다.</t>
-  </si>
-  <si>
     <t>원암 덤벨 로우 (벤치 지지) / 원암 머신 로우 (해머 스트랭스 한 팔씩) / 시티드 케이블 로우 5세트로 합치기</t>
   </si>
   <si>
@@ -3500,6 +3453,154 @@
   </si>
   <si>
     <t>[2026-09-05] 6일차를 하루 미룸 — 늦게 일어나 갔더니 헬스장이 닫혀 있었다. 실제 1일차는 08-31이었으나 앱 달력 기준을 09-01로 당겨 적어 09-06이 6일차가 되게 했다(이 사이클만 11일, 다음 사이클 1일차 09-11).</t>
+  </si>
+  <si>
+    <t>레그 프레스</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>레그 익스텐션</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>대퇴사두</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>8~12</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>10~12</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵 스쿼트 / 레그 익스텐션 / 프론트 스쿼트 / 45도 레그 프레스</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱글 레그 익스텐션 / 시시 스쿼트 / 레그 프레스 발판 높게</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>드롭(초)</t>
+  </si>
+  <si>
+    <t>[2026-09-05 신설] 랫풀다운 4세트를 양팔 2 + 원암 2로 나눴다 (사용자 요청). 하이 풀리에 D핸들을 걸고 뉴트럴 그립으로 한 팔씩 — 좌우를 따로 세니 약한 쪽이 강한 쪽에 묻히지 않고, 당기는 쪽으로 몸통을 살짝 기울여 광배를 더 늘린 자리에서 시작할 수 있다. 팔꿈치를 옆구리 쪽으로 끌어내리고 맨 아래에서 1초 정지. 세트 수는 좌우 한 번씩을 1세트로 센다(수행 80초 = 40초 × 2). 무게는 양팔의 절반에서 시작해 약한 쪽 기준으로 올린다. 광배 직접 세트는 이 날 8 그대로. [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 20~30% 내려 두 번. 한쪽을 끝까지 내려간 뒤 반대쪽. 팔로 당기기 시작하면 그 자리에서 끝. 세트 수 그대로, 증량 판정은 첫 세트로만. +120초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>드롭</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>세트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (2026-09-07)</t>
+    </r>
+  </si>
+  <si>
+    <t>· 원암 랫풀다운 마지막 세트에 드롭 2단, +120초 (사용자 요청). 편측이라 한쪽을 끝까지 내려간 뒤 반대쪽으로 넘어간다 — 번갈아 하면 쉬는 시간이 생겨 드롭 효과가 약해진다. 광배는 주당 12.4로 낮고 예산은 잠겨 있어, 세트 수를 안 늘리고 자극만 얹는 자리다.</t>
+  </si>
+  <si>
+    <t>· O열 '드롭(초)'는 마지막 세트에 더해지는 시간이다. I열 종목 분에 합산되고, 앱 타이머는 마지막 세트를 그만큼 늘린 뒤 '드롭세트'라고 읊는다. E열 세트 수와 세트검산은 건드리지 않는다.</t>
+  </si>
+  <si>
+    <t>덤벨은 아래 구간에 저항이 안 걸린다 — 원암 케이블(7일차)이 그 구간을 메운다 [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 20~30% 내려 두 번. 무거운 구간에서 승모가 끼면 내린 무게로 어깨만 마저 채운다. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+  </si>
+  <si>
+    <t>[2026-09-05 4일차 → 2일차 이동] 벤치·딥스·플라이·레이즈를 다 마친 뒤 마지막에 — 프레스에서 이미 지친 삼두를 고립으로 마무리하는 자리다. 4일차에 있을 때의 근거였던 '삼두가 안 쓰인 날의 신선함'은 포기했고, 대신 밀기 날에 삼두가 같이 끝난다. 로프로 마지막에 손등을 바깥으로 벌리면 외측두가 끝까지 수축한다. 팔꿈치는 옆구리에 고정 — 어깨로 누르면 광배 종목이 된다. 9일차 라잉 익스텐션이 늘어난 구간(장두)이라 여기는 짧아진 구간(외측두·내측두)으로 축을 나눈다. 삼두 직접은 2일차 4 · 9일차 4로 사이클당 2회 그대로. [2026-08-28 — 원래 1일차 인클라인 덤벨 컬 자리에 들어왔던 종목] [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 팔꿈치는 끝까지 옆구리에. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 레터럴 레이즈 · 리버스 펙덱 · 푸쉬다운 마지막 세트에 드롭 2단, 각 +60초 (사용자 요청). 벤치 뒤라 셋이 몰려도 메인에 영향이 없다. 20~30%씩 내려 쉬지 않고 두 번, 세 번째부터는 피로만 쌓인다.</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 프레싱 두 종목을 끝내고 고립으로 마무리하는 자리. 팔꿈치 각도를 고정한 채 어깨 수평 내전만 — 굽혔다 펴면 프레스가 된다. 첫날은 25kg으로 10~12회가 실패 2~3회 안에 들어오는지 보고 맞춘다. 이 종목을 넣어 흉근 합산이 주당 환산 24.1이 됐다(천장 20 초과) — 사용자가 알고 선택한 것이며, 세트 질이 떨어지면 2일차 디클라인 케이블 플라이 3세트를 먼저 뺀다. [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 펙덱 플라이 마지막 세트에 드롭 2단, +60초 (사용자 요청). 인클라인 스미스 뒤 흉근 마지막 자리라 여기. 인클라인 프레스 계열은 복합이라 드롭을 붙이지 않는다.</t>
+  </si>
+  <si>
+    <t>[2026-09-05 신설] 시티드 케이블 로우 5세트를 양팔 3 + 원암 2로 나눴다 (사용자 요청). 같은 로우 스테이션에서 바를 D핸들로 바꿔 한 팔씩 — 팔꿈치를 몸통에 붙이고, 당기는 쪽으로 몸통을 살짝 돌려 광배 수축을 끝까지 가져간다(반대 손은 기구를 잡아 몸통을 고정). 좌우를 따로 세니 약한 쪽이 강한 쪽에 묻히지 않는다. 세트 수는 좌우 한 번씩을 1세트로 센다(수행 80초 = 40초 × 2). 무게는 양팔의 절반에서 시작해 약한 쪽 기준으로 올린다. 광배 직접 세트는 이 날 5 그대로. 4번 스캡 슈러그는 이 뒤에 바를 다시 걸고 이어서 한다. [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 20~30% 내려 두 번. 한쪽을 끝까지 내려간 뒤 반대쪽. 몸통이 돌아가거나 팔로 당기기 시작하면 그 자리에서 끝. 세트 수 그대로, 증량 판정은 첫 세트로만. +120초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>반동이 차단되는 종목. 인클라인(9일차)과 각도를 나눈다 [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 20~30% 내려 두 번. 팔꿈치가 패드에 고정돼 지쳐도 자세가 남는 종목이라 이두 드롭은 여기 한 곳. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 원암 로우(+120초 · 편측) · 프리쳐 컬(+60초) 마지막 세트에 드롭 2단 (사용자 요청). 원암 로우는 몸통이 돌아가거나 팔로 당기기 시작하면 그 자리에서 끝 — 지친 상태에서 광배가 빠지기 가장 쉬운 종목이다. 이두 드롭은 여기 한 곳이다. 9일차 인클라인 컬은 이틀 뒤 1일차 친업 때문에 직선으로 둔다.</t>
+  </si>
+  <si>
+    <t>[2026-09-05 4일차 → 7일차 이동 — 사용자 요청] 흉근 중하부 고립. 헤머 체스트·인클라인 머신 두 프레스 뒤 마무리 자리다. 위에서 아래로 내리는 궤적이라 하부 섬유 비중이 크고, 케이블이라 수축 지점에서도 장력이 유지된다. 흉근 합산이 천장(20)을 넘어 있어 세트 질이 떨어지면 먼저 빼는 후보가 이 3세트다. [이력] 이 행은 v18 전 삼두 종목 자리였고, 2026-09-04 2일차 → 4일차, 오늘 7일차로 왔다. [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 팔을 굽혀 프레스처럼 밀기 시작하면 끝. 4일차 펙덱과 3일 간격. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 디클라인 케이블 플라이 마지막 세트에 드롭 2단, +60초 (사용자 요청). 4일차 펙덱과 3일 간격. 머신 숄더 프레스에는 붙이지 않는다 — 복합 프레스이고, 전면 삼각근은 프레스 4종으로 이미 충분하며, 밀리터리 직후·벤치 3일 전이라 피로만 얹힌다.</t>
+  </si>
+  <si>
+    <t>대퇴사두 사이클당 2회를 만들기 위한 배치. 3일차 스쿼트 볼륨과 5일 간격 [2026-09-07 레그 프레스 뒤로 이동 + 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 드롭으로 대퇴를 다 쓴 뒤 프레스를 하면 프레스 3세트가 죽어서 순서를 바꿨다. 세트 수 그대로, 증량 판정은 앞 세트로만. +75초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>수/토 3+3 분할. 데드·힙 이후라 대퇴가 예열된 상태에서 궤도 고정으로 확실히 간다 [2026-09-07 레그 익스텐션과 자리 바꿈 — 복합을 먼저, 고립 드롭을 마지막에]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 레그 프레스 ↔ 레그 익스텐션 자리 바꿈 — 복합을 먼저, 고립을 마지막에. 익스텐션 마지막 세트에 드롭 2단, +75초 (사용자 요청). 드롭으로 대퇴를 다 쓴 뒤 프레스를 하면 프레스 3세트가 죽어서 순서를 바꿨다. 다음 하체는 3일차, 5일 뒤라 회복이 겹치지 않는다.</t>
+  </si>
+  <si>
+    <t>· 고립·케이블 9곳의 마지막 세트에만 드롭 2단 — 1일차 원암 랫풀다운, 2일차 레터럴·리버스 펙덱·푸쉬다운, 4일차 펙덱, 6일차 원암 로우·프리쳐 컬, 7일차 디클라인 케이블 플라이, 8일차 레그 익스텐션. 메인 4종, 척추 부하 종목, 복합 프레스·로우, 기술 종목(오버헤드 슈러그·프론 Y·업라이트 로우)에는 붙이지 않는다.</t>
+  </si>
+  <si>
+    <t>· 세트 수·예산(244)은 그대로다. 드롭은 같은 세트의 연장이지 새 세트가 아니다. 시간만 O열 '드롭(초)'로 얹혀 세션이 +1~3분. 증량 판정은 드롭이 없는 앞 세트로만 한다.</t>
+  </si>
+  <si>
+    <t>· 3·9일차는 드롭 0 — 스쿼트가 있는 날과 36세트로 이미 꽉 찬 날이다. 이두는 프리쳐 컬 한 곳(9일차 인클라인 컬은 이틀 뒤 친업), 머신 숄더 프레스는 제외(전면 삼각근은 프레스 4종으로 충분).</t>
+  </si>
+  <si>
+    <t>측면·후면 삼각근 + 승모 하부 + 흉근(인클라인 스미스 · 펙덱) + 이두 · 전완 + 종아리. 약 71분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B. [2026-09-05] 이너·아우터 타이·리스트 컬은 9일차로, 디클라인 플라이는 7일차로, 시티드 카프는 6일차로 갔고, 9일차의 리버스 리스트 컬·리버스컬과 6일차 스탠딩 카프·오버헤드 슈러그가 왔다. 펙덱 마지막 세트 드롭 +1분 — 약 72분 (2026-09-07).</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다. [2026-09-05] 스탠딩 카프는 4일차로, 중량 크런치는 7일차로 갔고 9일차 케이블 힙 외전이 왔다. 약 72분. 오버헤드 슈러그는 4일차로 가고 4일차 시티드 카프 2세트가 왔다 — 약 71분. 원암 로우·프리쳐 컬 마지막 세트 드롭 +3분 — 약 75분 (2026-09-07).</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버헤드 프레싱 · 흉근 상부 · 어깨 측면/후면. 벤치(2일차)와 5일 간격이라 무게가 온전히 나온다. [2026-09-05] 4일차 디클라인 케이블 플라이 3세트가 왔다 — 흉근 9세트(헤머 · 인클라인 머신 · 디클라인). 6일차 중량 크런치 3세트도 마지막에 왔다 — 약 72분. 디클라인 플라이 마지막 세트 드롭 +1분 — 약 73분 (2026-09-07).</t>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3510,7 +3611,7 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3862,6 +3963,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -3974,7 +4090,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4227,6 +4343,7 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5155,7 +5272,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -5168,29 +5285,30 @@
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1">
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="30" customHeight="1">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1">
+    <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
         <v>3</v>
       </c>
@@ -5233,8 +5351,11 @@
       <c r="N5" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O5" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" customHeight="1">
       <c r="A6" s="20">
         <v>1</v>
       </c>
@@ -5260,7 +5381,7 @@
         <v>70</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND((E6*(G6+H6)+O6)/60,1))</f>
         <v>7.5</v>
       </c>
       <c r="J6" s="21"/>
@@ -5270,8 +5391,9 @@
       <c r="L6" s="21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:15" ht="16.5" customHeight="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
@@ -5307,8 +5429,9 @@
       <c r="L7" s="21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:15" ht="16.5" customHeight="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
@@ -5346,8 +5469,9 @@
       <c r="L8" s="21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" customHeight="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
@@ -5385,13 +5509,14 @@
       <c r="L9" s="21" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O9" s="26"/>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>300</v>
@@ -5412,18 +5537,19 @@
         <v>105</v>
       </c>
       <c r="I10" s="26">
-        <f>IF(E10=0,0,ROUND(E10*(G10+H10)/60,1))</f>
+        <f t="shared" si="0"/>
         <v>7.3</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O10" s="26"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
       <c r="A11" s="20">
         <v>6</v>
       </c>
@@ -5459,8 +5585,9 @@
       <c r="L11" s="21" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O11" s="26"/>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
@@ -5498,13 +5625,14 @@
       <c r="L12" s="21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O12" s="26"/>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
       <c r="B13" s="81" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>45</v>
@@ -5530,24 +5658,25 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="16.5" customHeight="1">
+        <v>370</v>
+      </c>
+      <c r="O13" s="26"/>
+    </row>
+    <row r="14" spans="1:15" ht="16.5" customHeight="1">
       <c r="A14" s="20">
         <v>9</v>
       </c>
       <c r="B14" s="81" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>336</v>
-      </c>
       <c r="D14" s="20" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E14" s="20">
         <v>5</v>
@@ -5567,21 +5696,22 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="N14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+        <v>338</v>
+      </c>
+      <c r="O14" s="26"/>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
       <c r="B15" s="81" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>60</v>
@@ -5607,16 +5737,17 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N15" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="16.5" customHeight="1">
+        <v>338</v>
+      </c>
+      <c r="O15" s="26"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1">
       <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
@@ -5763,27 +5894,27 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="31" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1106</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N15">
+  <conditionalFormatting sqref="A6:O15">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -5808,24 +5939,24 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="114" t="s">
-        <v>469</v>
-      </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="A2" s="115" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$80,"?")</f>
@@ -5833,46 +5964,46 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A4" s="112" t="s">
-        <v>471</v>
-      </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
+      <c r="A4" s="113" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
+        <v>465</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>468</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>469</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>470</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>471</v>
+      </c>
+      <c r="H6" s="44" t="s">
         <v>472</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>473</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>474</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>475</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>476</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>477</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>478</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B7" s="45" t="s">
         <v>237</v>
@@ -5892,15 +6023,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B8" s="45" t="s">
         <v>243</v>
@@ -5920,18 +6051,18 @@
         <v>0.4</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C9" s="45" t="s">
         <v>44</v>
@@ -5948,18 +6079,18 @@
         <v>1</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C10" s="45" t="s">
         <v>44</v>
@@ -5976,15 +6107,15 @@
         <v>0.99</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="45" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>288</v>
@@ -6004,15 +6135,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="H11" s="50" t="s">
         <v>481</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="45" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B12" s="45" t="s">
         <v>295</v>
@@ -6032,18 +6163,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C13" s="45" t="s">
         <v>39</v>
@@ -6060,18 +6191,18 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C14" s="45" t="s">
         <v>39</v>
@@ -6088,15 +6219,15 @@
         <v>1.5</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="B15" s="45" t="s">
         <v>299</v>
@@ -6116,15 +6247,15 @@
         <v>1.5</v>
       </c>
       <c r="G15" s="49" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="45" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B16" s="45" t="s">
         <v>43</v>
@@ -6144,18 +6275,18 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C17" s="45" t="s">
         <v>45</v>
@@ -6172,18 +6303,18 @@
         <v>1.32</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>45</v>
@@ -6200,15 +6331,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="45" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B19" s="45" t="s">
         <v>288</v>
@@ -6228,15 +6359,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>299</v>
@@ -6256,18 +6387,18 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="H20" s="50" t="s">
         <v>493</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C21" s="45" t="s">
         <v>27</v>
@@ -6284,18 +6415,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C22" s="45" t="s">
         <v>18</v>
@@ -6312,15 +6443,15 @@
         <v>0.99</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B23" s="45" t="s">
         <v>26</v>
@@ -6340,15 +6471,15 @@
         <v>0.99</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="45" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B24" s="45" t="s">
         <v>26</v>
@@ -6368,15 +6499,15 @@
         <v>0.99</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B25" s="45" t="s">
         <v>252</v>
@@ -6396,15 +6527,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="45" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B26" s="45" t="s">
         <v>33</v>
@@ -6424,15 +6555,15 @@
         <v>1.5</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B27" s="45" t="s">
         <v>33</v>
@@ -6452,18 +6583,18 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C28" s="45" t="s">
         <v>238</v>
@@ -6480,18 +6611,18 @@
         <v>2.5</v>
       </c>
       <c r="G28" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C29" s="45" t="s">
         <v>246</v>
@@ -6508,18 +6639,18 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C30" s="45" t="s">
         <v>246</v>
@@ -6536,21 +6667,21 @@
         <v>0</v>
       </c>
       <c r="G30" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D31" s="46">
         <v>0.2</v>
@@ -6564,21 +6695,21 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D32" s="46">
         <v>0.33</v>
@@ -6592,21 +6723,21 @@
         <v>0.33</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>271</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D33" s="46">
         <v>0.5</v>
@@ -6620,21 +6751,21 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D34" s="46">
         <v>0.5</v>
@@ -6648,21 +6779,21 @@
         <v>2.5</v>
       </c>
       <c r="G34" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B35" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="C35" s="45" t="s">
         <v>322</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>323</v>
       </c>
       <c r="D35" s="46">
         <v>0.33</v>
@@ -6676,21 +6807,21 @@
         <v>0.99</v>
       </c>
       <c r="G35" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D36" s="46">
         <v>0.5</v>
@@ -6704,21 +6835,21 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D37" s="46">
         <v>0.5</v>
@@ -6732,21 +6863,21 @@
         <v>1.5</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>271</v>
       </c>
       <c r="C38" s="45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D38" s="46">
         <v>0.5</v>
@@ -6760,18 +6891,18 @@
         <v>1.5</v>
       </c>
       <c r="G38" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C39" s="45" t="s">
         <v>272</v>
@@ -6788,18 +6919,18 @@
         <v>0</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C40" s="45" t="s">
         <v>272</v>
@@ -6816,18 +6947,18 @@
         <v>0</v>
       </c>
       <c r="G40" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C41" s="45" t="s">
         <v>272</v>
@@ -6844,21 +6975,21 @@
         <v>1.5</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D42" s="46">
         <v>0.5</v>
@@ -6872,18 +7003,18 @@
         <v>1.5</v>
       </c>
       <c r="G42" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="45" t="s">
         <v>60</v>
@@ -6900,18 +7031,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C44" s="45" t="s">
         <v>238</v>
@@ -6928,21 +7059,21 @@
         <v>0</v>
       </c>
       <c r="G44" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D45" s="46">
         <v>0.33</v>
@@ -6956,21 +7087,21 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G45" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D46" s="46">
         <v>0.33</v>
@@ -6984,21 +7115,21 @@
         <v>0.99</v>
       </c>
       <c r="G46" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="45" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D47" s="46">
         <v>0.33</v>
@@ -7012,15 +7143,15 @@
         <v>0.99</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="45" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B48" s="45" t="s">
         <v>288</v>
@@ -7040,18 +7171,18 @@
         <v>0</v>
       </c>
       <c r="G48" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C49" s="45" t="s">
         <v>289</v>
@@ -7068,21 +7199,21 @@
         <v>0</v>
       </c>
       <c r="G49" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C50" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D50" s="46">
         <v>0</v>
@@ -7096,21 +7227,21 @@
         <v>0</v>
       </c>
       <c r="G50" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C51" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D51" s="46">
         <v>0.2</v>
@@ -7124,21 +7255,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C52" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D52" s="46">
         <v>0</v>
@@ -7152,15 +7283,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H52" s="50" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="45" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B53" s="45" t="s">
         <v>237</v>
@@ -7180,18 +7311,18 @@
         <v>0.8</v>
       </c>
       <c r="G53" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C54" s="45" t="s">
         <v>34</v>
@@ -7208,18 +7339,18 @@
         <v>1</v>
       </c>
       <c r="G54" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="45" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C55" s="45" t="s">
         <v>246</v>
@@ -7236,21 +7367,21 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G55" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B56" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="C56" s="45" t="s">
         <v>322</v>
-      </c>
-      <c r="C56" s="45" t="s">
-        <v>323</v>
       </c>
       <c r="D56" s="46">
         <v>0.33</v>
@@ -7264,21 +7395,21 @@
         <v>0.99</v>
       </c>
       <c r="G56" s="52" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D57" s="46">
         <v>0.33</v>
@@ -7292,15 +7423,15 @@
         <v>0.99</v>
       </c>
       <c r="G57" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B58" s="45" t="s">
         <v>26</v>
@@ -7320,15 +7451,15 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H58" s="50" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="45" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B59" s="45" t="s">
         <v>26</v>
@@ -7348,18 +7479,18 @@
         <v>1.5</v>
       </c>
       <c r="G59" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C60" s="45" t="s">
         <v>39</v>
@@ -7376,15 +7507,15 @@
         <v>1.5</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="45" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B61" s="45" t="s">
         <v>295</v>
@@ -7404,18 +7535,18 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C62" s="45" t="s">
         <v>27</v>
@@ -7432,15 +7563,15 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H62" s="50" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="45" t="s">
-        <v>1097</v>
+        <v>1088</v>
       </c>
       <c r="B63" s="45" t="s">
         <v>51</v>
@@ -7460,18 +7591,18 @@
         <v>0.8</v>
       </c>
       <c r="G63" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="45" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>246</v>
@@ -7488,21 +7619,21 @@
         <v>0.99</v>
       </c>
       <c r="G64" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="45" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B65" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="C65" s="45" t="s">
         <v>350</v>
-      </c>
-      <c r="C65" s="45" t="s">
-        <v>351</v>
       </c>
       <c r="D65" s="46">
         <v>0.33</v>
@@ -7516,18 +7647,18 @@
         <v>0.99</v>
       </c>
       <c r="G65" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="45" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B66" s="45" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>246</v>
@@ -7544,15 +7675,15 @@
         <v>0.99</v>
       </c>
       <c r="G66" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" s="45" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B67" s="45" t="s">
         <v>256</v>
@@ -7572,21 +7703,21 @@
         <v>0.99</v>
       </c>
       <c r="G67" s="52" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15" customHeight="1">
       <c r="A68" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B68" s="45" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C68" s="45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D68" s="46">
         <v>0.33</v>
@@ -7600,21 +7731,21 @@
         <v>0.66</v>
       </c>
       <c r="G68" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C69" s="45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D69" s="46">
         <v>0.5</v>
@@ -7628,21 +7759,21 @@
         <v>1</v>
       </c>
       <c r="G69" s="49" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="45" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C70" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D70" s="46">
         <v>0</v>
@@ -7656,15 +7787,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="49" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s">
         <v>245</v>
@@ -7684,15 +7815,15 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H71" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s">
         <v>245</v>
@@ -7712,18 +7843,18 @@
         <v>0.8</v>
       </c>
       <c r="G72" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H72" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="C73" t="s">
         <v>44</v>
@@ -7740,18 +7871,18 @@
         <v>0.66</v>
       </c>
       <c r="G73" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H73" t="s">
-        <v>1130</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="C74" t="s">
         <v>44</v>
@@ -7768,18 +7899,18 @@
         <v>0.66</v>
       </c>
       <c r="G74" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H74" t="s">
-        <v>1131</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B75" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="C75" t="s">
         <v>246</v>
@@ -7796,10 +7927,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H75" t="s">
-        <v>1132</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -7828,30 +7959,30 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="G2" s="94" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="H2" s="95">
         <v>10</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="J2" s="95">
         <v>244</v>
       </c>
       <c r="K2" s="94" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="L2" s="96">
         <f>B25</f>
@@ -7864,21 +7995,21 @@
         <v/>
       </c>
       <c r="G3" s="94" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="H3" s="98">
         <f>$J$2-$L$2</f>
         <v>3</v>
       </c>
       <c r="I3" s="94" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="J3" s="98">
         <f>ROUND($L$2*7/$H$2,1)</f>
         <v>168.7</v>
       </c>
       <c r="K3" s="94" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="L3" s="98" t="str">
         <f>IF($H$3&lt;0,"INVALID","VALID")</f>
@@ -7890,19 +8021,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="J4" s="99" t="str">
         <f>"주당 환산 (×7/"&amp;$H$2&amp;")"</f>
@@ -7930,10 +8061,10 @@
         <v>유지</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>569</v>
-      </c>
-      <c r="G5" s="115" t="s">
-        <v>570</v>
+        <v>562</v>
+      </c>
+      <c r="G5" s="116" t="s">
+        <v>563</v>
       </c>
       <c r="H5" s="56">
         <f ca="1">SUM(D5:D6)</f>
@@ -7973,9 +8104,9 @@
         <v>성장</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="G6" s="116"/>
+        <v>564</v>
+      </c>
+      <c r="G6" s="117"/>
       <c r="J6" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>12.6</v>
@@ -8006,10 +8137,10 @@
         <v>성장</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>572</v>
-      </c>
-      <c r="G7" s="115" t="s">
-        <v>573</v>
+        <v>565</v>
+      </c>
+      <c r="G7" s="116" t="s">
+        <v>566</v>
       </c>
       <c r="H7" s="56">
         <f ca="1">SUM(D7:D10)</f>
@@ -8026,7 +8157,7 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
       <c r="A8" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B8" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A8)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A8)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A8)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A8)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A8)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A8)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A8)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A8)</f>
@@ -8045,9 +8176,9 @@
         <v>유지 미만</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>574</v>
-      </c>
-      <c r="G8" s="116"/>
+        <v>567</v>
+      </c>
+      <c r="G8" s="117"/>
       <c r="J8" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -8078,9 +8209,9 @@
         <v>유지</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>575</v>
-      </c>
-      <c r="G9" s="116"/>
+        <v>568</v>
+      </c>
+      <c r="G9" s="117"/>
       <c r="J9" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.8000000000000007</v>
@@ -8111,9 +8242,9 @@
         <v>성장</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>576</v>
-      </c>
-      <c r="G10" s="116"/>
+        <v>569</v>
+      </c>
+      <c r="G10" s="117"/>
       <c r="J10" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>15.4</v>
@@ -8144,7 +8275,7 @@
         <v>유지</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="G11" s="57"/>
       <c r="J11" s="55">
@@ -8177,7 +8308,7 @@
         <v>성장</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="G12" s="57"/>
       <c r="J12" s="55">
@@ -8210,7 +8341,7 @@
         <v>성장</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="G13" s="57"/>
       <c r="J13" s="55">
@@ -8243,7 +8374,7 @@
         <v>성장</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="56"/>
@@ -8258,7 +8389,7 @@
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1">
       <c r="A15" s="53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B15" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A15)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A15)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A15)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A15)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A15)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A15)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A15)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A15)</f>
@@ -8277,10 +8408,10 @@
         <v>성장</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="H15" s="56">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -8297,7 +8428,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1">
       <c r="A16" s="53" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B16" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A16)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A16)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A16)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A16)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A16)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A16)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A16)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A16)</f>
@@ -8316,7 +8447,7 @@
         <v>유지</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G16" s="57"/>
       <c r="J16" s="55">
@@ -8330,7 +8461,7 @@
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" s="53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B17" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A17)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A17)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A17)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A17)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A17)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A17)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A17)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A17)</f>
@@ -8349,10 +8480,10 @@
         <v>성장</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>583</v>
-      </c>
-      <c r="G17" s="115" t="s">
-        <v>323</v>
+        <v>576</v>
+      </c>
+      <c r="G17" s="116" t="s">
+        <v>322</v>
       </c>
       <c r="H17" s="56">
         <f ca="1">SUM(D17:D18)</f>
@@ -8388,9 +8519,9 @@
         <v>유지</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>584</v>
-      </c>
-      <c r="G18" s="116"/>
+        <v>577</v>
+      </c>
+      <c r="G18" s="117"/>
       <c r="J18" s="55">
         <f t="shared" ca="1" si="2"/>
         <v>9.1</v>
@@ -8421,7 +8552,7 @@
         <v>유지</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="G19" s="57"/>
       <c r="J19" s="55">
@@ -8454,7 +8585,7 @@
         <v>성장</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>1133</v>
+        <v>1119</v>
       </c>
       <c r="G20" s="57"/>
       <c r="J20" s="55">
@@ -8487,7 +8618,7 @@
         <v>성장</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="G21" s="57"/>
       <c r="J21" s="55">
@@ -8520,7 +8651,7 @@
         <v>성장</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="G22" s="57"/>
       <c r="J22" s="55">
@@ -8553,7 +8684,7 @@
         <v>유지</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G23" s="57"/>
       <c r="J23" s="55">
@@ -8567,7 +8698,7 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="A24" s="53" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B24" s="59">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A24)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A24)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A24)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A24)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A24)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A24)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A24)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A24)</f>
@@ -8586,7 +8717,7 @@
         <v>유지</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="G24" s="57"/>
       <c r="J24" s="55">
@@ -8600,7 +8731,7 @@
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
@@ -8624,22 +8755,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="48" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="48" customHeight="1">
@@ -8647,22 +8778,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
@@ -8670,124 +8801,124 @@
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="77.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="39" customHeight="1">
       <c r="A39" s="63" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="48" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48" customHeight="1">
       <c r="A44" s="90" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51.75" customHeight="1">
       <c r="A45" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="90" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="48" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="93" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="100" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="B58" s="100" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="C58" s="100" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="D58" s="100" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="E58" s="100" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -8801,7 +8932,7 @@
         <v>239</v>
       </c>
       <c r="D59" s="102" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="E59" s="102" t="s">
         <v>150</v>
@@ -8818,10 +8949,10 @@
         <v>239</v>
       </c>
       <c r="D60" s="107" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="E60" s="107" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -8835,45 +8966,45 @@
         <v>244</v>
       </c>
       <c r="D61" s="111" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="E61" s="111" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="104" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -8923,50 +9054,50 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="64" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="64" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="64" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -8975,13 +9106,13 @@
     </row>
     <row r="8" spans="1:13" ht="84" customHeight="1">
       <c r="A8" s="64" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8989,40 +9120,40 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L9" s="100" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="M9" s="100" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9171,7 +9302,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="65" t="s">
-        <v>1136</v>
+        <v>1122</v>
       </c>
       <c r="L14" s="103"/>
       <c r="M14" s="103"/>
@@ -9381,17 +9512,17 @@
     </row>
     <row r="23" spans="1:13" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="120" customHeight="1">
@@ -9399,52 +9530,52 @@
     </row>
     <row r="27" spans="1:13" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -9465,45 +9596,45 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -9511,80 +9642,80 @@
         <v>272</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="67" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="67" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -9592,47 +9723,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -9658,31 +9789,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="70" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>7</v>
@@ -9691,111 +9822,111 @@
         <v>148</v>
       </c>
       <c r="G5" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="71" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E6" s="71">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="G6" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="G7" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D8" s="71" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="E8" s="71">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="73" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="G8" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B9" s="72" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="E9" s="71">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="73" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="G9" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="71" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C10" s="72" t="s">
         <v>150</v>
@@ -9810,7 +9941,7 @@
         <v>150</v>
       </c>
       <c r="G10" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -9825,7 +9956,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -9846,32 +9977,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -9879,22 +10010,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -9902,32 +10033,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -9935,47 +10066,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="74" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -9985,27 +10116,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -10036,12 +10167,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10093,7 +10224,7 @@
         <v>99</v>
       </c>
       <c r="C5" s="67" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D5" s="75">
         <f>시작중량_설정!$E$7</f>
@@ -10116,10 +10247,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="K5" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>294</v>
@@ -10130,7 +10261,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="C6" s="67" t="s">
         <v>27</v>
@@ -10156,13 +10287,13 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="K6" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="L6" s="68" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10170,10 +10301,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>150</v>
@@ -10195,10 +10326,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="K7" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10206,10 +10337,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>150</v>
@@ -10231,10 +10362,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="K8" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10242,10 +10373,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>150</v>
@@ -10267,10 +10398,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="K9" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10278,13 +10409,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>336</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -10303,10 +10434,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="K10" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10339,10 +10470,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="K11" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10350,13 +10481,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="87" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="76" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -10375,10 +10506,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="K12" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -10411,10 +10542,10 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="K13" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
@@ -10437,72 +10568,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
     </row>
   </sheetData>
@@ -10533,12 +10664,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10613,10 +10744,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="K5" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -10624,13 +10755,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>246</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -10649,13 +10780,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="K6" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="L6" s="53" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10663,7 +10794,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>238</v>
@@ -10688,10 +10819,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="K7" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10724,13 +10855,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="K8" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="L8" s="53" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -10738,13 +10869,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>246</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -10763,10 +10894,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="K9" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10774,13 +10905,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -10799,10 +10930,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="K10" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10835,13 +10966,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="K11" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="L11" s="53" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10849,7 +10980,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>289</v>
@@ -10874,10 +11005,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="K12" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -10885,13 +11016,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="76" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E13" s="28">
         <v>3</v>
@@ -10910,10 +11041,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="K13" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -10921,7 +11052,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -10946,10 +11077,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="K14" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -10957,7 +11088,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -10982,10 +11113,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="K15" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
@@ -11008,112 +11139,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="63" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -11144,12 +11275,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -11204,7 +11335,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E5" s="67">
         <v>4</v>
@@ -11223,7 +11354,7 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="K5" t="s">
         <v>32</v>
@@ -11259,10 +11390,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="K6" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11270,13 +11401,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -11295,10 +11426,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="K7" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11306,7 +11437,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>23</v>
@@ -11331,10 +11462,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="K8" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11342,13 +11473,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -11367,10 +11498,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="K9" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11403,10 +11534,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="K10" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11414,13 +11545,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -11439,10 +11570,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="K11" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -11475,10 +11606,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="K12" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -11486,10 +11617,10 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" t="s">
         <v>331</v>
-      </c>
-      <c r="C13" t="s">
-        <v>332</v>
       </c>
       <c r="D13" t="s">
         <v>150</v>
@@ -11511,10 +11642,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="K13" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -11522,7 +11653,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C14" s="87" t="s">
         <v>261</v>
@@ -11547,10 +11678,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="K14" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
@@ -11569,72 +11700,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
     </row>
   </sheetData>
@@ -11665,12 +11796,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -11745,10 +11876,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="K5" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>294</v>
@@ -11759,13 +11890,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>300</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -11784,10 +11915,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="K6" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11795,7 +11926,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>300</v>
@@ -11820,10 +11951,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="K7" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11831,7 +11962,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="89" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>246</v>
@@ -11856,10 +11987,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="K8" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11867,7 +11998,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>238</v>
@@ -11892,10 +12023,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="K9" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11928,10 +12059,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="K10" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11939,13 +12070,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -11964,10 +12095,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="K11" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -11999,27 +12130,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
     </row>
   </sheetData>
@@ -12031,7 +12162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -12089,7 +12220,7 @@
       </c>
       <c r="F5" s="20" t="str">
         <f>"약 "&amp;INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))&amp;"분"</f>
-        <v>약 72분</v>
+        <v>약 74분</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
@@ -12103,7 +12234,7 @@
         <v>153</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="E6" s="20">
         <f>INDEX(D2_밀기A!$E:$E,MATCH("세트 합계",D2_밀기A!$D:$D,0))</f>
@@ -12111,7 +12242,7 @@
       </c>
       <c r="F6" s="20" t="str">
         <f>"약 "&amp;INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))&amp;"분"</f>
-        <v>약 68분</v>
+        <v>약 71분</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
@@ -12147,7 +12278,7 @@
         <v>150</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="E8" s="20">
         <f>INDEX(D4_어깨팔A!$E:$E,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))</f>
@@ -12155,7 +12286,7 @@
       </c>
       <c r="F8" s="20" t="str">
         <f>"약 "&amp;INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))&amp;"분"</f>
-        <v>약 71분</v>
+        <v>약 72분</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
@@ -12189,7 +12320,7 @@
         <v>150</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="E10" s="20">
         <f>INDEX(D6_당기기B!$E:$E,MATCH("세트 합계",D6_당기기B!$D:$D,0))</f>
@@ -12197,7 +12328,7 @@
       </c>
       <c r="F10" s="20" t="str">
         <f>"약 "&amp;INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))&amp;"분"</f>
-        <v>약 72분</v>
+        <v>약 75분</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
@@ -12211,7 +12342,7 @@
         <v>161</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="E11" s="20">
         <f>INDEX(D7_밀기B!$E:$E,MATCH("세트 합계",D7_밀기B!$D:$D,0))</f>
@@ -12219,7 +12350,7 @@
       </c>
       <c r="F11" s="20" t="str">
         <f>"약 "&amp;INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))&amp;"분"</f>
-        <v>약 72분</v>
+        <v>약 73분</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
@@ -12241,7 +12372,7 @@
       </c>
       <c r="F12" s="20" t="str">
         <f>"약 "&amp;INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))&amp;"분"</f>
-        <v>약 73분</v>
+        <v>약 74분</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
@@ -12255,7 +12386,7 @@
         <v>150</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="E13" s="20">
         <f>INDEX(D9_어깨팔B!$E:$E,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))</f>
@@ -12299,7 +12430,7 @@
       </c>
       <c r="F15" t="str">
         <f>"약 "&amp;(INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0)))&amp;"분 ("&amp;INT((INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0)))/60)&amp;"시간 "&amp;MOD((INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))),60)&amp;"분)"</f>
-        <v>약 568분 (9시간 28분)</v>
+        <v>약 579분 (9시간 39분)</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="89.25" customHeight="1"/>
@@ -12393,32 +12524,32 @@
     </row>
     <row r="35" spans="1:1" ht="90" customHeight="1">
       <c r="A35" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="90" customHeight="1">
       <c r="A36" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="90" customHeight="1">
       <c r="A37" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="90" customHeight="1">
       <c r="A38" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="90" customHeight="1">
       <c r="A39" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="90" customHeight="1">
       <c r="A40" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="51.75" customHeight="1">
@@ -12681,6 +12812,26 @@
     <row r="96" spans="1:1" ht="242.25" customHeight="1">
       <c r="A96" s="30" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="112" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>1151</v>
       </c>
     </row>
   </sheetData>
@@ -12702,166 +12853,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>150</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="79" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="B13" s="80" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="C13" s="80" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="D13" s="79" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="B14" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="C14" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="D14" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -12872,22 +13023,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -12895,137 +13046,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="63" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
     </row>
   </sheetData>
@@ -13051,17 +13202,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -13070,41 +13221,41 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="B6" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C6" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E6" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="F6" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="G6" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="H6" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
@@ -13121,18 +13272,18 @@
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H7" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B8" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -13149,18 +13300,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H8" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B9" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -13177,18 +13328,18 @@
         <v>0.8</v>
       </c>
       <c r="G9" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H9" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B10" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -13205,15 +13356,15 @@
         <v>1.32</v>
       </c>
       <c r="G10" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H10" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B11" t="s">
         <v>237</v>
@@ -13233,15 +13384,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H11" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -13261,18 +13412,18 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H12" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B13" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
@@ -13289,15 +13440,15 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H13" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -13317,18 +13468,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H15" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B16" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -13345,15 +13496,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H16" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B17" t="s">
         <v>295</v>
@@ -13373,15 +13524,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H17" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B18" t="s">
         <v>103</v>
@@ -13401,18 +13552,18 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H18" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B19" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -13429,15 +13580,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H19" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B20" t="s">
         <v>295</v>
@@ -13457,18 +13608,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H20" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B21" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -13485,18 +13636,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H21" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B22" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C22" t="s">
         <v>238</v>
@@ -13513,18 +13664,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H22" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B23" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C23" t="s">
         <v>238</v>
@@ -13541,18 +13692,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H23" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B24" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C24" t="s">
         <v>246</v>
@@ -13569,18 +13720,18 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H24" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="B25" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C25" t="s">
         <v>246</v>
@@ -13597,18 +13748,18 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H25" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="B26" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C26" t="s">
         <v>246</v>
@@ -13625,18 +13776,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H26" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B27" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="C27" t="s">
         <v>246</v>
@@ -13653,21 +13804,21 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H27" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B28" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="C28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D28">
         <v>0.2</v>
@@ -13681,21 +13832,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H28" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B29" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D29">
         <v>0.2</v>
@@ -13709,21 +13860,21 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H29" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D30">
         <v>0.2</v>
@@ -13737,15 +13888,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H30" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B31" t="s">
         <v>237</v>
@@ -13765,18 +13916,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H31" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B32" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
@@ -13793,15 +13944,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H32" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B33" t="s">
         <v>99</v>
@@ -13821,18 +13972,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H33" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B34" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C34" t="s">
         <v>272</v>
@@ -13849,18 +14000,18 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H34" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B35" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C35" t="s">
         <v>272</v>
@@ -13877,21 +14028,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H35" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B36" t="s">
         <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D36">
         <v>0.5</v>
@@ -13905,21 +14056,21 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H36" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B37" t="s">
         <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D37">
         <v>0.5</v>
@@ -13933,21 +14084,21 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H37" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B38" t="s">
+        <v>321</v>
+      </c>
+      <c r="C38" t="s">
         <v>322</v>
-      </c>
-      <c r="C38" t="s">
-        <v>323</v>
       </c>
       <c r="D38">
         <v>0.33</v>
@@ -13961,21 +14112,21 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H38" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="B39" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D39">
         <v>0.5</v>
@@ -13989,21 +14140,21 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H39" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B40" t="s">
         <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D40">
         <v>0.5</v>
@@ -14017,21 +14168,21 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H40" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B41" t="s">
         <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D41">
         <v>0.2</v>
@@ -14045,21 +14196,21 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H41" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D42">
         <v>0.2</v>
@@ -14073,15 +14224,15 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H42" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -14101,18 +14252,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H43" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B44" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C44" t="s">
         <v>45</v>
@@ -14129,15 +14280,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H44" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -14157,18 +14308,18 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H45" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B46" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C46" t="s">
         <v>289</v>
@@ -14185,15 +14336,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H46" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B47" t="s">
         <v>101</v>
@@ -14213,15 +14364,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H47" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -14241,15 +14392,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H48" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -14269,18 +14420,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H49" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B50" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C50" t="s">
         <v>289</v>
@@ -14297,18 +14448,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H50" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B51" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -14325,10 +14476,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H51" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
     </row>
   </sheetData>
@@ -14354,12 +14505,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -14367,22 +14518,22 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C4" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="D4" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="E4" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F4" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="G4" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -14406,13 +14557,13 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="G5" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="H5" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="I5">
         <f ca="1">SUM(D5:D6)</f>
@@ -14440,10 +14591,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="G6" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -14467,13 +14618,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="G7" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="H7" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -14482,7 +14633,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B8">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A8)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A8)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A8)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A8)</f>
@@ -14501,10 +14652,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="G8" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14528,10 +14679,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="G9" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14555,10 +14706,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="G10" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14582,10 +14733,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="G11" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14609,10 +14760,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="G12" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14636,10 +14787,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="G13" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -14663,15 +14814,15 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="G14" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B15">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A15)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A15)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A15)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A15)</f>
@@ -14690,13 +14841,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="G15" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="H15" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -14705,7 +14856,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B16">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A16)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A16)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A16)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A16)</f>
@@ -14724,15 +14875,15 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="G16" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B17">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A17)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A17)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A17)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A17)</f>
@@ -14751,10 +14902,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="G17" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -14778,10 +14929,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="G18" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -14805,10 +14956,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="G19" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -14832,10 +14983,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="G20" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -14859,10 +15010,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="G21" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -14886,10 +15037,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="G22" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -14913,15 +15064,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="G23" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B24">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A24)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A24)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A24)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A24)</f>
@@ -14940,15 +15091,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="G24" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B25">
         <f>SUM(B5:B24)</f>
@@ -14961,67 +15112,67 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -15032,7 +15183,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -15045,29 +15196,30 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1">
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="33" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1">
+    <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
         <v>3</v>
       </c>
@@ -15110,8 +15262,11 @@
       <c r="N5" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O5" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" customHeight="1">
       <c r="A6" s="20">
         <v>1</v>
       </c>
@@ -15137,7 +15292,7 @@
         <v>155</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND((E6*(G6+H6)+O6)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J6" s="21" t="s">
@@ -15152,8 +15307,9 @@
       <c r="M6" s="26" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:15" ht="16.5" customHeight="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
@@ -15186,18 +15342,19 @@
         <v>44</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:15" ht="16.5" customHeight="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>238</v>
@@ -15209,7 +15366,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -15218,20 +15375,23 @@
         <v>120</v>
       </c>
       <c r="I8" s="26">
-        <f>IF(E8=0,0,ROUND(E8*(G8+H8)/60,1))</f>
-        <v>6.7</v>
+        <f t="shared" si="0"/>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>44</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="16.5" customHeight="1">
+        <v>1109</v>
+      </c>
+      <c r="O8" s="26">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" customHeight="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
@@ -15269,8 +15429,9 @@
       <c r="L9" s="21" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O9" s="26"/>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
@@ -15308,8 +15469,9 @@
       <c r="L10" s="21" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O10" s="26"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
       <c r="A11" s="20">
         <v>6</v>
       </c>
@@ -15347,8 +15509,9 @@
       <c r="L11" s="22" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O11" s="26"/>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
@@ -15384,8 +15547,9 @@
       <c r="L12" s="86" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O12" s="26"/>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
@@ -15421,8 +15585,9 @@
       <c r="L13" s="86" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1">
+      <c r="O13" s="26"/>
+    </row>
+    <row r="14" spans="1:15" ht="15" customHeight="1">
       <c r="A14" s="20">
         <v>9</v>
       </c>
@@ -15458,8 +15623,9 @@
       <c r="L14" s="86" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1">
+      <c r="O14" s="26"/>
+    </row>
+    <row r="15" spans="1:15" ht="15" customHeight="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
@@ -15497,8 +15663,9 @@
       <c r="L15" s="36" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1">
+      <c r="O15" s="26"/>
+    </row>
+    <row r="16" spans="1:15" ht="15" customHeight="1">
       <c r="A16" s="20">
         <v>11</v>
       </c>
@@ -15534,6 +15701,7 @@
       <c r="L16" s="36" t="s">
         <v>278</v>
       </c>
+      <c r="O16" s="26"/>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1">
       <c r="A17" s="20"/>
@@ -15551,7 +15719,7 @@
       <c r="H17" s="26"/>
       <c r="I17" s="26">
         <f>ROUND(SUM(I6:I16),0)</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="36"/>
@@ -15560,11 +15728,26 @@
     <row r="18" spans="1:12" ht="15" customHeight="1"/>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="112" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -15578,7 +15761,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N16">
+  <conditionalFormatting sqref="A6:O16">
     <cfRule type="expression" dxfId="10" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -15593,7 +15776,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -15606,6 +15789,7 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
@@ -15615,7 +15799,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -15719,12 +15903,12 @@
         <v>287</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1">
+    <row r="18" spans="1:15" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16.5" customHeight="1">
+    <row r="19" spans="1:15" ht="16.5" customHeight="1">
       <c r="A19" s="34" t="s">
         <v>3</v>
       </c>
@@ -15767,8 +15951,11 @@
       <c r="N19" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O19" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.5" customHeight="1">
       <c r="A20" s="38">
         <v>1</v>
       </c>
@@ -15795,7 +15982,7 @@
         <v>180</v>
       </c>
       <c r="I20" s="38">
-        <f t="shared" ref="I20:I25" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
+        <f t="shared" ref="I20:I25" si="0">IF(E20=0,0,ROUND((E20*(G20+H20)+O20)/60,1))</f>
         <v>17.5</v>
       </c>
       <c r="J20" s="39" t="s">
@@ -15810,8 +15997,9 @@
       <c r="M20" s="38" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O20" s="38"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1">
       <c r="A21" s="20">
         <v>2</v>
       </c>
@@ -15852,8 +16040,9 @@
       <c r="M21" s="26" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O21" s="26"/>
+    </row>
+    <row r="22" spans="1:15" ht="16.5" customHeight="1">
       <c r="A22" s="20">
         <v>3</v>
       </c>
@@ -15889,8 +16078,9 @@
       <c r="L22" s="21" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O22" s="26"/>
+    </row>
+    <row r="23" spans="1:15" ht="16.5" customHeight="1">
       <c r="A23" s="20">
         <v>4</v>
       </c>
@@ -15917,22 +16107,25 @@
       </c>
       <c r="I23" s="26">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L23" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="L23" s="21" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O23" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.5" customHeight="1">
       <c r="A24" s="20">
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C24" s="43" t="s">
         <v>23</v>
@@ -15954,20 +16147,25 @@
       </c>
       <c r="I24" s="26">
         <f t="shared" si="0"/>
-        <v>9.1999999999999993</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
+      <c r="K24" s="21" t="s">
+        <v>1136</v>
+      </c>
       <c r="L24" s="86" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="16.5" customHeight="1">
+        <v>311</v>
+      </c>
+      <c r="O24" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="16.5" customHeight="1">
       <c r="A25" s="20">
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>39</v>
@@ -15989,17 +16187,20 @@
       </c>
       <c r="I25" s="26">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1072</v>
+        <v>1137</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="16.5" customHeight="1">
+        <v>365</v>
+      </c>
+      <c r="O25" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.5" customHeight="1">
       <c r="D26" s="3" t="s">
         <v>63</v>
       </c>
@@ -16009,13 +16210,27 @@
       </c>
       <c r="I26">
         <f>ROUND(SUM(I20:I25),0)</f>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="16.5" customHeight="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A27" s="112" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>1134</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A20:N25">
+  <conditionalFormatting sqref="A20:O25">
     <cfRule type="expression" dxfId="9" priority="1">
       <formula>$E20=0</formula>
     </cfRule>
@@ -16027,7 +16242,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -16040,24 +16255,25 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A2" s="18" t="s">
+    <row r="4" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
@@ -16068,7 +16284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1">
+    <row r="6" spans="1:15" ht="15" customHeight="1">
       <c r="A6" s="20">
         <f>MAX(20,MROUND(시작중량_설정!$E$7*0.4,2.5))</f>
         <v>22.5</v>
@@ -16080,7 +16296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1">
+    <row r="7" spans="1:15" ht="15" customHeight="1">
       <c r="A7" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$7*0.6,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$7*0.4,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$7*0.6,2.5)))</f>
         <v>35</v>
@@ -16092,7 +16308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1">
+    <row r="8" spans="1:15" ht="15" customHeight="1">
       <c r="A8" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$7*0.75,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$7*0.6,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$7*0.75,2.5)))</f>
         <v>42.5</v>
@@ -16104,7 +16320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1">
+    <row r="9" spans="1:15" ht="15" customHeight="1">
       <c r="A9" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$7*0.9,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$7*0.75,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$7*0.9,2.5)))</f>
         <v>52.5</v>
@@ -16116,7 +16332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1">
+    <row r="10" spans="1:15" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$7</f>
         <v>57.5</v>
@@ -16128,17 +16344,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1">
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1">
+    <row r="13" spans="1:15" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16.5" customHeight="1">
+    <row r="14" spans="1:15" ht="16.5" customHeight="1">
       <c r="A14" s="34" t="s">
         <v>3</v>
       </c>
@@ -16181,16 +16397,19 @@
       <c r="N14" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O14" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1">
       <c r="A15" s="40">
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="40" t="s">
         <v>316</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>317</v>
       </c>
       <c r="D15" s="41">
         <f>시작중량_설정!$E$7</f>
@@ -16209,31 +16428,32 @@
         <v>193</v>
       </c>
       <c r="I15" s="38">
-        <f t="shared" ref="I15:I21" si="0">IF(E15=0,0,ROUND(E15*(G15+H15)/60,1))</f>
+        <f t="shared" ref="I15:I21" si="0">IF(E15=0,0,ROUND((E15*(G15+H15)+O15)/60,1))</f>
         <v>19</v>
       </c>
       <c r="J15" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="K15" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="L15" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="L15" s="39" t="s">
+      <c r="M15" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="M15" s="38" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O15" s="38"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1">
       <c r="A16" s="20">
         <v>2</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D16" s="26">
         <v>120</v>
@@ -16255,24 +16475,25 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J16" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="K16" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="K16" s="21" t="s">
+      <c r="L16" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="L16" s="21" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O16" s="26"/>
+    </row>
+    <row r="17" spans="1:15" ht="16.5" customHeight="1">
       <c r="A17" s="20">
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>247</v>
@@ -16281,7 +16502,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G17" s="26">
         <v>90</v>
@@ -16294,24 +16515,25 @@
         <v>12</v>
       </c>
       <c r="J17" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="K17" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="K17" s="21" t="s">
+      <c r="L17" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="L17" s="21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O17" s="26"/>
+    </row>
+    <row r="18" spans="1:15" ht="16.5" customHeight="1">
       <c r="A18" s="20">
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>331</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>332</v>
       </c>
       <c r="D18" s="26">
         <v>40</v>
@@ -16334,21 +16556,22 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="L18" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="L18" s="21" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O18" s="26"/>
+    </row>
+    <row r="19" spans="1:15" ht="16.5" customHeight="1">
       <c r="A19" s="20">
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>335</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>336</v>
       </c>
       <c r="D19" s="26">
         <v>35</v>
@@ -16371,21 +16594,22 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="L19" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="L19" s="21" t="s">
+      <c r="N19" t="s">
         <v>338</v>
       </c>
-      <c r="N19" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O19" s="26"/>
+    </row>
+    <row r="20" spans="1:15" ht="16.5" customHeight="1">
       <c r="A20" s="20">
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>60</v>
@@ -16411,21 +16635,22 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="L20" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="L20" s="21" t="s">
-        <v>342</v>
-      </c>
       <c r="N20" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="16.5" customHeight="1">
+        <v>338</v>
+      </c>
+      <c r="O20" s="26"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1">
       <c r="A21" s="20">
         <v>7</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>261</v>
@@ -16451,13 +16676,14 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="L21" s="21" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1">
+      <c r="O21" s="26"/>
+    </row>
+    <row r="22" spans="1:15" ht="15" customHeight="1">
       <c r="D22" s="3" t="s">
         <v>63</v>
       </c>
@@ -16470,10 +16696,10 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1"/>
+    <row r="23" spans="1:15" ht="15" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A15:N21">
+  <conditionalFormatting sqref="A15:O21">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>$E15=0</formula>
     </cfRule>
@@ -16485,7 +16711,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -16498,29 +16724,30 @@
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="30" customHeight="1">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1">
+    <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
         <v>3</v>
       </c>
@@ -16563,13 +16790,16 @@
       <c r="N5" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O5" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" customHeight="1">
       <c r="A6" s="20">
         <v>1</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>18</v>
@@ -16590,23 +16820,24 @@
         <v>70</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND((E6*(G6+H6)+O6)/60,1))</f>
         <v>5.5</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="L6" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="L6" s="21" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:15" ht="16.5" customHeight="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>18</v>
@@ -16631,21 +16862,22 @@
         <v>5.8</v>
       </c>
       <c r="J7" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="K7" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="L7" s="21" t="s">
         <v>352</v>
       </c>
-      <c r="L7" s="21" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:15" ht="16.5" customHeight="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>23</v>
@@ -16670,21 +16902,22 @@
         <v>5.5</v>
       </c>
       <c r="J8" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="K8" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="L8" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="L8" s="21" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" customHeight="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>23</v>
@@ -16709,27 +16942,28 @@
         <v>6</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K9" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="L9" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O9" s="26"/>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
       <c r="B10" s="91" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E10" s="20">
         <v>3</v>
@@ -16749,13 +16983,14 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1109</v>
+        <v>1099</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1">
+        <v>403</v>
+      </c>
+      <c r="O10" s="26"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
       <c r="A11" s="20">
         <v>6</v>
       </c>
@@ -16788,25 +17023,26 @@
         <v>302</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
       <c r="L11" s="36" t="s">
         <v>303</v>
       </c>
       <c r="M11" s="92"/>
-    </row>
-    <row r="12" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O11" s="26"/>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>289</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
@@ -16822,19 +17058,22 @@
       </c>
       <c r="I12" s="26">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>27</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>364</v>
+        <v>1139</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="16.5" customHeight="1">
+        <v>363</v>
+      </c>
+      <c r="O12" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
@@ -16845,7 +17084,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E13" s="20">
         <v>3</v>
@@ -16867,13 +17106,14 @@
         <v>45</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="16.5" customHeight="1">
+        <v>368</v>
+      </c>
+      <c r="O13" s="26"/>
+    </row>
+    <row r="14" spans="1:15" ht="16.5" customHeight="1">
       <c r="A14" s="20">
         <v>9</v>
       </c>
@@ -16904,13 +17144,14 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O14" s="26"/>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
@@ -16943,13 +17184,14 @@
         <v>53</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O15" s="26"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1">
       <c r="A16" s="20">
         <v>11</v>
       </c>
@@ -16980,11 +17222,12 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>407</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O16" s="26"/>
     </row>
     <row r="17" spans="1:9" ht="16.5" customHeight="1">
       <c r="D17" s="3" t="s">
@@ -16996,91 +17239,103 @@
       </c>
       <c r="I17">
         <f>ROUND(SUM(I6:I16),0)</f>
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="19" spans="1:9" ht="16.5" customHeight="1">
       <c r="A19" s="108" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="109" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16.5" customHeight="1">
       <c r="A21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.5" customHeight="1">
       <c r="A22" s="109" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1">
       <c r="A23" s="109" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5" customHeight="1">
       <c r="A24" s="109" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" customHeight="1">
       <c r="A25" s="109" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5" customHeight="1">
       <c r="A26" s="109" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" customHeight="1">
       <c r="A28" s="109" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="30" spans="1:9" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" customHeight="1">
       <c r="A31" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" customHeight="1">
       <c r="A32" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="35" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="36" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="37" spans="1:1" ht="16.5" customHeight="1"/>
+    <row r="35" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A35" s="112" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A36" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A37" t="s">
+        <v>1134</v>
+      </c>
+    </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N16">
+  <conditionalFormatting sqref="A6:O16">
     <cfRule type="expression" dxfId="7" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -17091,7 +17346,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -17104,29 +17359,30 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="33" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
         <v>3</v>
       </c>
@@ -17169,13 +17425,16 @@
       <c r="N5" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O5" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" customHeight="1">
       <c r="A6" s="20">
         <v>1</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>246</v>
@@ -17196,25 +17455,26 @@
         <v>150</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND((E6*(G6+H6)+O6)/60,1))</f>
         <v>15.8</v>
       </c>
       <c r="J6" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="L6" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="K6" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:15" ht="16.5" customHeight="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>238</v>
@@ -17239,21 +17499,22 @@
         <v>9.5</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="16.5" customHeight="1">
+        <v>389</v>
+      </c>
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:15" ht="16.5" customHeight="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>238</v>
@@ -17265,7 +17526,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -17274,25 +17535,28 @@
         <v>150</v>
       </c>
       <c r="I8" s="26">
-        <f>IF(E8=0,0,ROUND(E8*(G8+H8)/60,1))</f>
-        <v>7.7</v>
+        <f t="shared" si="0"/>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>1126</v>
+        <v>1141</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="16.5" customHeight="1">
+        <v>1113</v>
+      </c>
+      <c r="O8" s="26">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" customHeight="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>246</v>
@@ -17317,21 +17581,22 @@
         <v>6.7</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>1128</v>
+        <v>1114</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="16.5" customHeight="1">
+        <v>392</v>
+      </c>
+      <c r="O9" s="26"/>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>23</v>
@@ -17356,21 +17621,22 @@
         <v>0</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1">
+        <v>394</v>
+      </c>
+      <c r="O10" s="26"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
       <c r="A11" s="20">
         <v>6</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>44</v>
@@ -17392,27 +17658,30 @@
       </c>
       <c r="I11" s="26">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>45</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>398</v>
+        <v>1142</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="16.5" customHeight="1">
+        <v>396</v>
+      </c>
+      <c r="O11" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D12" s="20">
         <v>20</v>
@@ -17434,16 +17703,17 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="16.5" customHeight="1">
+        <v>400</v>
+      </c>
+      <c r="O12" s="26"/>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
@@ -17474,13 +17744,14 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O13" s="26"/>
+    </row>
+    <row r="14" spans="1:15" ht="16.5" customHeight="1">
       <c r="A14" s="20">
         <v>9</v>
       </c>
@@ -17511,13 +17782,14 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O14" s="26"/>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
@@ -17553,8 +17825,9 @@
       <c r="L15" s="21" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1">
+      <c r="O15" s="26"/>
+    </row>
+    <row r="16" spans="1:15" ht="15" customHeight="1">
       <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
@@ -17564,35 +17837,48 @@
       </c>
       <c r="I16">
         <f>ROUND(SUM(I6:I15),0)</f>
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>1129</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
+      <c r="A22" s="112" t="s">
+        <v>1132</v>
+      </c>
       <c r="B22" s="83"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>1134</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N15">
+  <conditionalFormatting sqref="A6:O15">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -17604,7 +17890,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -17617,21 +17903,22 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1102</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -17730,12 +18017,12 @@
         <v>287</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1">
+    <row r="18" spans="1:15" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16.5" customHeight="1">
+    <row r="19" spans="1:15" ht="16.5" customHeight="1">
       <c r="A19" s="34" t="s">
         <v>3</v>
       </c>
@@ -17778,13 +18065,16 @@
       <c r="N19" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O19" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.5" customHeight="1">
       <c r="A20" s="40">
         <v>1</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C20" s="40" t="s">
         <v>27</v>
@@ -17806,23 +18096,24 @@
         <v>180</v>
       </c>
       <c r="I20" s="38">
-        <f t="shared" ref="I20:I29" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
+        <f t="shared" ref="I20:I29" si="0">IF(E20=0,0,ROUND((E20*(G20+H20)+O20)/60,1))</f>
         <v>10.5</v>
       </c>
       <c r="J20" s="39" t="s">
         <v>30</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L20" s="39" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="M20" s="38" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="16.5" customHeight="1">
+        <v>412</v>
+      </c>
+      <c r="O20" s="38"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1">
       <c r="A21" s="20">
         <v>2</v>
       </c>
@@ -17852,21 +18143,22 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="16.5" customHeight="1">
+        <v>415</v>
+      </c>
+      <c r="O21" s="26"/>
+    </row>
+    <row r="22" spans="1:15" ht="16.5" customHeight="1">
       <c r="A22" s="20">
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>34</v>
@@ -17894,18 +18186,19 @@
         <v>249</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="16.5" customHeight="1">
+        <v>417</v>
+      </c>
+      <c r="O22" s="26"/>
+    </row>
+    <row r="23" spans="1:15" ht="16.5" customHeight="1">
       <c r="A23" s="20">
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>289</v>
@@ -17933,18 +18226,19 @@
         <v>39</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="16.5" customHeight="1">
+        <v>420</v>
+      </c>
+      <c r="O23" s="26"/>
+    </row>
+    <row r="24" spans="1:15" ht="16.5" customHeight="1">
       <c r="A24" s="20">
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>300</v>
@@ -17972,18 +18266,19 @@
         <v>291</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="16.5" customHeight="1">
+        <v>423</v>
+      </c>
+      <c r="O24" s="26"/>
+    </row>
+    <row r="25" spans="1:15" ht="16.5" customHeight="1">
       <c r="A25" s="20">
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C25" s="43" t="s">
         <v>289</v>
@@ -18005,22 +18300,25 @@
       </c>
       <c r="I25" s="26">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1088</v>
+        <v>1144</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="16.5" customHeight="1">
+        <v>1080</v>
+      </c>
+      <c r="O25" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.5" customHeight="1">
       <c r="A26" s="20">
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>23</v>
@@ -18046,18 +18344,19 @@
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="16.5" customHeight="1">
+        <v>426</v>
+      </c>
+      <c r="O26" s="26"/>
+    </row>
+    <row r="27" spans="1:15" ht="16.5" customHeight="1">
       <c r="A27" s="20">
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>18</v>
@@ -18083,13 +18382,14 @@
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="16.5" customHeight="1">
+        <v>429</v>
+      </c>
+      <c r="O27" s="26"/>
+    </row>
+    <row r="28" spans="1:15" ht="16.5" customHeight="1">
       <c r="A28" s="20">
         <v>9</v>
       </c>
@@ -18119,21 +18419,22 @@
         <v>5</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K28" s="21" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="16.5" customHeight="1">
+        <v>431</v>
+      </c>
+      <c r="O28" s="26"/>
+    </row>
+    <row r="29" spans="1:15" ht="16.5" customHeight="1">
       <c r="A29" s="20">
         <v>10</v>
       </c>
       <c r="B29" s="85" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>261</v>
@@ -18159,13 +18460,14 @@
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1">
+        <v>406</v>
+      </c>
+      <c r="O29" s="26"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1">
       <c r="A30" s="20"/>
       <c r="B30" s="21"/>
       <c r="C30" s="20"/>
@@ -18181,71 +18483,86 @@
       <c r="H30" s="26"/>
       <c r="I30" s="26">
         <f>ROUND(SUM(I20:I29),0)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1">
+    <row r="31" spans="1:15" ht="15" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="31" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1105</v>
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="112" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>1134</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A20:N29">
+  <conditionalFormatting sqref="A20:O29">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>$E20=0</formula>
     </cfRule>
@@ -18257,7 +18574,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -18270,24 +18587,25 @@
     <col min="10" max="11" width="11" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="16.5" customHeight="1">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.5" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
@@ -18298,7 +18616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1">
+    <row r="6" spans="1:15" ht="15" customHeight="1">
       <c r="A6" s="20">
         <f>MAX(20,MROUND(시작중량_설정!$E$8*0.4,2.5))</f>
         <v>25</v>
@@ -18310,7 +18628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1">
+    <row r="7" spans="1:15" ht="15" customHeight="1">
       <c r="A7" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$8*0.6,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$8*0.4,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$8*0.6,2.5)))</f>
         <v>37.5</v>
@@ -18322,7 +18640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1">
+    <row r="8" spans="1:15" ht="15" customHeight="1">
       <c r="A8" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$8*0.75,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$8*0.6,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$8*0.75,2.5)))</f>
         <v>47.5</v>
@@ -18334,7 +18652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1">
+    <row r="9" spans="1:15" ht="15" customHeight="1">
       <c r="A9" s="20">
         <f>IF(MAX(20,MROUND(시작중량_설정!$E$8*0.9,2.5))&lt;=MAX(20,MROUND(시작중량_설정!$E$8*0.75,2.5)),"생략",MAX(20,MROUND(시작중량_설정!$E$8*0.9,2.5)))</f>
         <v>57.5</v>
@@ -18346,7 +18664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1">
+    <row r="10" spans="1:15" ht="15" customHeight="1">
       <c r="A10" s="37">
         <f>시작중량_설정!$E$8</f>
         <v>62.5</v>
@@ -18358,17 +18676,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1">
+    <row r="11" spans="1:15" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1">
+    <row r="13" spans="1:15" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16.5" customHeight="1">
+    <row r="14" spans="1:15" ht="16.5" customHeight="1">
       <c r="A14" s="34" t="s">
         <v>3</v>
       </c>
@@ -18411,13 +18729,16 @@
       <c r="N14" s="35" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="O14" s="35" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1">
       <c r="A15" s="40">
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C15" s="40" t="s">
         <v>272</v>
@@ -18439,25 +18760,26 @@
         <v>240</v>
       </c>
       <c r="I15" s="38">
-        <f t="shared" ref="I15:I22" si="0">IF(E15=0,0,ROUND(E15*(G15+H15)/60,1))</f>
+        <f t="shared" ref="I15:I22" si="0">IF(E15=0,0,ROUND((E15*(G15+H15)+O15)/60,1))</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L15" s="39" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="16.5" customHeight="1">
+        <v>446</v>
+      </c>
+      <c r="O15" s="38"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1">
       <c r="A16" s="40">
         <v>2</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C16" s="40" t="s">
         <v>272</v>
@@ -18483,24 +18805,25 @@
         <v>7.2</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L16" s="39" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="16.5" customHeight="1">
+        <v>446</v>
+      </c>
+      <c r="O16" s="38"/>
+    </row>
+    <row r="17" spans="1:15" ht="16.5" customHeight="1">
       <c r="A17" s="20">
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D17" s="26">
         <v>25</v>
@@ -18522,24 +18845,25 @@
         <v>13</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="16.5" customHeight="1">
+        <v>451</v>
+      </c>
+      <c r="O17" s="26"/>
+    </row>
+    <row r="18" spans="1:15" ht="16.5" customHeight="1">
       <c r="A18" s="20">
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D18" s="20">
         <v>35</v>
@@ -18561,24 +18885,25 @@
         <v>9.5</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="16.5" customHeight="1">
+        <v>454</v>
+      </c>
+      <c r="O18" s="26"/>
+    </row>
+    <row r="19" spans="1:15" ht="16.5" customHeight="1">
       <c r="A19" s="20">
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D19" s="26">
         <v>15</v>
@@ -18601,90 +18926,94 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="16.5" customHeight="1">
+        <v>457</v>
+      </c>
+      <c r="O19" s="26"/>
+    </row>
+    <row r="20" spans="1:15" ht="16.5" customHeight="1">
       <c r="A20" s="20">
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>461</v>
+        <v>1123</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>317</v>
+        <v>1125</v>
       </c>
       <c r="D20" s="26">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="E20" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>305</v>
+        <v>1126</v>
       </c>
       <c r="G20" s="26">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H20" s="26">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I20" s="26">
         <f t="shared" si="0"/>
-        <v>10.7</v>
-      </c>
-      <c r="J20" s="21"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>322</v>
+      </c>
       <c r="K20" s="21" t="s">
-        <v>462</v>
+        <v>1147</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="16.5" customHeight="1">
+        <v>1128</v>
+      </c>
+      <c r="O20" s="26"/>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1">
       <c r="A21" s="20">
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>322</v>
+        <v>1124</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>317</v>
+        <v>1125</v>
       </c>
       <c r="D21" s="26">
-        <f>D3_하체A!D16</f>
+        <v>42</v>
+      </c>
+      <c r="E21" s="20">
+        <v>4</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G21" s="26">
+        <v>40</v>
+      </c>
+      <c r="H21" s="26">
         <v>120</v>
-      </c>
-      <c r="E21" s="20">
-        <v>3</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="26">
-        <v>45</v>
-      </c>
-      <c r="H21" s="26">
-        <v>150</v>
       </c>
       <c r="I21" s="26">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>323</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>464</v>
+        <v>1146</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="16.5" customHeight="1">
+        <v>1129</v>
+      </c>
+      <c r="O21" s="26">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.5" customHeight="1">
       <c r="A22" s="20">
         <v>8</v>
       </c>
@@ -18715,13 +19044,14 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="16.5" customHeight="1">
+        <v>460</v>
+      </c>
+      <c r="O22" s="26"/>
+    </row>
+    <row r="23" spans="1:15" ht="16.5" customHeight="1">
       <c r="D23" s="3" t="s">
         <v>63</v>
       </c>
@@ -18731,16 +19061,30 @@
       </c>
       <c r="I23">
         <f>ROUND(SUM(I15:I22),0)</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15" customHeight="1">
+      <c r="A24" s="112" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>1134</v>
+      </c>
+    </row>
     <row r="33" spans="2:2">
       <c r="B33" s="83"/>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A15:N22">
+  <conditionalFormatting sqref="A15:O22">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$E15=0</formula>
     </cfRule>

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{518ACB2F-0356-4DC5-93E2-AE6AB317B5F0}"/>
+  <xr:revisionPtr revIDLastSave="569" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6628712A-9782-40EA-8F3D-F8BBE07F82EC}"/>
   <bookViews>
     <workbookView xWindow="6360" yWindow="2400" windowWidth="29040" windowHeight="18480" tabRatio="883" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="1158">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -1052,9 +1052,6 @@
     <t>햄스트링</t>
   </si>
   <si>
-    <t>무릎 굴곡. 8일차 RDL(고관절 신전)과 기능이 다르다 — 둘 다 필요</t>
-  </si>
-  <si>
     <t>라잉 레그 컬 · 시티드 레그 컬 (시티드가 늘어난 구간을 더 씀) / 노르딕 햄 컬</t>
   </si>
   <si>
@@ -1095,9 +1092,6 @@
   </si>
   <si>
     <t>머신 레터럴 레이즈</t>
-  </si>
-  <si>
-    <t>궤도가 고정돼 반동이 안 들어간다. 중간 구간을 끝까지 쓴다. 어깨가 으쓱 따라 올라가면 승모가 대신 일하는 것 — 무게를 내린다.</t>
   </si>
   <si>
     <t>덤벨 레터럴 (머신 없을 때 — 몸 옆이 아니라 살짝 앞) / 케이블 레터럴 양팔 크로스</t>
@@ -3422,10 +3416,6 @@
   </si>
   <si>
     <t>원암 덤벨 로우 (벤치 지지) / 원암 머신 로우 (해머 스트랭스 한 팔씩) / 시티드 케이블 로우 5세트로 합치기</t>
-  </si>
-  <si>
-    <t>2번 시티드 케이블 로우와 같은 스테이션 — 3번 원암 로우 뒤에 바를 다시 걸고 무게만 내려 이어서 한다 (자리 이동 없음). 팔꿈치 각도를 세트 내내 고정하고 견갑골만 뒤로 — 가동범위 2~3cm, 모은 자리에서 1초 정지. 상체를 뒤로 눕히면 하부 승모 각도가 되고, 팔을 당기면 광배로 넘어간다. 케이블이라 수축 지점에서도 장력이 유지되고 핀 단위 미세 증량이 된다 (플레이트 로드 머신은 이 무게대에서 계단이 너무 큼).</t>
-    <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
     <t>· 시티드 케이블 로우 5 → 양팔 3 + 원암 2 (사용자 요청). 3번 원암 케이블 로우를 새로 두고 스캡 슈러그부터 번호가 하나씩 밀렸다. 광배 직접 세트는 5 그대로 · 30세트 · 약 72분.</t>
@@ -3582,24 +3572,48 @@
     <t>· 레그 프레스 ↔ 레그 익스텐션 자리 바꿈 — 복합을 먼저, 고립을 마지막에. 익스텐션 마지막 세트에 드롭 2단, +75초 (사용자 요청). 드롭으로 대퇴를 다 쓴 뒤 프레스를 하면 프레스 3세트가 죽어서 순서를 바꿨다. 다음 하체는 3일차, 5일 뒤라 회복이 겹치지 않는다.</t>
   </si>
   <si>
-    <t>· 고립·케이블 9곳의 마지막 세트에만 드롭 2단 — 1일차 원암 랫풀다운, 2일차 레터럴·리버스 펙덱·푸쉬다운, 4일차 펙덱, 6일차 원암 로우·프리쳐 컬, 7일차 디클라인 케이블 플라이, 8일차 레그 익스텐션. 메인 4종, 척추 부하 종목, 복합 프레스·로우, 기술 종목(오버헤드 슈러그·프론 Y·업라이트 로우)에는 붙이지 않는다.</t>
-  </si>
-  <si>
-    <t>· 세트 수·예산(244)은 그대로다. 드롭은 같은 세트의 연장이지 새 세트가 아니다. 시간만 O열 '드롭(초)'로 얹혀 세션이 +1~3분. 증량 판정은 드롭이 없는 앞 세트로만 한다.</t>
-  </si>
-  <si>
-    <t>· 3·9일차는 드롭 0 — 스쿼트가 있는 날과 36세트로 이미 꽉 찬 날이다. 이두는 프리쳐 컬 한 곳(9일차 인클라인 컬은 이틀 뒤 친업), 머신 숄더 프레스는 제외(전면 삼각근은 프레스 4종으로 충분).</t>
-  </si>
-  <si>
-    <t>측면·후면 삼각근 + 승모 하부 + 흉근(인클라인 스미스 · 펙덱) + 이두 · 전완 + 종아리. 약 71분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B. [2026-09-05] 이너·아우터 타이·리스트 컬은 9일차로, 디클라인 플라이는 7일차로, 시티드 카프는 6일차로 갔고, 9일차의 리버스 리스트 컬·리버스컬과 6일차 스탠딩 카프·오버헤드 슈러그가 왔다. 펙덱 마지막 세트 드롭 +1분 — 약 72분 (2026-09-07).</t>
+    <t>오버헤드 프레싱 · 흉근 상부 · 어깨 측면/후면. 벤치(2일차)와 5일 간격이라 무게가 온전히 나온다. [2026-09-05] 4일차 디클라인 케이블 플라이 3세트가 왔다 — 흉근 9세트(헤머 · 인클라인 머신 · 디클라인). 6일차 중량 크런치 3세트도 마지막에 왔다 — 약 72분. 디클라인 플라이 마지막 세트 드롭 +1분 — 약 73분 (2026-09-07).</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다. [2026-09-05] 스탠딩 카프는 4일차로, 중량 크런치는 7일차로 갔고 9일차 케이블 힙 외전이 왔다. 약 72분. 오버헤드 슈러그는 4일차로 가고 4일차 시티드 카프 2세트가 왔다 — 약 71분. 원암 로우·프리쳐 컬 마지막 세트 드롭 +3분 — 약 75분 (2026-09-07).</t>
+    <t>무릎 굴곡. 8일차 RDL(고관절 신전)과 기능이 다르다 — 둘 다 필요 [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 지친 햄스트링은 수축 위치에서 쥐가 잘 나니 위에서 멈추지 말고 바로 내린다. 다음 햄스트링은 8일차, 5일 뒤. 세트 수 그대로, 증량 판정은 앞 세트로만. +75초는 O열]</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>오버헤드 프레싱 · 흉근 상부 · 어깨 측면/후면. 벤치(2일차)와 5일 간격이라 무게가 온전히 나온다. [2026-09-05] 4일차 디클라인 케이블 플라이 3세트가 왔다 — 흉근 9세트(헤머 · 인클라인 머신 · 디클라인). 6일차 중량 크런치 3세트도 마지막에 왔다 — 약 72분. 디클라인 플라이 마지막 세트 드롭 +1분 — 약 73분 (2026-09-07).</t>
+    <t>· 레그 컬 마지막 세트에 드롭 2단, +75초 (사용자 요청). 핀 스택 단관절이고 그날 햄스트링 마지막 종목이다. 다음 햄스트링은 8일차 RDL, 5일 뒤. 3일차 뒤는 4일차 고립·5일차 휴식이라 회복이 겹치지 않는다. 지친 햄스트링은 수축 위치에서 쥐가 나기 쉬우니 드롭 반복은 위에서 멈추지 않는다.</t>
+  </si>
+  <si>
+    <t>궤도가 고정돼 반동이 안 들어간다. 중간 구간을 끝까지 쓴다. 어깨가 으쓱 따라 올라가면 승모가 대신 일하는 것 — 무게를 내린다. [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 측면 두 번째 드롭 자리(2일차 레터럴과 이틀 간격, 사용자 선택). 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 머신 레터럴 레이즈 마지막 세트에도 드롭 2단, +60초 (사용자 선택, 2026-09-07 추가). 측면 두 번째 자리 — 2일차 레터럴과 이틀 간격이지만 측면은 회복이 빠르다. 4일차 드롭은 둘, 약 73분.</t>
+  </si>
+  <si>
+    <t>측면·후면 삼각근 + 승모 하부 + 흉근(인클라인 스미스 · 펙덱) + 이두 · 전완 + 종아리. 약 71분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B. [2026-09-05] 이너·아우터 타이·리스트 컬은 9일차로, 디클라인 플라이는 7일차로, 시티드 카프는 6일차로 갔고, 9일차의 리버스 리스트 컬·리버스컬과 6일차 스탠딩 카프·오버헤드 슈러그가 왔다. 펙덱·머신 레터럴 마지막 세트 드롭 +2분 — 약 73분 (2026-09-07).</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 시티드 케이블 로우와 같은 스테이션 — 3번 원암 로우 뒤에 바를 다시 걸고 무게만 내려 이어서 한다 (자리 이동 없음). 팔꿈치 각도를 세트 내내 고정하고 견갑골만 뒤로 — 가동범위 2~3cm, 모은 자리에서 1초 정지. 상체를 뒤로 눕히면 하부 승모 각도가 되고, 팔을 당기면 광배로 넘어간다. 케이블이라 수축 지점에서도 장력이 유지되고 핀 단위 미세 증량이 된다 (플레이트 로드 머신은 이 무게대에서 계단이 너무 큼). [2026-09-07 마지막 세트 드롭 2단 — 실패 뒤 쉬지 않고 핀 20~30% 내려 두 번. 지치면 팔로 당겨 로우가 되는데 그래도 등 상부라 손해가 작다. 세트 수 그대로, 증량 판정은 앞 세트로만. +60초는 O열]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 스캡 슈러그 마지막 세트에도 드롭 2단, +60초 (사용자 요청, 2026-09-07 추가). 핀 스택 단관절이고 그날 승모 중부 마지막 종목이다. 지치면 팔로 당겨 로우가 되는데 그래도 등 상부라 손해가 작다. 6일차 드롭은 셋, 약 76분.</t>
+  </si>
+  <si>
+    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다. [2026-09-05] 스탠딩 카프는 4일차로, 중량 크런치는 7일차로 갔고 9일차 케이블 힙 외전이 왔다. 약 72분. 오버헤드 슈러그는 4일차로 가고 4일차 시티드 카프 2세트가 왔다 — 약 71분. 원암 로우·프리쳐 컬·스캡 슈러그 마지막 세트 드롭 +4분 — 약 76분 (2026-09-07).</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 고립·케이블 12곳의 마지막 세트에만 드롭 2단 — 1일차 원암 랫풀다운, 2일차 레터럴·리버스 펙덱·푸쉬다운, 3일차 레그 컬, 4일차 머신 레터럴·펙덱, 6일차 원암 로우·스캡 슈러그·프리쳐 컬, 7일차 디클라인 케이블 플라이, 8일차 레그 익스텐션. 메인 4종, 척추 부하 종목, 복합 프레스·로우, 기술 종목(오버헤드 슈러그·프론 Y·업라이트 로우)에는 붙이지 않는다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 세트 수·예산(244)은 그대로다. 드롭은 같은 세트의 연장이지 새 세트가 아니다. 시간만 O열 '드롭(초)'로 얹혀 세션이 +1~4분. 증량 판정은 드롭이 없는 앞 세트로만 한다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 9일차는 드롭 0 — 36세트로 이미 꽉 찬 날이다. 측면은 2일차 레터럴에 더해 4일차 머신 레터럴에도 붙였다(사용자 선택, 둘 다 +60초). 이두는 프리쳐 컬 한 곳(9일차 인클라인 컬은 이틀 뒤 친업), 머신 숄더 프레스는 제외(전면 삼각근은 프레스 4종으로 충분), 시티드 카프·트랩바 슈러그·흉근 상부(케이블 플라이 교체 필요)는 보류.</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
@@ -5295,7 +5309,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
@@ -5352,7 +5366,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -5516,7 +5530,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>300</v>
@@ -5542,7 +5556,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>307</v>
@@ -5632,7 +5646,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="81" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>45</v>
@@ -5658,10 +5672,10 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O13" s="26"/>
     </row>
@@ -5670,13 +5684,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="81" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>335</v>
-      </c>
       <c r="D14" s="20" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E14" s="20">
         <v>5</v>
@@ -5696,13 +5710,13 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O14" s="26"/>
     </row>
@@ -5711,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>60</v>
@@ -5737,13 +5751,13 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="N15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O15" s="26"/>
     </row>
@@ -5894,22 +5908,22 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="31" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -5939,12 +5953,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="115" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="114"/>
@@ -5956,7 +5970,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$80,"?")</f>
@@ -5965,7 +5979,7 @@
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="113" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B4" s="114"/>
       <c r="C4" s="114"/>
@@ -5977,33 +5991,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
+        <v>463</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>465</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="D6" s="44" t="s">
         <v>466</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="E6" s="44" t="s">
         <v>467</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="F6" s="44" t="s">
         <v>468</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="G6" s="44" t="s">
         <v>469</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="H6" s="44" t="s">
         <v>470</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>471</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B7" s="45" t="s">
         <v>237</v>
@@ -6023,15 +6037,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B8" s="45" t="s">
         <v>243</v>
@@ -6051,18 +6065,18 @@
         <v>0.4</v>
       </c>
       <c r="G8" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="H8" s="50" t="s">
         <v>474</v>
-      </c>
-      <c r="H8" s="50" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C9" s="45" t="s">
         <v>44</v>
@@ -6079,18 +6093,18 @@
         <v>1</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C10" s="45" t="s">
         <v>44</v>
@@ -6107,15 +6121,15 @@
         <v>0.99</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>288</v>
@@ -6135,15 +6149,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B12" s="45" t="s">
         <v>295</v>
@@ -6163,18 +6177,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C13" s="45" t="s">
         <v>39</v>
@@ -6191,18 +6205,18 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C14" s="45" t="s">
         <v>39</v>
@@ -6219,15 +6233,15 @@
         <v>1.5</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B15" s="45" t="s">
         <v>299</v>
@@ -6247,15 +6261,15 @@
         <v>1.5</v>
       </c>
       <c r="G15" s="49" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B16" s="45" t="s">
         <v>43</v>
@@ -6275,18 +6289,18 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C17" s="45" t="s">
         <v>45</v>
@@ -6303,18 +6317,18 @@
         <v>1.32</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>45</v>
@@ -6331,15 +6345,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B19" s="45" t="s">
         <v>288</v>
@@ -6359,15 +6373,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>299</v>
@@ -6387,18 +6401,18 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C21" s="45" t="s">
         <v>27</v>
@@ -6415,18 +6429,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C22" s="45" t="s">
         <v>18</v>
@@ -6443,15 +6457,15 @@
         <v>0.99</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B23" s="45" t="s">
         <v>26</v>
@@ -6471,15 +6485,15 @@
         <v>0.99</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B24" s="45" t="s">
         <v>26</v>
@@ -6499,15 +6513,15 @@
         <v>0.99</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B25" s="45" t="s">
         <v>252</v>
@@ -6527,15 +6541,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B26" s="45" t="s">
         <v>33</v>
@@ -6555,15 +6569,15 @@
         <v>1.5</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B27" s="45" t="s">
         <v>33</v>
@@ -6583,18 +6597,18 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C28" s="45" t="s">
         <v>238</v>
@@ -6611,18 +6625,18 @@
         <v>2.5</v>
       </c>
       <c r="G28" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C29" s="45" t="s">
         <v>246</v>
@@ -6639,18 +6653,18 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C30" s="45" t="s">
         <v>246</v>
@@ -6667,18 +6681,18 @@
         <v>0</v>
       </c>
       <c r="G30" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C31" s="45" t="s">
         <v>331</v>
@@ -6695,18 +6709,18 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C32" s="45" t="s">
         <v>331</v>
@@ -6723,15 +6737,15 @@
         <v>0.33</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>271</v>
@@ -6751,15 +6765,15 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B34" s="45" t="s">
         <v>315</v>
@@ -6779,15 +6793,15 @@
         <v>2.5</v>
       </c>
       <c r="G34" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B35" s="45" t="s">
         <v>321</v>
@@ -6807,18 +6821,18 @@
         <v>0.99</v>
       </c>
       <c r="G35" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C36" s="45" t="s">
         <v>322</v>
@@ -6835,18 +6849,18 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C37" s="45" t="s">
         <v>322</v>
@@ -6863,15 +6877,15 @@
         <v>1.5</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>271</v>
@@ -6891,15 +6905,15 @@
         <v>1.5</v>
       </c>
       <c r="G38" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B39" s="45" t="s">
         <v>315</v>
@@ -6919,18 +6933,18 @@
         <v>0</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C40" s="45" t="s">
         <v>272</v>
@@ -6947,18 +6961,18 @@
         <v>0</v>
       </c>
       <c r="G40" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C41" s="45" t="s">
         <v>272</v>
@@ -6975,15 +6989,15 @@
         <v>1.5</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B42" s="45" t="s">
         <v>325</v>
@@ -7003,15 +7017,15 @@
         <v>1.5</v>
       </c>
       <c r="G42" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B43" s="45" t="s">
         <v>325</v>
@@ -7031,18 +7045,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C44" s="45" t="s">
         <v>238</v>
@@ -7059,21 +7073,21 @@
         <v>0</v>
       </c>
       <c r="G44" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B45" s="45" t="s">
         <v>315</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D45" s="46">
         <v>0.33</v>
@@ -7087,21 +7101,21 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G45" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B46" s="45" t="s">
         <v>321</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D46" s="46">
         <v>0.33</v>
@@ -7115,21 +7129,21 @@
         <v>0.99</v>
       </c>
       <c r="G46" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B47" s="45" t="s">
         <v>325</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D47" s="46">
         <v>0.33</v>
@@ -7143,15 +7157,15 @@
         <v>0.99</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B48" s="45" t="s">
         <v>288</v>
@@ -7171,18 +7185,18 @@
         <v>0</v>
       </c>
       <c r="G48" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C49" s="45" t="s">
         <v>289</v>
@@ -7199,21 +7213,21 @@
         <v>0</v>
       </c>
       <c r="G49" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C50" s="45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D50" s="46">
         <v>0</v>
@@ -7227,21 +7241,21 @@
         <v>0</v>
       </c>
       <c r="G50" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C51" s="45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D51" s="46">
         <v>0.2</v>
@@ -7255,21 +7269,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C52" s="45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D52" s="46">
         <v>0</v>
@@ -7283,15 +7297,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H52" s="50" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B53" s="45" t="s">
         <v>237</v>
@@ -7311,18 +7325,18 @@
         <v>0.8</v>
       </c>
       <c r="G53" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C54" s="45" t="s">
         <v>34</v>
@@ -7339,15 +7353,15 @@
         <v>1</v>
       </c>
       <c r="G54" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B55" s="45" t="s">
         <v>310</v>
@@ -7367,15 +7381,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G55" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B56" s="45" t="s">
         <v>321</v>
@@ -7395,21 +7409,21 @@
         <v>0.99</v>
       </c>
       <c r="G56" s="52" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B57" s="45" t="s">
         <v>321</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D57" s="46">
         <v>0.33</v>
@@ -7423,15 +7437,15 @@
         <v>0.99</v>
       </c>
       <c r="G57" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B58" s="45" t="s">
         <v>26</v>
@@ -7451,15 +7465,15 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H58" s="50" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B59" s="45" t="s">
         <v>26</v>
@@ -7479,18 +7493,18 @@
         <v>1.5</v>
       </c>
       <c r="G59" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C60" s="45" t="s">
         <v>39</v>
@@ -7507,15 +7521,15 @@
         <v>1.5</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B61" s="45" t="s">
         <v>295</v>
@@ -7535,18 +7549,18 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C62" s="45" t="s">
         <v>27</v>
@@ -7563,15 +7577,15 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H62" s="50" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="45" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B63" s="45" t="s">
         <v>51</v>
@@ -7591,18 +7605,18 @@
         <v>0.8</v>
       </c>
       <c r="G63" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>246</v>
@@ -7619,21 +7633,21 @@
         <v>0.99</v>
       </c>
       <c r="G64" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B65" s="45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D65" s="46">
         <v>0.33</v>
@@ -7647,18 +7661,18 @@
         <v>0.99</v>
       </c>
       <c r="G65" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B66" s="45" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>246</v>
@@ -7675,15 +7689,15 @@
         <v>0.99</v>
       </c>
       <c r="G66" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" s="45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B67" s="45" t="s">
         <v>256</v>
@@ -7703,18 +7717,18 @@
         <v>0.99</v>
       </c>
       <c r="G67" s="52" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15" customHeight="1">
       <c r="A68" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B68" s="45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C68" s="45" t="s">
         <v>331</v>
@@ -7731,18 +7745,18 @@
         <v>0.66</v>
       </c>
       <c r="G68" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C69" s="45" t="s">
         <v>322</v>
@@ -7759,21 +7773,21 @@
         <v>1</v>
       </c>
       <c r="G69" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C70" s="45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D70" s="46">
         <v>0</v>
@@ -7787,15 +7801,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="49" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s">
         <v>245</v>
@@ -7815,15 +7829,15 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H71" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s">
         <v>245</v>
@@ -7843,18 +7857,18 @@
         <v>0.8</v>
       </c>
       <c r="G72" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H72" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C73" t="s">
         <v>44</v>
@@ -7871,18 +7885,18 @@
         <v>0.66</v>
       </c>
       <c r="G73" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H73" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B74" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C74" t="s">
         <v>44</v>
@@ -7899,18 +7913,18 @@
         <v>0.66</v>
       </c>
       <c r="G74" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H74" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C75" t="s">
         <v>246</v>
@@ -7927,10 +7941,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H75" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -7959,30 +7973,30 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G2" s="94" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H2" s="95">
         <v>10</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J2" s="95">
         <v>244</v>
       </c>
       <c r="K2" s="94" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="L2" s="96">
         <f>B25</f>
@@ -7995,21 +8009,21 @@
         <v/>
       </c>
       <c r="G3" s="94" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H3" s="98">
         <f>$J$2-$L$2</f>
         <v>3</v>
       </c>
       <c r="I3" s="94" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J3" s="98">
         <f>ROUND($L$2*7/$H$2,1)</f>
         <v>168.7</v>
       </c>
       <c r="K3" s="94" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L3" s="98" t="str">
         <f>IF($H$3&lt;0,"INVALID","VALID")</f>
@@ -8021,19 +8035,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>561</v>
       </c>
       <c r="J4" s="99" t="str">
         <f>"주당 환산 (×7/"&amp;$H$2&amp;")"</f>
@@ -8061,10 +8075,10 @@
         <v>유지</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G5" s="116" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H5" s="56">
         <f ca="1">SUM(D5:D6)</f>
@@ -8104,7 +8118,7 @@
         <v>성장</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G6" s="117"/>
       <c r="J6" s="55">
@@ -8137,10 +8151,10 @@
         <v>성장</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G7" s="116" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H7" s="56">
         <f ca="1">SUM(D7:D10)</f>
@@ -8157,7 +8171,7 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
       <c r="A8" s="53" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B8" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A8)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A8)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A8)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A8)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A8)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A8)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A8)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A8)</f>
@@ -8176,7 +8190,7 @@
         <v>유지 미만</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G8" s="117"/>
       <c r="J8" s="55">
@@ -8209,7 +8223,7 @@
         <v>유지</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G9" s="117"/>
       <c r="J9" s="55">
@@ -8242,7 +8256,7 @@
         <v>성장</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G10" s="117"/>
       <c r="J10" s="55">
@@ -8275,7 +8289,7 @@
         <v>유지</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G11" s="57"/>
       <c r="J11" s="55">
@@ -8308,7 +8322,7 @@
         <v>성장</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G12" s="57"/>
       <c r="J12" s="55">
@@ -8341,7 +8355,7 @@
         <v>성장</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G13" s="57"/>
       <c r="J13" s="55">
@@ -8374,7 +8388,7 @@
         <v>성장</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="56"/>
@@ -8411,7 +8425,7 @@
         <v>325</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H15" s="56">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -8447,7 +8461,7 @@
         <v>유지</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G16" s="57"/>
       <c r="J16" s="55">
@@ -8480,7 +8494,7 @@
         <v>성장</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G17" s="116" t="s">
         <v>322</v>
@@ -8519,7 +8533,7 @@
         <v>유지</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G18" s="117"/>
       <c r="J18" s="55">
@@ -8552,7 +8566,7 @@
         <v>유지</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G19" s="57"/>
       <c r="J19" s="55">
@@ -8585,7 +8599,7 @@
         <v>성장</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="G20" s="57"/>
       <c r="J20" s="55">
@@ -8618,7 +8632,7 @@
         <v>성장</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G21" s="57"/>
       <c r="J21" s="55">
@@ -8651,7 +8665,7 @@
         <v>성장</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G22" s="57"/>
       <c r="J22" s="55">
@@ -8684,7 +8698,7 @@
         <v>유지</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G23" s="57"/>
       <c r="J23" s="55">
@@ -8698,7 +8712,7 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="A24" s="53" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B24" s="59">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A24)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A24)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A24)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A24)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A24)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A24)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A24)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A24)</f>
@@ -8717,7 +8731,7 @@
         <v>유지</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G24" s="57"/>
       <c r="J24" s="55">
@@ -8731,7 +8745,7 @@
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
@@ -8755,22 +8769,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="48" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="48" customHeight="1">
@@ -8778,22 +8792,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
@@ -8801,124 +8815,124 @@
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="77.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="39" customHeight="1">
       <c r="A39" s="63" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="48" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48" customHeight="1">
       <c r="A44" s="90" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51.75" customHeight="1">
       <c r="A45" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="90" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="48" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="93" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="100" t="s">
+        <v>611</v>
+      </c>
+      <c r="B58" s="100" t="s">
+        <v>612</v>
+      </c>
+      <c r="C58" s="100" t="s">
         <v>613</v>
       </c>
-      <c r="B58" s="100" t="s">
+      <c r="D58" s="100" t="s">
         <v>614</v>
       </c>
-      <c r="C58" s="100" t="s">
+      <c r="E58" s="100" t="s">
         <v>615</v>
-      </c>
-      <c r="D58" s="100" t="s">
-        <v>616</v>
-      </c>
-      <c r="E58" s="100" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -8932,7 +8946,7 @@
         <v>239</v>
       </c>
       <c r="D59" s="102" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E59" s="102" t="s">
         <v>150</v>
@@ -8949,10 +8963,10 @@
         <v>239</v>
       </c>
       <c r="D60" s="107" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E60" s="107" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -8966,45 +8980,45 @@
         <v>244</v>
       </c>
       <c r="D61" s="111" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E61" s="111" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="104" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -9054,50 +9068,50 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="64" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="64" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="64" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -9106,13 +9120,13 @@
     </row>
     <row r="8" spans="1:13" ht="84" customHeight="1">
       <c r="A8" s="64" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9120,40 +9134,40 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F9" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>646</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L9" s="100" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M9" s="100" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9302,7 +9316,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="65" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="L14" s="103"/>
       <c r="M14" s="103"/>
@@ -9512,17 +9526,17 @@
     </row>
     <row r="23" spans="1:13" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="120" customHeight="1">
@@ -9530,52 +9544,52 @@
     </row>
     <row r="27" spans="1:13" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -9596,45 +9610,45 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>664</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -9642,80 +9656,80 @@
         <v>272</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="67" t="s">
+        <v>671</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>672</v>
+      </c>
+      <c r="C8" s="68" t="s">
         <v>673</v>
-      </c>
-      <c r="B8" s="67" t="s">
-        <v>674</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="67" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>678</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="C11" s="53" t="s">
         <v>681</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C12" s="53" t="s">
         <v>684</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -9723,47 +9737,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -9789,31 +9803,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="70" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>703</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>705</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>7</v>
@@ -9822,111 +9836,111 @@
         <v>148</v>
       </c>
       <c r="G5" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="71" t="s">
+        <v>705</v>
+      </c>
+      <c r="B6" s="72" t="s">
+        <v>706</v>
+      </c>
+      <c r="C6" s="72" t="s">
         <v>707</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="D6" s="71" t="s">
         <v>708</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>709</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>710</v>
       </c>
       <c r="E6" s="71">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G7" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
+        <v>715</v>
+      </c>
+      <c r="B8" s="72" t="s">
+        <v>716</v>
+      </c>
+      <c r="C8" s="72" t="s">
+        <v>702</v>
+      </c>
+      <c r="D8" s="71" t="s">
         <v>717</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>718</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>704</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>719</v>
       </c>
       <c r="E8" s="71">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="73" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G8" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
+        <v>720</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>721</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>702</v>
+      </c>
+      <c r="D9" s="71" t="s">
         <v>722</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>723</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>704</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>724</v>
       </c>
       <c r="E9" s="71">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="73" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G9" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="71" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C10" s="72" t="s">
         <v>150</v>
@@ -9941,7 +9955,7 @@
         <v>150</v>
       </c>
       <c r="G10" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -9956,7 +9970,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -9977,32 +9991,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -10010,22 +10024,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -10033,32 +10047,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -10066,47 +10080,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="74" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -10116,27 +10130,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>
@@ -10167,12 +10181,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10247,10 +10261,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="K5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>294</v>
@@ -10261,7 +10275,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C6" s="67" t="s">
         <v>27</v>
@@ -10287,13 +10301,13 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="K6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="L6" s="68" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10326,10 +10340,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="K7" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10337,7 +10351,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>316</v>
@@ -10362,10 +10376,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K8" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10373,7 +10387,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>331</v>
@@ -10398,10 +10412,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="K9" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10409,13 +10423,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
+        <v>333</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>335</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -10434,10 +10448,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="K10" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10470,10 +10484,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="K11" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10481,13 +10495,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="87" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="76" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -10506,10 +10520,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="K12" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -10542,10 +10556,10 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="K13" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
@@ -10568,72 +10582,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
   </sheetData>
@@ -10664,12 +10678,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10744,10 +10758,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="K5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -10755,13 +10769,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>246</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -10780,13 +10794,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
+        <v>802</v>
+      </c>
+      <c r="K6" t="s">
+        <v>803</v>
+      </c>
+      <c r="L6" s="53" t="s">
         <v>804</v>
-      </c>
-      <c r="K6" t="s">
-        <v>805</v>
-      </c>
-      <c r="L6" s="53" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10794,7 +10808,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>238</v>
@@ -10819,10 +10833,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K7" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10855,13 +10869,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
+        <v>808</v>
+      </c>
+      <c r="K8" t="s">
+        <v>809</v>
+      </c>
+      <c r="L8" s="53" t="s">
         <v>810</v>
-      </c>
-      <c r="K8" t="s">
-        <v>811</v>
-      </c>
-      <c r="L8" s="53" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -10869,13 +10883,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>246</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -10894,10 +10908,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="K9" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10905,13 +10919,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -10930,10 +10944,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="K10" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10966,13 +10980,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
+        <v>816</v>
+      </c>
+      <c r="K11" t="s">
+        <v>817</v>
+      </c>
+      <c r="L11" s="53" t="s">
         <v>818</v>
-      </c>
-      <c r="K11" t="s">
-        <v>819</v>
-      </c>
-      <c r="L11" s="53" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10980,7 +10994,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>289</v>
@@ -11005,10 +11019,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="K12" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -11016,13 +11030,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="76" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E13" s="28">
         <v>3</v>
@@ -11041,10 +11055,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="K13" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -11052,7 +11066,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -11077,10 +11091,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K14" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -11088,7 +11102,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -11113,10 +11127,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="K15" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
@@ -11139,112 +11153,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="63" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -11275,12 +11289,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -11335,7 +11349,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E5" s="67">
         <v>4</v>
@@ -11354,7 +11368,7 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="K5" t="s">
         <v>32</v>
@@ -11390,10 +11404,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="K6" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11401,13 +11415,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -11426,10 +11440,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="K7" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11437,7 +11451,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>23</v>
@@ -11462,10 +11476,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="K8" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11473,13 +11487,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -11498,10 +11512,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="K9" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11534,10 +11548,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="K10" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11545,13 +11559,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C11" t="s">
         <v>322</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -11570,10 +11584,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="K11" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -11606,10 +11620,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="K12" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -11642,10 +11656,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="K13" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -11653,7 +11667,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C14" s="87" t="s">
         <v>261</v>
@@ -11678,10 +11692,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="K14" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
@@ -11700,72 +11714,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -11796,12 +11810,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -11876,10 +11890,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="K5" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>294</v>
@@ -11890,13 +11904,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>300</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -11915,10 +11929,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="K6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11926,7 +11940,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>300</v>
@@ -11951,10 +11965,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="K7" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11962,7 +11976,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="89" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>246</v>
@@ -11987,10 +12001,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="K8" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11998,7 +12012,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>238</v>
@@ -12023,10 +12037,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="K9" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -12059,10 +12073,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="K10" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -12070,13 +12084,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -12095,10 +12109,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="K11" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -12130,27 +12144,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -12234,7 +12248,7 @@
         <v>153</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E6" s="20">
         <f>INDEX(D2_밀기A!$E:$E,MATCH("세트 합계",D2_밀기A!$D:$D,0))</f>
@@ -12264,7 +12278,7 @@
       </c>
       <c r="F7" s="20" t="str">
         <f>"약 "&amp;INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))&amp;"분"</f>
-        <v>약 70분</v>
+        <v>약 71분</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
@@ -12278,7 +12292,7 @@
         <v>150</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E8" s="20">
         <f>INDEX(D4_어깨팔A!$E:$E,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))</f>
@@ -12286,7 +12300,7 @@
       </c>
       <c r="F8" s="20" t="str">
         <f>"약 "&amp;INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))&amp;"분"</f>
-        <v>약 72분</v>
+        <v>약 73분</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
@@ -12320,7 +12334,7 @@
         <v>150</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="E10" s="20">
         <f>INDEX(D6_당기기B!$E:$E,MATCH("세트 합계",D6_당기기B!$D:$D,0))</f>
@@ -12328,7 +12342,7 @@
       </c>
       <c r="F10" s="20" t="str">
         <f>"약 "&amp;INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))&amp;"분"</f>
-        <v>약 75분</v>
+        <v>약 76분</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
@@ -12342,7 +12356,7 @@
         <v>161</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="E11" s="20">
         <f>INDEX(D7_밀기B!$E:$E,MATCH("세트 합계",D7_밀기B!$D:$D,0))</f>
@@ -12386,7 +12400,7 @@
         <v>150</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E13" s="20">
         <f>INDEX(D9_어깨팔B!$E:$E,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))</f>
@@ -12430,7 +12444,7 @@
       </c>
       <c r="F15" t="str">
         <f>"약 "&amp;(INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0)))&amp;"분 ("&amp;INT((INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0)))/60)&amp;"시간 "&amp;MOD((INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))),60)&amp;"분)"</f>
-        <v>약 579분 (9시간 39분)</v>
+        <v>약 582분 (9시간 42분)</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="89.25" customHeight="1"/>
@@ -12524,32 +12538,32 @@
     </row>
     <row r="35" spans="1:1" ht="90" customHeight="1">
       <c r="A35" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="90" customHeight="1">
       <c r="A36" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="90" customHeight="1">
       <c r="A37" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="90" customHeight="1">
       <c r="A38" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="90" customHeight="1">
       <c r="A39" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="90" customHeight="1">
       <c r="A40" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="51.75" customHeight="1">
@@ -12816,22 +12830,22 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
     </row>
   </sheetData>
@@ -12853,166 +12867,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>915</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>916</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="69" t="s">
         <v>918</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="D6" s="53" t="s">
         <v>921</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>922</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="53" t="s">
         <v>925</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>926</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>926</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>928</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="53" t="s">
         <v>929</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>930</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>930</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="D9" s="53" t="s">
         <v>933</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="D10" s="53" t="s">
         <v>937</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>150</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="D12" s="53" t="s">
         <v>944</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>945</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="79" t="s">
+        <v>945</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>946</v>
+      </c>
+      <c r="C13" s="80" t="s">
         <v>947</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="D13" s="79" t="s">
         <v>948</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>949</v>
-      </c>
-      <c r="D13" s="79" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>949</v>
+      </c>
+      <c r="B14" t="s">
+        <v>950</v>
+      </c>
+      <c r="C14" t="s">
         <v>951</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>952</v>
-      </c>
-      <c r="C14" t="s">
-        <v>953</v>
-      </c>
-      <c r="D14" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -13023,22 +13037,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -13046,137 +13060,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="63" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
   </sheetData>
@@ -13202,17 +13216,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -13221,41 +13235,41 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D6" t="s">
         <v>466</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>467</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>468</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>469</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>470</v>
-      </c>
-      <c r="G6" t="s">
-        <v>471</v>
-      </c>
-      <c r="H6" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
@@ -13272,18 +13286,18 @@
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H7" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B8" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -13300,18 +13314,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H8" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B9" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -13328,18 +13342,18 @@
         <v>0.8</v>
       </c>
       <c r="G9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H9" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B10" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -13356,15 +13370,15 @@
         <v>1.32</v>
       </c>
       <c r="G10" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H10" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B11" t="s">
         <v>237</v>
@@ -13384,15 +13398,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H11" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -13412,18 +13426,18 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H12" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
@@ -13440,15 +13454,15 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H13" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -13468,18 +13482,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H15" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B16" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -13496,15 +13510,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H16" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B17" t="s">
         <v>295</v>
@@ -13524,15 +13538,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H17" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B18" t="s">
         <v>103</v>
@@ -13552,18 +13566,18 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H18" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -13580,15 +13594,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H19" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B20" t="s">
         <v>295</v>
@@ -13608,18 +13622,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H20" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B21" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -13636,18 +13650,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H21" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B22" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C22" t="s">
         <v>238</v>
@@ -13664,18 +13678,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H22" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B23" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C23" t="s">
         <v>238</v>
@@ -13692,18 +13706,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H23" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B24" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C24" t="s">
         <v>246</v>
@@ -13720,18 +13734,18 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H24" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B25" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C25" t="s">
         <v>246</v>
@@ -13748,18 +13762,18 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H25" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B26" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C26" t="s">
         <v>246</v>
@@ -13776,18 +13790,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H26" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B27" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C27" t="s">
         <v>246</v>
@@ -13804,21 +13818,21 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H27" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B28" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C28" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D28">
         <v>0.2</v>
@@ -13832,21 +13846,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H28" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B29" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D29">
         <v>0.2</v>
@@ -13860,21 +13874,21 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H29" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D30">
         <v>0.2</v>
@@ -13888,15 +13902,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H30" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B31" t="s">
         <v>237</v>
@@ -13916,18 +13930,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H31" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B32" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
@@ -13944,15 +13958,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H32" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B33" t="s">
         <v>99</v>
@@ -13972,18 +13986,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H33" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B34" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C34" t="s">
         <v>272</v>
@@ -14000,18 +14014,18 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H34" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B35" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C35" t="s">
         <v>272</v>
@@ -14028,15 +14042,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H35" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B36" t="s">
         <v>99</v>
@@ -14056,15 +14070,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B37" t="s">
         <v>101</v>
@@ -14084,15 +14098,15 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H37" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B38" t="s">
         <v>321</v>
@@ -14112,18 +14126,18 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H38" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B39" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C39" t="s">
         <v>331</v>
@@ -14140,15 +14154,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H39" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B40" t="s">
         <v>101</v>
@@ -14168,21 +14182,21 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H40" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B41" t="s">
         <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D41">
         <v>0.2</v>
@@ -14196,21 +14210,21 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H41" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B42" t="s">
         <v>321</v>
       </c>
       <c r="C42" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D42">
         <v>0.2</v>
@@ -14224,15 +14238,15 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H42" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -14252,18 +14266,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H43" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B44" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C44" t="s">
         <v>45</v>
@@ -14280,15 +14294,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H44" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -14308,18 +14322,18 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H45" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B46" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C46" t="s">
         <v>289</v>
@@ -14336,15 +14350,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H46" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B47" t="s">
         <v>101</v>
@@ -14364,15 +14378,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H47" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -14392,15 +14406,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H48" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -14420,18 +14434,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H49" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B50" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C50" t="s">
         <v>289</v>
@@ -14448,18 +14462,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H50" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B51" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -14476,10 +14490,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H51" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
   </sheetData>
@@ -14505,12 +14519,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -14518,22 +14532,22 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D4" t="s">
         <v>557</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>558</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>559</v>
       </c>
-      <c r="E4" t="s">
-        <v>560</v>
-      </c>
-      <c r="F4" t="s">
-        <v>561</v>
-      </c>
       <c r="G4" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -14557,13 +14571,13 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="G5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I5">
         <f ca="1">SUM(D5:D6)</f>
@@ -14591,10 +14605,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -14618,13 +14632,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H7" t="s">
         <v>1031</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1032</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1033</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -14633,7 +14647,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B8">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A8)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A8)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A8)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A8)</f>
@@ -14652,10 +14666,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G8" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14679,10 +14693,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="G9" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14706,10 +14720,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G10" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14733,10 +14747,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="G11" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14760,10 +14774,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G12" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14787,10 +14801,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G13" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -14814,10 +14828,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14841,13 +14855,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G15" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="H15" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -14875,10 +14889,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G16" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -14902,10 +14916,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G17" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -14929,10 +14943,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G18" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -14956,10 +14970,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G19" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -14983,10 +14997,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G20" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -15010,10 +15024,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G21" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -15037,10 +15051,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="G22" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -15064,15 +15078,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G23" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B24">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A24)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A24)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A24)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A24)</f>
@@ -15091,15 +15105,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G24" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B25">
         <f>SUM(B5:B24)</f>
@@ -15112,67 +15126,67 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -15263,7 +15277,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -15342,7 +15356,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>244</v>
@@ -15354,7 +15368,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>238</v>
@@ -15366,7 +15380,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -15382,10 +15396,10 @@
         <v>44</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="O8" s="26">
         <v>120</v>
@@ -15728,27 +15742,27 @@
     <row r="18" spans="1:12" ht="15" customHeight="1"/>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -15799,7 +15813,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -15952,7 +15966,7 @@
         <v>16</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.5" customHeight="1">
@@ -16111,7 +16125,7 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="L23" s="21" t="s">
         <v>309</v>
@@ -16151,7 +16165,7 @@
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="L24" s="86" t="s">
         <v>311</v>
@@ -16165,7 +16179,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>39</v>
@@ -16191,10 +16205,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O25" s="26">
         <v>60</v>
@@ -16215,17 +16229,17 @@
     </row>
     <row r="27" spans="1:15" ht="16.5" customHeight="1">
       <c r="A27" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -16242,7 +16256,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -16398,7 +16412,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1">
@@ -16552,26 +16566,28 @@
       </c>
       <c r="I18" s="26">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>11.9</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L18" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="L18" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="O18" s="26"/>
+      <c r="O18" s="26">
+        <v>75</v>
+      </c>
     </row>
     <row r="19" spans="1:15" ht="16.5" customHeight="1">
       <c r="A19" s="20">
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>334</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>335</v>
       </c>
       <c r="D19" s="26">
         <v>35</v>
@@ -16594,13 +16610,13 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="L19" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="L19" s="21" t="s">
+      <c r="N19" t="s">
         <v>337</v>
-      </c>
-      <c r="N19" t="s">
-        <v>338</v>
       </c>
       <c r="O19" s="26"/>
     </row>
@@ -16609,7 +16625,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>60</v>
@@ -16635,13 +16651,13 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="L20" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="L20" s="21" t="s">
-        <v>341</v>
-      </c>
       <c r="N20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O20" s="26"/>
     </row>
@@ -16650,7 +16666,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>261</v>
@@ -16676,10 +16692,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>343</v>
-      </c>
-      <c r="L21" s="21" t="s">
-        <v>344</v>
       </c>
       <c r="O21" s="26"/>
     </row>
@@ -16693,10 +16709,24 @@
       </c>
       <c r="I22">
         <f>ROUND(SUM(I15:I21),0)</f>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15" customHeight="1">
+      <c r="A23" s="112" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>1131</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="A15:O21">
@@ -16729,12 +16759,12 @@
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
@@ -16791,7 +16821,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -16799,7 +16829,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>18</v>
@@ -16821,23 +16851,25 @@
       </c>
       <c r="I6" s="26">
         <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND((E6*(G6+H6)+O6)/60,1))</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>347</v>
+        <v>1149</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="O6" s="26"/>
+        <v>346</v>
+      </c>
+      <c r="O6" s="26">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" spans="1:15" ht="16.5" customHeight="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>18</v>
@@ -16862,13 +16894,13 @@
         <v>5.8</v>
       </c>
       <c r="J7" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="L7" s="21" t="s">
         <v>350</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>352</v>
       </c>
       <c r="O7" s="26"/>
     </row>
@@ -16877,7 +16909,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>23</v>
@@ -16902,13 +16934,13 @@
         <v>5.5</v>
       </c>
       <c r="J8" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="L8" s="21" t="s">
         <v>354</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>356</v>
       </c>
       <c r="O8" s="26"/>
     </row>
@@ -16917,7 +16949,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>23</v>
@@ -16942,13 +16974,13 @@
         <v>6</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O9" s="26"/>
     </row>
@@ -16957,13 +16989,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="91" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E10" s="20">
         <v>3</v>
@@ -16983,10 +17015,10 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O10" s="26"/>
     </row>
@@ -17023,7 +17055,7 @@
         <v>302</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="L11" s="36" t="s">
         <v>303</v>
@@ -17036,13 +17068,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>289</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
@@ -17064,10 +17096,10 @@
         <v>27</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O12" s="26">
         <v>60</v>
@@ -17084,7 +17116,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E13" s="20">
         <v>3</v>
@@ -17106,10 +17138,10 @@
         <v>45</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O13" s="26"/>
     </row>
@@ -17144,7 +17176,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>50</v>
@@ -17184,7 +17216,7 @@
         <v>53</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>54</v>
@@ -17222,10 +17254,10 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="O16" s="26"/>
     </row>
@@ -17239,98 +17271,102 @@
       </c>
       <c r="I17">
         <f>ROUND(SUM(I6:I16),0)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="19" spans="1:9" ht="16.5" customHeight="1">
       <c r="A19" s="108" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="109" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16.5" customHeight="1">
       <c r="A21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.5" customHeight="1">
       <c r="A22" s="109" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1">
       <c r="A23" s="109" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5" customHeight="1">
       <c r="A24" s="109" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" customHeight="1">
       <c r="A25" s="109" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5" customHeight="1">
       <c r="A26" s="109" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" customHeight="1">
       <c r="A28" s="109" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="30" spans="1:9" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" customHeight="1">
       <c r="A31" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" customHeight="1">
       <c r="A32" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="16.5" customHeight="1"/>
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A38" t="s">
+        <v>1150</v>
+      </c>
+    </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1"/>
   </sheetData>
@@ -17346,7 +17382,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -17364,17 +17400,17 @@
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="33" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
@@ -17426,7 +17462,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -17434,7 +17470,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>246</v>
@@ -17459,13 +17495,13 @@
         <v>15.8</v>
       </c>
       <c r="J6" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="L6" s="21" t="s">
         <v>385</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>387</v>
       </c>
       <c r="O6" s="26"/>
     </row>
@@ -17474,7 +17510,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>238</v>
@@ -17499,13 +17535,13 @@
         <v>9.5</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O7" s="26"/>
     </row>
@@ -17514,7 +17550,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>238</v>
@@ -17526,7 +17562,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -17539,13 +17575,13 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="O8" s="26">
         <v>120</v>
@@ -17556,7 +17592,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>246</v>
@@ -17578,25 +17614,27 @@
       </c>
       <c r="I9" s="26">
         <f t="shared" si="0"/>
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>1114</v>
+        <v>1152</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="O9" s="26"/>
+        <v>390</v>
+      </c>
+      <c r="O9" s="26">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>23</v>
@@ -17621,13 +17659,13 @@
         <v>0</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="O10" s="26"/>
     </row>
@@ -17636,7 +17674,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>44</v>
@@ -17664,10 +17702,10 @@
         <v>45</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O11" s="26">
         <v>60</v>
@@ -17678,10 +17716,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D12" s="20">
         <v>20</v>
@@ -17703,13 +17741,13 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="J12" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="L12" s="21" t="s">
         <v>398</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>400</v>
       </c>
       <c r="O12" s="26"/>
     </row>
@@ -17744,7 +17782,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>58</v>
@@ -17782,7 +17820,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>62</v>
@@ -17837,43 +17875,48 @@
       </c>
       <c r="I16">
         <f>ROUND(SUM(I6:I15),0)</f>
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B22" s="83"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>1134</v>
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>1153</v>
       </c>
     </row>
   </sheetData>
@@ -17908,17 +17951,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -18066,7 +18109,7 @@
         <v>16</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.5" customHeight="1">
@@ -18074,7 +18117,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C20" s="40" t="s">
         <v>27</v>
@@ -18103,13 +18146,13 @@
         <v>30</v>
       </c>
       <c r="K20" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="L20" s="39" t="s">
+        <v>409</v>
+      </c>
+      <c r="M20" s="38" t="s">
         <v>410</v>
-      </c>
-      <c r="L20" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="M20" s="38" t="s">
-        <v>412</v>
       </c>
       <c r="O20" s="38"/>
     </row>
@@ -18143,13 +18186,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>413</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="L21" s="21" t="s">
-        <v>415</v>
       </c>
       <c r="O21" s="26"/>
     </row>
@@ -18158,7 +18201,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>34</v>
@@ -18186,10 +18229,10 @@
         <v>249</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O22" s="26"/>
     </row>
@@ -18198,7 +18241,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>289</v>
@@ -18226,10 +18269,10 @@
         <v>39</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="O23" s="26"/>
     </row>
@@ -18238,7 +18281,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>300</v>
@@ -18266,10 +18309,10 @@
         <v>291</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="O24" s="26"/>
     </row>
@@ -18278,7 +18321,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C25" s="43" t="s">
         <v>289</v>
@@ -18304,10 +18347,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="O25" s="26">
         <v>60</v>
@@ -18318,7 +18361,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>23</v>
@@ -18344,10 +18387,10 @@
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O26" s="26"/>
     </row>
@@ -18356,7 +18399,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>18</v>
@@ -18382,10 +18425,10 @@
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="O27" s="26"/>
     </row>
@@ -18419,13 +18462,13 @@
         <v>5</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K28" s="21" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="O28" s="26"/>
     </row>
@@ -18434,7 +18477,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="85" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>261</v>
@@ -18460,10 +18503,10 @@
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="O29" s="26"/>
     </row>
@@ -18491,73 +18534,73 @@
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="31" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -18592,17 +18635,17 @@
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1">
@@ -18730,7 +18773,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1">
@@ -18738,7 +18781,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C15" s="40" t="s">
         <v>272</v>
@@ -18764,13 +18807,13 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="K15" s="39" t="s">
+        <v>443</v>
+      </c>
+      <c r="L15" s="39" t="s">
         <v>444</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="L15" s="39" t="s">
-        <v>446</v>
       </c>
       <c r="O15" s="38"/>
     </row>
@@ -18779,7 +18822,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C16" s="40" t="s">
         <v>272</v>
@@ -18805,13 +18848,13 @@
         <v>7.2</v>
       </c>
       <c r="J16" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>446</v>
+      </c>
+      <c r="L16" s="39" t="s">
         <v>444</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>448</v>
-      </c>
-      <c r="L16" s="39" t="s">
-        <v>446</v>
       </c>
       <c r="O16" s="38"/>
     </row>
@@ -18820,7 +18863,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>322</v>
@@ -18848,10 +18891,10 @@
         <v>331</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="O17" s="26"/>
     </row>
@@ -18860,7 +18903,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>331</v>
@@ -18888,10 +18931,10 @@
         <v>317</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="O18" s="26"/>
     </row>
@@ -18900,7 +18943,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>331</v>
@@ -18926,10 +18969,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="O19" s="26"/>
     </row>
@@ -18938,10 +18981,10 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D20" s="26">
         <v>120</v>
@@ -18950,7 +18993,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G20" s="26">
         <v>45</v>
@@ -18966,10 +19009,10 @@
         <v>322</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="O20" s="26"/>
     </row>
@@ -18978,10 +19021,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D21" s="26">
         <v>42</v>
@@ -18990,7 +19033,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -19004,10 +19047,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="O21" s="26">
         <v>75</v>
@@ -19044,10 +19087,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O22" s="26"/>
     </row>
@@ -19066,17 +19109,17 @@
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
       <c r="A24" s="112" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="33" spans="2:2">

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="569" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6628712A-9782-40EA-8F3D-F8BBE07F82EC}"/>
+  <xr:revisionPtr revIDLastSave="573" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F78A285-37AE-49D5-82CA-3AF2FCC32E0D}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="2400" windowWidth="29040" windowHeight="18480" tabRatio="883" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="2400" windowWidth="29040" windowHeight="18480" tabRatio="883" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -17476,7 +17476,7 @@
         <v>246</v>
       </c>
       <c r="D6" s="26">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E6" s="20">
         <v>5</v>
@@ -17516,7 +17516,7 @@
         <v>238</v>
       </c>
       <c r="D7" s="26">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E7" s="20">
         <v>3</v>
@@ -17722,7 +17722,7 @@
         <v>348</v>
       </c>
       <c r="D12" s="20">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E12" s="20">
         <v>4</v>
@@ -17800,7 +17800,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E14" s="20">
         <v>3</v>

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="985" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF7E59C-9738-4EAE-8A98-E91A2FA901A1}"/>
+  <xr:revisionPtr revIDLastSave="997" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91B3E5B-AF4A-41E0-9982-B58D6B7D1901}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" firstSheet="2" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="1210">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -2246,9 +2246,6 @@
     <t>· 평일 두 세션은 둘 다 척추 부하가 0이다. 어느 요일에 걸려도 다음날 근무를 망치지 않도록 그렇게 짰다.</t>
   </si>
   <si>
-    <t>· 12시간이 월·수 / 월·목 / 화·목으로 걸리는 주에는 다음날 회피까지 감안하면 8시간인 평일이 하루뿐이다. 그 주는 3회로 간다 — 평일 B를 뺀다.</t>
-  </si>
-  <si>
     <t>· 평일 두 세션은 붙이지 말고 사이에 하루를 둔다. 볼륨은 시간이 남는 토 · 일로 몰고 평일은 짧게 유지한다 — 근무 뒤에 들어가는 자리이기 때문이다.</t>
   </si>
   <si>
@@ -2660,9 +2657,6 @@
     <t>· 8시간인 평일이 하루뿐인 주에는 이 세션을 뺀다. 네 개 중 가장 먼저 버리는 자리다.</t>
   </si>
   <si>
-    <t>· 다만 뺀 주에는 후면삼각 7세트와 이두 3세트가 통째로 빠지므로 2주 연속으로 빼지는 않는다.</t>
-  </si>
-  <si>
     <t>· 그것은 의지박약이 아니라 그 상황에서의 규율이다.</t>
   </si>
   <si>
@@ -2886,9 +2880,6 @@
   </si>
   <si>
     <t>[105세트가 버거우면 이 순서로 뺀다]</t>
-  </si>
-  <si>
-    <t>· 1순위 — 평일 B 전체(26). 메인 리프트가 없는 유일한 세션이라 주 3회로 떨어뜨리는 가장 싼 방법이다.</t>
   </si>
   <si>
     <t>· 2순위 — 전완 2종목(6). 그립은 현장에서 온종일 쓰므로 실질 손실이 가장 적다.</t>
@@ -3800,6 +3791,39 @@
   </si>
   <si>
     <t>· 중둔근 3.0 → 8.0 — 2026-09-13에 토요일 아우터 타이를 이너 타이와 슈퍼세트로 넣고 5세트로 올렸다. 유지 하한에 닿았다. 프로그램 최하위였던 자리이고, 슈퍼세트라 5세트 값이 6분이다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>[평일 B를 빼는 주 — 어깨 축약분]</t>
+  </si>
+  <si>
+    <t>· 8시간 평일이 하루뿐인 주에는 평일 B가 빠진다. 그 주에는 이 세션 맨 뒤에 두 종목을 얹는다 — 레터럴 레이즈 3세트(8~10kg · 12~15회 · 수행 40초 · 휴식 60초) · 케이블 리버스 플라이 3세트(5~7kg · 12~15회 · 수행 40초 · 휴식 60초).</t>
+  </si>
+  <si>
+    <t>· 이 6세트만 얹는 이유 — 평일 B가 빠지면 측면 삼각이 12 → 4, 후면 삼각이 10 → 3으로 내려앉는다. 둘 다 현장 일 보정이 '없음'인 부위라 빠진 만큼이 그대로 손실이다. 반대로 광배 · 승모 중부 · 대퇴사두는 평일 B에 한 세트도 없어 아무 영향이 없다.</t>
+  </si>
+  <si>
+    <t>· 이두 3 · 둔근 3 · 복부 3도 같이 빠지지만 얹지 않는다. 이두는 일요일 프리쳐 컬 3세트가 남고, 둔근은 스쿼트 · 데드의 간접이 4.5를 채운다. 복부 3세트는 한 주 비워도 되는 자리다.</t>
+  </si>
+  <si>
+    <t>· 그 주의 평일 A는 34세트 · 약 86분이 된다. 평상시(28 · 80분)보다 길지만 그 주는 주 3회라 총량이 이미 35세트 줄어 있다. 근무 뒤 세션이므로 축약분은 맨 뒤에 두고, 시간이 없으면 레터럴부터 한다 — 측면 삼각이 잃는 양이 더 크다.</t>
+  </si>
+  <si>
+    <t>· 축약분은 세트검산과 총량 예산에 넣지 않는다. 평상시 배치가 아니라 그 주에만 쓰는 대체분이다.</t>
+  </si>
+  <si>
+    <t>· 다만 뺀 주에는 측면 삼각이 12 → 4, 후면 삼각이 10 → 3으로 내려앉는다. 둘 다 현장 일이 안 채워주는 부위다. 그래서 빼는 주에는 평일 A 뒤에 레터럴 3 + 케이블 리버스 플라이 3을 얹는다 — 복귀_평일A_가슴 시트 아래 [평일 B를 빼는 주 — 어깨 축약분] 참조.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 2주 연속으로 빼지는 않는다. 빼는 주는 증량기록 메모에 적어 둔다 — 연속인지가 기억이 아니라 기록으로 보여야 지켜진다.</t>
+  </si>
+  <si>
+    <t>· 1순위 — 평일 B 전체. 메인 리프트가 없는 유일한 세션이라 주 3회로 떨어뜨리는 가장 싼 방법이다. 단 빼는 주에는 평일 A 뒤에 레터럴 3 + 케이블 리버스 플라이 3을 얹는다 — 어깨 세 갈래와 이두가 전부 이 세션에 있고 넷 다 현장 일이 안 채워주는 부위다. 싼 것은 메인 리프트를 안 잃는다는 뜻이고, 어깨까지 공짜라는 뜻은 아니다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 12시간이 월·수 / 월·목 / 화·목으로 걸리는 주에는 다음날 회피까지 감안하면 8시간인 평일이 하루뿐이다. 그 주는 3회로 간다 — 평일 B를 뺀다. 그 주에는 평일 A 뒤에 레터럴 3 + 케이블 리버스 플라이 3을 얹어 어깨 손실만 메운다 (복귀_평일A_가슴 시트 아래 [평일 B를 빼는 주 — 어깨 축약분]).</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
@@ -4770,6 +4794,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5193,7 +5221,7 @@
     </row>
     <row r="34" spans="1:5" ht="51.75" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="64.5" customHeight="1">
@@ -5208,17 +5236,17 @@
     </row>
     <row r="37" spans="1:5" ht="26.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.25" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5" customHeight="1">
@@ -5532,7 +5560,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
@@ -5589,7 +5617,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -5753,7 +5781,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>299</v>
@@ -5779,7 +5807,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>306</v>
@@ -5895,7 +5923,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>367</v>
@@ -5933,7 +5961,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>369</v>
@@ -5974,7 +6002,7 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>370</v>
@@ -5999,7 +6027,7 @@
     </row>
     <row r="17" spans="1:6" ht="16.5" customHeight="1">
       <c r="F17" s="87" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" customHeight="1">
@@ -6135,22 +6163,22 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="31" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -6468,7 +6496,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B15" s="45" t="s">
         <v>298</v>
@@ -6608,7 +6636,7 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>298</v>
@@ -7812,7 +7840,7 @@
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="45" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B63" s="45" t="s">
         <v>51</v>
@@ -8095,7 +8123,7 @@
         <v>470</v>
       </c>
       <c r="B73" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C73" t="s">
         <v>44</v>
@@ -8115,7 +8143,7 @@
         <v>471</v>
       </c>
       <c r="H73" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -8123,7 +8151,7 @@
         <v>474</v>
       </c>
       <c r="B74" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C74" t="s">
         <v>44</v>
@@ -8143,7 +8171,7 @@
         <v>471</v>
       </c>
       <c r="H74" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -8151,7 +8179,7 @@
         <v>474</v>
       </c>
       <c r="B75" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C75" t="s">
         <v>245</v>
@@ -8171,7 +8199,7 @@
         <v>471</v>
       </c>
       <c r="H75" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
@@ -8826,7 +8854,7 @@
         <v>성장</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="G20" s="57"/>
       <c r="J20" s="55">
@@ -9338,7 +9366,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -9353,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9543,7 +9571,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="65" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="L14" s="103"/>
       <c r="M14" s="103"/>
@@ -10238,12 +10266,12 @@
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>730</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -10251,22 +10279,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -10274,32 +10302,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -10307,47 +10335,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="74" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -10357,27 +10385,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -10408,28 +10436,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="19" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10494,23 +10522,23 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="31" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="19" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -10575,7 +10603,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="31" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -10624,7 +10652,7 @@
         <v>16</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="29.25" customHeight="1">
@@ -10658,10 +10686,10 @@
         <v>17.5</v>
       </c>
       <c r="J24" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="K24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L24" s="68" t="s">
         <v>293</v>
@@ -10672,7 +10700,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C25" s="67" t="s">
         <v>27</v>
@@ -10698,10 +10726,10 @@
         <v>10.5</v>
       </c>
       <c r="J25" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="K25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L25" s="68" t="s">
         <v>409</v>
@@ -10737,10 +10765,10 @@
         <v>13</v>
       </c>
       <c r="J26" t="s">
+        <v>760</v>
+      </c>
+      <c r="K26" t="s">
         <v>761</v>
-      </c>
-      <c r="K26" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
@@ -10773,10 +10801,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J27" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="K27" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="N27">
         <v>75</v>
@@ -10812,10 +10840,10 @@
         <v>9</v>
       </c>
       <c r="J28" t="s">
+        <v>763</v>
+      </c>
+      <c r="K28" t="s">
         <v>764</v>
-      </c>
-      <c r="K28" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
@@ -10829,7 +10857,7 @@
         <v>333</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E29" s="7">
         <v>4</v>
@@ -10848,10 +10876,10 @@
         <v>3.3</v>
       </c>
       <c r="J29" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="K29" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="M29" t="s">
         <v>336</v>
@@ -10887,7 +10915,7 @@
         <v>13.3</v>
       </c>
       <c r="J30" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="K30" t="s">
         <v>339</v>
@@ -10926,10 +10954,10 @@
         <v>5.8</v>
       </c>
       <c r="J31" t="s">
+        <v>767</v>
+      </c>
+      <c r="K31" t="s">
         <v>768</v>
-      </c>
-      <c r="K31" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
@@ -10937,13 +10965,13 @@
         <v>9</v>
       </c>
       <c r="B32" s="87" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="76" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E32" s="28">
         <v>3</v>
@@ -10962,10 +10990,10 @@
         <v>6</v>
       </c>
       <c r="J32" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="K32" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="N32">
         <v>60</v>
@@ -11001,10 +11029,10 @@
         <v>7.7</v>
       </c>
       <c r="J33" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="K33" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="N33">
         <v>60</v>
@@ -11030,97 +11058,97 @@
     </row>
     <row r="36" spans="1:14" ht="293.25" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="276" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="C58" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -11151,28 +11179,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="19" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -11237,7 +11265,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="31" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -11286,7 +11314,7 @@
         <v>16</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="29.25" customHeight="1">
@@ -11320,10 +11348,10 @@
         <v>3.5</v>
       </c>
       <c r="J15" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="K15" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -11331,13 +11359,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>245</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E16" s="7">
         <v>4</v>
@@ -11356,13 +11384,13 @@
         <v>12.7</v>
       </c>
       <c r="J16" t="s">
+        <v>791</v>
+      </c>
+      <c r="K16" t="s">
         <v>792</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="53" t="s">
         <v>793</v>
-      </c>
-      <c r="L16" s="53" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1">
@@ -11370,7 +11398,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="89" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>237</v>
@@ -11395,10 +11423,10 @@
         <v>13.7</v>
       </c>
       <c r="J17" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="K17" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N17">
         <v>60</v>
@@ -11434,13 +11462,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J18" t="s">
+        <v>796</v>
+      </c>
+      <c r="K18" t="s">
         <v>797</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" s="53" t="s">
         <v>798</v>
-      </c>
-      <c r="L18" s="53" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="29.25" customHeight="1">
@@ -11454,7 +11482,7 @@
         <v>245</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E19" s="7">
         <v>3</v>
@@ -11473,10 +11501,10 @@
         <v>6.8</v>
       </c>
       <c r="J19" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="K19" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N19">
         <v>60</v>
@@ -11493,7 +11521,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E20" s="7">
         <v>3</v>
@@ -11512,10 +11540,10 @@
         <v>5.8</v>
       </c>
       <c r="J20" t="s">
+        <v>801</v>
+      </c>
+      <c r="K20" t="s">
         <v>802</v>
-      </c>
-      <c r="K20" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1">
@@ -11548,13 +11576,13 @@
         <v>8</v>
       </c>
       <c r="J21" t="s">
+        <v>803</v>
+      </c>
+      <c r="K21" t="s">
         <v>804</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" s="53" t="s">
         <v>805</v>
-      </c>
-      <c r="L21" s="53" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
@@ -11587,10 +11615,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J22" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="K22" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N22">
         <v>60</v>
@@ -11626,10 +11654,10 @@
         <v>6.8</v>
       </c>
       <c r="J23" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="K23" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N23">
         <v>60</v>
@@ -11640,7 +11668,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C24" t="s">
         <v>45</v>
@@ -11665,10 +11693,10 @@
         <v>5</v>
       </c>
       <c r="J24" t="s">
+        <v>809</v>
+      </c>
+      <c r="K24" t="s">
         <v>810</v>
-      </c>
-      <c r="K24" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="17.25" customHeight="1">
@@ -11701,10 +11729,10 @@
         <v>5</v>
       </c>
       <c r="J25" t="s">
+        <v>811</v>
+      </c>
+      <c r="K25" t="s">
         <v>812</v>
-      </c>
-      <c r="K25" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="23.25" customHeight="1">
@@ -11727,132 +11755,132 @@
     </row>
     <row r="28" spans="1:14" ht="278.25" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="63" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="95.25" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="252.75" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="237.75" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="265.5" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="C58" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
   </sheetData>
@@ -11864,7 +11892,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11883,32 +11911,32 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="31" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="31" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="31" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -11957,7 +11985,7 @@
         <v>16</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
@@ -11990,7 +12018,7 @@
         <v>10.7</v>
       </c>
       <c r="J11" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K11" t="s">
         <v>32</v>
@@ -12026,10 +12054,10 @@
         <v>7.7</v>
       </c>
       <c r="J12" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="K12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="N12">
         <v>60</v>
@@ -12040,13 +12068,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E13" s="7">
         <v>4</v>
@@ -12065,10 +12093,10 @@
         <v>8</v>
       </c>
       <c r="J13" t="s">
+        <v>841</v>
+      </c>
+      <c r="K13" t="s">
         <v>842</v>
-      </c>
-      <c r="K13" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -12101,10 +12129,10 @@
         <v>6.7</v>
       </c>
       <c r="J14" t="s">
+        <v>843</v>
+      </c>
+      <c r="K14" t="s">
         <v>844</v>
-      </c>
-      <c r="K14" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -12118,7 +12146,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E15" s="7">
         <v>3</v>
@@ -12137,10 +12165,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
+        <v>845</v>
+      </c>
+      <c r="K15" t="s">
         <v>846</v>
-      </c>
-      <c r="K15" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -12173,10 +12201,10 @@
         <v>5.8</v>
       </c>
       <c r="J16" t="s">
+        <v>847</v>
+      </c>
+      <c r="K16" t="s">
         <v>848</v>
-      </c>
-      <c r="K16" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1">
@@ -12190,7 +12218,7 @@
         <v>321</v>
       </c>
       <c r="D17" s="76" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E17" s="28">
         <v>3</v>
@@ -12209,10 +12237,10 @@
         <v>8</v>
       </c>
       <c r="J17" t="s">
+        <v>850</v>
+      </c>
+      <c r="K17" t="s">
         <v>851</v>
-      </c>
-      <c r="K17" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -12245,10 +12273,10 @@
         <v>6.8</v>
       </c>
       <c r="J18" t="s">
+        <v>852</v>
+      </c>
+      <c r="K18" t="s">
         <v>853</v>
-      </c>
-      <c r="K18" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1">
@@ -12281,10 +12309,10 @@
         <v>11.9</v>
       </c>
       <c r="J19" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="K19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="N19">
         <v>75</v>
@@ -12320,10 +12348,10 @@
         <v>5</v>
       </c>
       <c r="J20" t="s">
+        <v>855</v>
+      </c>
+      <c r="K20" t="s">
         <v>856</v>
-      </c>
-      <c r="K20" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="25.5" customHeight="1">
@@ -12342,92 +12370,97 @@
     </row>
     <row r="22" spans="1:14" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>868</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>1153</v>
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="C43" t="s">
-        <v>870</v>
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="C44" t="s">
+        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -12439,7 +12472,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12458,28 +12491,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="19" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -12544,7 +12577,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="31" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -12613,7 +12646,7 @@
         <v>16</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1">
@@ -12647,10 +12680,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K20" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="L20" s="68" t="s">
         <v>293</v>
@@ -12667,7 +12700,7 @@
         <v>299</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E21" s="7">
         <v>5</v>
@@ -12686,10 +12719,10 @@
         <v>15.8</v>
       </c>
       <c r="J21" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="K21" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
@@ -12697,7 +12730,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>299</v>
@@ -12722,10 +12755,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="K22" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1">
@@ -12758,10 +12791,10 @@
         <v>12.7</v>
       </c>
       <c r="J23" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="K23" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1">
@@ -12769,7 +12802,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="89" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>237</v>
@@ -12794,10 +12827,10 @@
         <v>11.7</v>
       </c>
       <c r="J24" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="K24" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="N24">
         <v>60</v>
@@ -12833,10 +12866,10 @@
         <v>5.8</v>
       </c>
       <c r="J25" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="K25" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
@@ -12869,10 +12902,10 @@
         <v>6.5</v>
       </c>
       <c r="J26" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="K26" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="N26">
         <v>60</v>
@@ -12905,49 +12938,79 @@
     <row r="31" spans="1:14" ht="237.75" customHeight="1">
       <c r="A31" s="11"/>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="C53" t="s">
         <v>888</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="C46" t="s">
-        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -13031,7 +13094,7 @@
         <v>152</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E6" s="20">
         <f>INDEX(D2_밀기A!$E:$E,MATCH("세트 합계",D2_밀기A!$D:$D,0))</f>
@@ -13075,7 +13138,7 @@
         <v>149</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E8" s="20">
         <f>INDEX(D4_어깨팔A!$E:$E,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))</f>
@@ -13117,7 +13180,7 @@
         <v>149</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="E10" s="20">
         <f>INDEX(D6_당기기B!$E:$E,MATCH("세트 합계",D6_당기기B!$D:$D,0))</f>
@@ -13139,7 +13202,7 @@
         <v>160</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E11" s="20">
         <f>INDEX(D7_밀기B!$E:$E,MATCH("세트 합계",D7_밀기B!$D:$D,0))</f>
@@ -13183,7 +13246,7 @@
         <v>149</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="E13" s="20">
         <f>INDEX(D9_어깨팔B!$E:$E,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))</f>
@@ -13321,32 +13384,32 @@
     </row>
     <row r="35" spans="1:1" ht="90" customHeight="1">
       <c r="A35" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="90" customHeight="1">
       <c r="A36" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="90" customHeight="1">
       <c r="A37" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="90" customHeight="1">
       <c r="A38" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="90" customHeight="1">
       <c r="A39" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="90" customHeight="1">
       <c r="A40" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="51.75" customHeight="1">
@@ -13613,22 +13676,22 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
   </sheetData>
@@ -13650,23 +13713,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>893</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>894</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>895</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>661</v>
@@ -13674,16 +13737,16 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="69" t="s">
         <v>897</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>898</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
@@ -13691,125 +13754,125 @@
         <v>673</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="D6" s="53" t="s">
         <v>900</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>903</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="53" t="s">
         <v>904</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>905</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>907</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="53" t="s">
         <v>908</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="D10" s="53" t="s">
         <v>914</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>915</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>149</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="D12" s="53" t="s">
         <v>921</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>922</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="79" t="s">
+        <v>922</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>923</v>
+      </c>
+      <c r="C13" s="80" t="s">
         <v>924</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="D13" s="79" t="s">
         <v>925</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>926</v>
-      </c>
-      <c r="D13" s="79" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>926</v>
+      </c>
+      <c r="B14" t="s">
+        <v>927</v>
+      </c>
+      <c r="C14" t="s">
         <v>928</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>929</v>
-      </c>
-      <c r="C14" t="s">
-        <v>930</v>
-      </c>
-      <c r="D14" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -13817,37 +13880,37 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="39" customHeight="1">
@@ -13855,22 +13918,22 @@
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="39" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="51.75" customHeight="1">
@@ -13878,137 +13941,137 @@
     </row>
     <row r="29" spans="1:1" ht="39" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" customHeight="1">
       <c r="A30" s="63" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="51.75" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="39" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>944</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -14034,12 +14097,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -14053,12 +14116,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B6" t="s">
         <v>463</v>
@@ -14084,7 +14147,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B7" t="s">
         <v>381</v>
@@ -14107,15 +14170,15 @@
         <v>483</v>
       </c>
       <c r="H7" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B8" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -14135,15 +14198,15 @@
         <v>483</v>
       </c>
       <c r="H8" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -14163,15 +14226,15 @@
         <v>483</v>
       </c>
       <c r="H9" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -14191,12 +14254,12 @@
         <v>483</v>
       </c>
       <c r="H10" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B11" t="s">
         <v>236</v>
@@ -14219,12 +14282,12 @@
         <v>483</v>
       </c>
       <c r="H11" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -14247,12 +14310,12 @@
         <v>483</v>
       </c>
       <c r="H12" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B13" t="s">
         <v>418</v>
@@ -14275,12 +14338,12 @@
         <v>483</v>
       </c>
       <c r="H13" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -14303,15 +14366,15 @@
         <v>483</v>
       </c>
       <c r="H15" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B16" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -14331,12 +14394,12 @@
         <v>483</v>
       </c>
       <c r="H16" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B17" t="s">
         <v>294</v>
@@ -14359,12 +14422,12 @@
         <v>483</v>
       </c>
       <c r="H17" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B18" t="s">
         <v>103</v>
@@ -14387,12 +14450,12 @@
         <v>483</v>
       </c>
       <c r="H18" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B19" t="s">
         <v>418</v>
@@ -14415,12 +14478,12 @@
         <v>483</v>
       </c>
       <c r="H19" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B20" t="s">
         <v>294</v>
@@ -14443,15 +14506,15 @@
         <v>483</v>
       </c>
       <c r="H20" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B21" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -14471,12 +14534,12 @@
         <v>483</v>
       </c>
       <c r="H21" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B22" t="s">
         <v>381</v>
@@ -14499,15 +14562,15 @@
         <v>483</v>
       </c>
       <c r="H22" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B23" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C23" t="s">
         <v>237</v>
@@ -14527,15 +14590,15 @@
         <v>483</v>
       </c>
       <c r="H23" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B24" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C24" t="s">
         <v>245</v>
@@ -14555,12 +14618,12 @@
         <v>483</v>
       </c>
       <c r="H24" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B25" t="s">
         <v>350</v>
@@ -14583,12 +14646,12 @@
         <v>483</v>
       </c>
       <c r="H25" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B26" t="s">
         <v>421</v>
@@ -14611,15 +14674,15 @@
         <v>483</v>
       </c>
       <c r="H26" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B27" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C27" t="s">
         <v>245</v>
@@ -14639,15 +14702,15 @@
         <v>483</v>
       </c>
       <c r="H27" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B28" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C28" t="s">
         <v>347</v>
@@ -14667,15 +14730,15 @@
         <v>483</v>
       </c>
       <c r="H28" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B29" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C29" t="s">
         <v>347</v>
@@ -14695,12 +14758,12 @@
         <v>483</v>
       </c>
       <c r="H29" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -14723,12 +14786,12 @@
         <v>483</v>
       </c>
       <c r="H30" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B31" t="s">
         <v>236</v>
@@ -14751,15 +14814,15 @@
         <v>483</v>
       </c>
       <c r="H31" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B32" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
@@ -14779,12 +14842,12 @@
         <v>483</v>
       </c>
       <c r="H32" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B33" t="s">
         <v>99</v>
@@ -14807,15 +14870,15 @@
         <v>483</v>
       </c>
       <c r="H33" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B34" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C34" t="s">
         <v>271</v>
@@ -14835,12 +14898,12 @@
         <v>483</v>
       </c>
       <c r="H34" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B35" t="s">
         <v>398</v>
@@ -14863,12 +14926,12 @@
         <v>483</v>
       </c>
       <c r="H35" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B36" t="s">
         <v>99</v>
@@ -14896,7 +14959,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B37" t="s">
         <v>101</v>
@@ -14919,12 +14982,12 @@
         <v>483</v>
       </c>
       <c r="H37" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B38" t="s">
         <v>320</v>
@@ -14952,7 +15015,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B39" t="s">
         <v>446</v>
@@ -14975,12 +15038,12 @@
         <v>483</v>
       </c>
       <c r="H39" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B40" t="s">
         <v>101</v>
@@ -15003,12 +15066,12 @@
         <v>483</v>
       </c>
       <c r="H40" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B41" t="s">
         <v>99</v>
@@ -15031,12 +15094,12 @@
         <v>483</v>
       </c>
       <c r="H41" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B42" t="s">
         <v>320</v>
@@ -15059,12 +15122,12 @@
         <v>483</v>
       </c>
       <c r="H42" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -15092,7 +15155,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B44" t="s">
         <v>392</v>
@@ -15120,7 +15183,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -15143,12 +15206,12 @@
         <v>483</v>
       </c>
       <c r="H45" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B46" t="s">
         <v>418</v>
@@ -15171,12 +15234,12 @@
         <v>483</v>
       </c>
       <c r="H46" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B47" t="s">
         <v>101</v>
@@ -15199,12 +15262,12 @@
         <v>483</v>
       </c>
       <c r="H47" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -15227,12 +15290,12 @@
         <v>483</v>
       </c>
       <c r="H48" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -15255,15 +15318,15 @@
         <v>483</v>
       </c>
       <c r="H49" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B50" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C50" t="s">
         <v>288</v>
@@ -15283,15 +15346,15 @@
         <v>483</v>
       </c>
       <c r="H50" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B51" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -15311,7 +15374,7 @@
         <v>483</v>
       </c>
       <c r="H51" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
   </sheetData>
@@ -15337,15 +15400,15 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="G2" s="94" t="s">
         <v>548</v>
@@ -15414,7 +15477,7 @@
         <v>558</v>
       </c>
       <c r="G4" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -15438,7 +15501,7 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="G5" t="s">
         <v>619</v>
@@ -15472,7 +15535,7 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="G6" t="s">
         <v>619</v>
@@ -15499,13 +15562,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G7" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="H7" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -15533,10 +15596,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="G8" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -15560,10 +15623,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="G9" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -15587,10 +15650,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="G10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -15614,10 +15677,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="G11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -15641,7 +15704,7 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="G12" t="s">
         <v>619</v>
@@ -15668,7 +15731,7 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="G13" t="s">
         <v>619</v>
@@ -15695,7 +15758,7 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="G14" t="s">
         <v>619</v>
@@ -15722,13 +15785,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G15" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="H15" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -15756,10 +15819,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G16" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -15783,10 +15846,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="G17" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -15810,10 +15873,10 @@
         <v>하한</v>
       </c>
       <c r="F18" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="G18" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -15837,10 +15900,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="G19" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -15864,7 +15927,7 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="G20" t="s">
         <v>619</v>
@@ -15891,7 +15954,7 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="G21" t="s">
         <v>619</v>
@@ -15918,10 +15981,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="G22" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -15945,10 +16008,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="G23" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -15972,7 +16035,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="G24" t="s">
         <v>619</v>
@@ -15998,62 +16061,62 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -16089,7 +16152,7 @@
         <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="E45" t="s">
         <v>149</v>
@@ -16102,7 +16165,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -16112,17 +16175,17 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>
@@ -16226,7 +16289,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -16305,7 +16368,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>243</v>
@@ -16317,7 +16380,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>237</v>
@@ -16329,7 +16392,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -16345,10 +16408,10 @@
         <v>44</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="O8" s="26">
         <v>120</v>
@@ -16691,27 +16754,27 @@
     <row r="18" spans="1:12" ht="15" customHeight="1"/>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -16762,7 +16825,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -16915,7 +16978,7 @@
         <v>16</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.5" customHeight="1">
@@ -17074,7 +17137,7 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="L23" s="21" t="s">
         <v>308</v>
@@ -17114,7 +17177,7 @@
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="L24" s="86" t="s">
         <v>310</v>
@@ -17154,7 +17217,7 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="L25" s="21" t="s">
         <v>362</v>
@@ -17178,17 +17241,17 @@
     </row>
     <row r="27" spans="1:15" ht="16.5" customHeight="1">
       <c r="A27" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -17361,7 +17424,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1">
@@ -17519,7 +17582,7 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="L18" s="21" t="s">
         <v>331</v>
@@ -17663,17 +17726,17 @@
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1">
       <c r="A23" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -17713,7 +17776,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
@@ -17770,7 +17833,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -17804,7 +17867,7 @@
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="L6" s="21" t="s">
         <v>345</v>
@@ -17964,7 +18027,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>400</v>
@@ -18004,7 +18067,7 @@
         <v>301</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="L11" s="36" t="s">
         <v>302</v>
@@ -18045,7 +18108,7 @@
         <v>27</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="L12" s="21" t="s">
         <v>360</v>
@@ -18125,7 +18188,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>50</v>
@@ -18165,7 +18228,7 @@
         <v>53</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>54</v>
@@ -18203,7 +18266,7 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="L16" s="21" t="s">
         <v>401</v>
@@ -18225,7 +18288,7 @@
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1">
       <c r="F18" s="87" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.5" customHeight="1">
@@ -18255,7 +18318,7 @@
     </row>
     <row r="24" spans="1:9" ht="16.5" customHeight="1">
       <c r="A24" s="109" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" customHeight="1">
@@ -18270,7 +18333,7 @@
     </row>
     <row r="27" spans="1:9" ht="16.5" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" customHeight="1">
@@ -18281,43 +18344,43 @@
     <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="30" spans="1:9" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" customHeight="1">
       <c r="A31" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" customHeight="1">
       <c r="A32" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
@@ -18358,7 +18421,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -18415,7 +18478,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -18491,7 +18554,7 @@
         <v>382</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>386</v>
@@ -18503,7 +18566,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>237</v>
@@ -18515,7 +18578,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -18531,10 +18594,10 @@
         <v>382</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="O8" s="26">
         <v>120</v>
@@ -18573,7 +18636,7 @@
         <v>388</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="L9" s="21" t="s">
         <v>389</v>
@@ -18655,7 +18718,7 @@
         <v>45</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="L11" s="22" t="s">
         <v>393</v>
@@ -18735,7 +18798,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>58</v>
@@ -18773,7 +18836,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>62</v>
@@ -18833,43 +18896,43 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="B22" s="83"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -18909,7 +18972,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -19062,7 +19125,7 @@
         <v>16</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.5" customHeight="1">
@@ -19300,10 +19363,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="O25" s="26">
         <v>60</v>
@@ -19456,7 +19519,7 @@
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="L29" s="21" t="s">
         <v>403</v>
@@ -19528,32 +19591,32 @@
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -19726,7 +19789,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1">
@@ -19934,10 +19997,10 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="D20" s="26">
         <v>120</v>
@@ -19946,7 +20009,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="G20" s="26">
         <v>45</v>
@@ -19962,10 +20025,10 @@
         <v>321</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="O20" s="26"/>
     </row>
@@ -19974,10 +20037,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="D21" s="26">
         <v>42</v>
@@ -19986,7 +20049,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -20000,10 +20063,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="O21" s="26">
         <v>75</v>
@@ -20062,17 +20125,17 @@
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
       <c r="A24" s="112" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="33" spans="2:2">

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="997" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91B3E5B-AF4A-41E0-9982-B58D6B7D1901}"/>
+  <xr:revisionPtr revIDLastSave="1012" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84267A0D-6D16-48F2-B716-3D008ECB9859}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" firstSheet="2" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="1221">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -3825,6 +3825,39 @@
   <si>
     <t>· 12시간이 월·수 / 월·목 / 화·목으로 걸리는 주에는 다음날 회피까지 감안하면 8시간인 평일이 하루뿐이다. 그 주는 3회로 간다 — 평일 B를 뺀다. 그 주에는 평일 A 뒤에 레터럴 3 + 케이블 리버스 플라이 3을 얹어 어깨 손실만 메운다 (복귀_평일A_가슴 시트 아래 [평일 B를 빼는 주 — 어깨 축약분]).</t>
     <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>복귀 운용 — 날짜로 자동 계산 (2026-09-13 신설)</t>
+  </si>
+  <si>
+    <t>복귀 시작일</t>
+  </si>
+  <si>
+    <t>← 복귀 1주차가 시작된 월요일. 주차는 월요일에 넘어간다</t>
+  </si>
+  <si>
+    <t>복귀 시작 사이클</t>
+  </si>
+  <si>
+    <t>← 그 주에 쓰고 있던 사이클 번호</t>
+  </si>
+  <si>
+    <t>사이클 전진(주)</t>
+  </si>
+  <si>
+    <t>← 몇 주마다 사이클을 한 칸 올릴지. 복귀는 2주</t>
+  </si>
+  <si>
+    <t>· 앱 '복귀 → 달력'이 이 세 칸으로 오늘의 주차 · 사이클 · 네 리프트 중량을 계산한다. 손으로 셀 필요가 없고, 어디쯤인지 까먹어도 달력이 알려준다.</t>
+  </si>
+  <si>
+    <t>· 디로드 주나 통째로 쉰 주가 있으면 앱 달력에서 '한 주 미루기'를 누른다 — 그 폰에만 저장되고 사이클이 그만큼 늦게 올라간다. 영구히 맞추려면 위 '복귀 시작일'을 그만큼 뒤로 미룬다.</t>
+  </si>
+  <si>
+    <t>· 중량 자체는 증량기록 표(사이클 단위)가 그대로 정한다. 이 칸들이 정하는 것은 '오늘이 몇 번째 칸인가'뿐이다 — 표가 두 벌로 갈리지 않게 하려고 그렇게 뒀다.</t>
+  </si>
+  <si>
+    <t>· 재택으로 돌아가면 이 칸들은 무시된다. 재택은 일차 회전을 증량기록 '날짜 (1일차)'로 따라간다.</t>
   </si>
 </sst>
 </file>
@@ -4977,7 +5010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5526,6 +5559,64 @@
     <row r="56" spans="1:5" ht="51.75" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C59" s="113">
+        <v>46265</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C60">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>1220</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1012" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84267A0D-6D16-48F2-B716-3D008ECB9859}"/>
+  <xr:revisionPtr revIDLastSave="1039" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAA239DB-EB37-4545-B0BF-1D3FEBFBA271}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" firstSheet="2" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="1223">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -1391,9 +1391,6 @@
     <t>데드리프트 (백오프)</t>
   </si>
   <si>
-    <t>백오프 = 톱세트 − 5kg = 직전 사이클의 톱세트 중량. 즉 모든 중량을 두 번 만난다 — 한 사이클은 톱으로 5회, 다음 사이클은 백오프로 10회. 중량 하나당 노출이 5 → 15회다. 여기는 기록이 아니라 폼 연습 자리다. 여유 있게 5회, 매 렙 셋업을 새로 잡을 것 — 무겁게 느껴지면 톱세트가 과했던 것이다. 현장 복귀 시 이 행은 0세트로 내린다 (복귀판은 데드 1×5가 상한)</t>
-  </si>
-  <si>
     <t>힙 쓰러스트</t>
   </si>
   <si>
@@ -2498,12 +2495,6 @@
     <t>[데드리프트 운용 규칙]</t>
   </si>
   <si>
-    <t>· 첫 4주는 1×5를 넘기지 않는다. 허리는 현장 일과 직접 경쟁하는 유일한 부위이고, 여기를 밀려다 나머지 셋이 다 무너진다.</t>
-  </si>
-  <si>
-    <t>· 4주간 다음 근무일 아침 허리가 깨끗하면 2×5로 올린다. 그때가 데드가 성장으로 돌아서는 지점이다.</t>
-  </si>
-  <si>
     <t>· 볼륨을 올리고 싶은데 허리가 애매하면 트랩바로 바꾸는 것이 먼저다 — 요추 전단력이 낮아 같은 세트에서 비용이 싸다.</t>
   </si>
   <si>
@@ -3087,9 +3078,6 @@
   </si>
   <si>
     <t>직접 11세트: 평일A 넓은 그립 해머 로우 4 · 일요일 넓은 그립 스미스 바벨 로우 4 · 스캡 슈러그 3. 간접은 시티드 케이블 로우 0.5 · 리어델트 계열(케이블 리버스 플라이 0.5 · 벤트오버 머신 0.33 · 리버스 펙덱 0.33).</t>
-  </si>
-  <si>
-    <t>스쿼트 0.2×5 + 스미스 로우 0.2×3 + 오버헤드 슈러그 0.2×3 = 2.2. 직접 1세트(데드 1×5). 낮은 것이 의도다 — 허리는 현장 일과 직접 경쟁하므로 데드 주 1회 1세트가 상한이다. 4주간 지표가 깨끗하면 2×5로 올린다.</t>
   </si>
   <si>
     <t>벤치 0.5×5 + 인클라인 머신 0.5×3 + 딥스 0.2×3 = 4.6. 직접 6세트: 머신 숄더 3 · 스미스 오버헤드 3.</t>
@@ -3717,10 +3705,6 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>지키는 종목. 허리는 현장 일과 직접 경쟁하므로 첫 4주는 1×5로 두고 지표만 본다 (주 +2.5kg · 사이클 칸은 2주에 한 번)</t>
-    <phoneticPr fontId="32" type="noConversion"/>
-  </si>
-  <si>
     <t>■ 주간 총량 예산 — 늘리려면 먼저 어딘가에서 빼라</t>
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
@@ -3858,6 +3842,32 @@
   </si>
   <si>
     <t>· 재택으로 돌아가면 이 칸들은 무시된다. 재택은 일차 회전을 증량기록 '날짜 (1일차)'로 따라간다.</t>
+  </si>
+  <si>
+    <t>백오프 = 직전 사이클의 톱세트 중량. 이미 들어본 무게라 톱엔드 부하를 안 올리고 노출만 늘린다 — 중량 하나당 5회에서 15회로. [2026-09-13 신설] 데드는 주 1회 1×5로 주 5렙인데 증량은 스쿼트(주 25렙)와 같은 +2.5kg였다. 렙당 증량이 0.5kg 대 0.10kg, 5배다. 5년 공백에서 폼을 다시 배우는 종목을 가장 적은 반복으로 밀고 있었다는 뜻이다. 여기는 기록이 아니라 폼 연습 자리다 — 여유 있게 5회, 매 렙 셋업을 새로 잡는다. 무겁게 느껴지면 톱세트가 과했던 것이다. 다음 근무일 아침 허리가 무거우면 이 행을 1세트로 내리거나 그 주는 건너뛴다 — 톱세트보다 먼저 깎는 자리다.</t>
+  </si>
+  <si>
+    <t>트랩바 데드 (요추 전단력 ↓ — 허리가 애매한 주의 1순위) / 랙풀 (무릎 위에서 시작) / 루마니안 데드 (힌지 연습만)</t>
+  </si>
+  <si>
+    <t>지키는 종목. 허리는 현장 일과 직접 경쟁하므로 첫 4주는 1×5로 두고 지표만 본다 (주 +2.5kg · 사이클 칸은 2주에 한 번) [2026-09-13 — 아래 백오프 2세트 신설. 톱세트 강도는 그대로 두고 반복 노출만 3배로 늘린 것이다. 2×5 스트레이트로 가지 않은 이유는 그쪽이 제일 무거운 중량에서 허리 비용을 두 배로 만들기 때문이다.]</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 첫 4주 규칙은 이제 '톱세트'에만 걸린다 — 톱은 4주간 1×5를 넘기지 않는다. 백오프 2세트는 직전 사이클 중량(이미 들어본 무게)이라 2026-09-13부터 바로 넣는다. 2×5 스트레이트와 달리 제일 무거운 중량의 노출이 안 늘기 때문이다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 4주간 다음 근무일 아침 허리가 깨끗하면 톱을 2×5로 올린다. 그때가 데드가 성장으로 돌아서는 지점이다. 반대로 무거운 주가 오면 톱이 아니라 백오프를 먼저 깎는다 — 2 → 1세트 → 건너뛰기 순서다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>스쿼트 0.2×5 + 스미스 로우 0.2×3 + 오버헤드 슈러그 0.2×3 = 2.2. 직접 3세트(데드 톱 1×5 + 백오프 2×5, 2026-09-13 신설). 낮은 것이 의도다 — 허리는 현장 일과 직접 경쟁하므로 톱세트는 주 1회 1세트가 상한이고, 백오프는 직전 사이클 중량이라 폼 연습으로 센다. 4주간 지표가 깨끗하면 톱을 2×5로 올린다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>백오프 = 톱세트 − 5kg = 직전 사이클의 톱세트 중량. 즉 모든 중량을 두 번 만난다 — 한 사이클은 톱으로 5회, 다음 사이클은 백오프로 10회. 중량 하나당 노출이 5 → 15회다. 여기는 기록이 아니라 폼 연습 자리다. 여유 있게 5회, 매 렙 셋업을 새로 잡을 것 — 무겁게 느껴지면 톱세트가 과했던 것이다. [2026-09-13 정정] 현장 복귀판에도 같은 구조를 넣었다 — 복귀_일_등에 톱 1 + 백오프 2. 복귀에서 상한인 것은 톱세트뿐이고, 백오프는 직전 사이클 중량이라 톱엔드 노출을 안 늘린다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5254,7 +5264,7 @@
     </row>
     <row r="34" spans="1:5" ht="51.75" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="64.5" customHeight="1">
@@ -5269,17 +5279,17 @@
     </row>
     <row r="37" spans="1:5" ht="26.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.25" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5" customHeight="1">
@@ -5563,60 +5573,60 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="C59" s="113">
         <v>46265</v>
       </c>
       <c r="D59" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="C60">
         <v>5</v>
       </c>
       <c r="D60" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
     </row>
   </sheetData>
@@ -5651,7 +5661,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
@@ -5708,7 +5718,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -5872,7 +5882,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>299</v>
@@ -5898,7 +5908,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>306</v>
@@ -6014,7 +6024,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>367</v>
@@ -6052,7 +6062,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>369</v>
@@ -6093,7 +6103,7 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>370</v>
@@ -6118,7 +6128,7 @@
     </row>
     <row r="17" spans="1:6" ht="16.5" customHeight="1">
       <c r="F17" s="87" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" customHeight="1">
@@ -6254,22 +6264,22 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="31" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
@@ -6299,12 +6309,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="116" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B2" s="115"/>
       <c r="C2" s="115"/>
@@ -6316,7 +6326,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$80,"?")</f>
@@ -6325,7 +6335,7 @@
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="114" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B4" s="115"/>
       <c r="C4" s="115"/>
@@ -6337,33 +6347,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="44" t="s">
+        <v>461</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="44" t="s">
         <v>463</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="D6" s="44" t="s">
         <v>464</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="E6" s="44" t="s">
         <v>465</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="F6" s="44" t="s">
         <v>466</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="G6" s="44" t="s">
         <v>467</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="H6" s="44" t="s">
         <v>468</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B7" s="45" t="s">
         <v>236</v>
@@ -6383,15 +6393,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="49" t="s">
+        <v>470</v>
+      </c>
+      <c r="H7" s="50" t="s">
         <v>471</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B8" s="45" t="s">
         <v>242</v>
@@ -6411,15 +6421,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B9" s="45" t="s">
         <v>381</v>
@@ -6439,15 +6449,15 @@
         <v>0.8</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B10" s="45" t="s">
         <v>385</v>
@@ -6467,15 +6477,15 @@
         <v>0.66</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>287</v>
@@ -6495,15 +6505,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B12" s="45" t="s">
         <v>294</v>
@@ -6523,15 +6533,15 @@
         <v>2</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B13" s="45" t="s">
         <v>406</v>
@@ -6551,15 +6561,15 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B14" s="45" t="s">
         <v>418</v>
@@ -6579,15 +6589,15 @@
         <v>1.5</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B15" s="45" t="s">
         <v>298</v>
@@ -6607,15 +6617,15 @@
         <v>1.5</v>
       </c>
       <c r="G15" s="49" t="s">
+        <v>482</v>
+      </c>
+      <c r="H15" s="50" t="s">
         <v>483</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B16" s="45" t="s">
         <v>43</v>
@@ -6635,15 +6645,15 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B17" s="45" t="s">
         <v>392</v>
@@ -6663,15 +6673,15 @@
         <v>1.32</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B18" s="45" t="s">
         <v>394</v>
@@ -6691,15 +6701,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B19" s="45" t="s">
         <v>287</v>
@@ -6719,15 +6729,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>298</v>
@@ -6747,15 +6757,15 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H20" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B21" s="45" t="s">
         <v>418</v>
@@ -6775,15 +6785,15 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B22" s="45" t="s">
         <v>406</v>
@@ -6803,15 +6813,15 @@
         <v>0.99</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H22" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B23" s="45" t="s">
         <v>26</v>
@@ -6831,15 +6841,15 @@
         <v>0.99</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B24" s="45" t="s">
         <v>26</v>
@@ -6859,15 +6869,15 @@
         <v>0.99</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H24" s="50" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B25" s="45" t="s">
         <v>251</v>
@@ -6887,15 +6897,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B26" s="45" t="s">
         <v>33</v>
@@ -6915,15 +6925,15 @@
         <v>1.5</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B27" s="45" t="s">
         <v>33</v>
@@ -6943,15 +6953,15 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B28" s="45" t="s">
         <v>381</v>
@@ -6971,15 +6981,15 @@
         <v>2</v>
       </c>
       <c r="G28" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B29" s="45" t="s">
         <v>385</v>
@@ -6999,15 +7009,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B30" s="45" t="s">
         <v>350</v>
@@ -7027,18 +7037,18 @@
         <v>0</v>
       </c>
       <c r="G30" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C31" s="45" t="s">
         <v>330</v>
@@ -7055,15 +7065,15 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B32" s="45" t="s">
         <v>440</v>
@@ -7083,15 +7093,15 @@
         <v>0.33</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>270</v>
@@ -7111,15 +7121,15 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B34" s="45" t="s">
         <v>314</v>
@@ -7139,15 +7149,15 @@
         <v>2.5</v>
       </c>
       <c r="G34" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B35" s="45" t="s">
         <v>320</v>
@@ -7167,15 +7177,15 @@
         <v>0.99</v>
       </c>
       <c r="G35" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B36" s="45" t="s">
         <v>440</v>
@@ -7195,18 +7205,18 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C37" s="45" t="s">
         <v>321</v>
@@ -7223,15 +7233,15 @@
         <v>1.5</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>270</v>
@@ -7251,15 +7261,15 @@
         <v>1.5</v>
       </c>
       <c r="G38" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B39" s="45" t="s">
         <v>314</v>
@@ -7279,15 +7289,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B40" s="45" t="s">
         <v>394</v>
@@ -7307,18 +7317,18 @@
         <v>0</v>
       </c>
       <c r="G40" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C41" s="45" t="s">
         <v>271</v>
@@ -7335,15 +7345,15 @@
         <v>1.5</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B42" s="45" t="s">
         <v>324</v>
@@ -7363,15 +7373,15 @@
         <v>1.5</v>
       </c>
       <c r="G42" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H42" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B43" s="45" t="s">
         <v>324</v>
@@ -7391,15 +7401,15 @@
         <v>0.99</v>
       </c>
       <c r="G43" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B44" s="45" t="s">
         <v>440</v>
@@ -7419,15 +7429,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B45" s="45" t="s">
         <v>314</v>
@@ -7447,15 +7457,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G45" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B46" s="45" t="s">
         <v>320</v>
@@ -7475,15 +7485,15 @@
         <v>0.99</v>
       </c>
       <c r="G46" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="45" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B47" s="45" t="s">
         <v>324</v>
@@ -7503,15 +7513,15 @@
         <v>0.99</v>
       </c>
       <c r="G47" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B48" s="45" t="s">
         <v>287</v>
@@ -7531,15 +7541,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B49" s="45" t="s">
         <v>418</v>
@@ -7559,15 +7569,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B50" s="45" t="s">
         <v>381</v>
@@ -7587,15 +7597,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B51" s="45" t="s">
         <v>406</v>
@@ -7615,15 +7625,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B52" s="45" t="s">
         <v>440</v>
@@ -7643,15 +7653,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H52" s="50" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B53" s="45" t="s">
         <v>236</v>
@@ -7671,15 +7681,15 @@
         <v>0.8</v>
       </c>
       <c r="G53" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="45" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B54" s="45" t="s">
         <v>381</v>
@@ -7699,15 +7709,15 @@
         <v>0.8</v>
       </c>
       <c r="G54" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B55" s="45" t="s">
         <v>309</v>
@@ -7727,15 +7737,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G55" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B56" s="45" t="s">
         <v>320</v>
@@ -7755,15 +7765,15 @@
         <v>0.99</v>
       </c>
       <c r="G56" s="52" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B57" s="45" t="s">
         <v>320</v>
@@ -7783,15 +7793,15 @@
         <v>0.99</v>
       </c>
       <c r="G57" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B58" s="45" t="s">
         <v>26</v>
@@ -7811,15 +7821,15 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H58" s="50" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B59" s="45" t="s">
         <v>26</v>
@@ -7839,15 +7849,15 @@
         <v>1.5</v>
       </c>
       <c r="G59" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B60" s="45" t="s">
         <v>415</v>
@@ -7867,15 +7877,15 @@
         <v>1.5</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B61" s="45" t="s">
         <v>294</v>
@@ -7895,15 +7905,15 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B62" s="45" t="s">
         <v>415</v>
@@ -7923,15 +7933,15 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H62" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="45" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B63" s="45" t="s">
         <v>51</v>
@@ -7951,15 +7961,15 @@
         <v>0.8</v>
       </c>
       <c r="G63" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B64" s="45" t="s">
         <v>350</v>
@@ -7979,15 +7989,15 @@
         <v>0.99</v>
       </c>
       <c r="G64" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B65" s="45" t="s">
         <v>346</v>
@@ -8007,15 +8017,15 @@
         <v>0.99</v>
       </c>
       <c r="G65" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B66" s="45" t="s">
         <v>354</v>
@@ -8035,15 +8045,15 @@
         <v>0.99</v>
       </c>
       <c r="G66" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" s="45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B67" s="45" t="s">
         <v>255</v>
@@ -8063,15 +8073,15 @@
         <v>0.99</v>
       </c>
       <c r="G67" s="52" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15" customHeight="1">
       <c r="A68" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B68" s="45" t="s">
         <v>444</v>
@@ -8091,15 +8101,15 @@
         <v>0.66</v>
       </c>
       <c r="G68" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B69" s="45" t="s">
         <v>444</v>
@@ -8119,15 +8129,15 @@
         <v>1</v>
       </c>
       <c r="G69" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B70" s="45" t="s">
         <v>444</v>
@@ -8147,15 +8157,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s">
         <v>244</v>
@@ -8175,15 +8185,15 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H71" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s">
         <v>244</v>
@@ -8203,18 +8213,18 @@
         <v>0.8</v>
       </c>
       <c r="G72" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H72" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C73" t="s">
         <v>44</v>
@@ -8231,18 +8241,18 @@
         <v>0.66</v>
       </c>
       <c r="G73" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H73" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C74" t="s">
         <v>44</v>
@@ -8259,18 +8269,18 @@
         <v>0.66</v>
       </c>
       <c r="G74" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H74" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B75" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C75" t="s">
         <v>245</v>
@@ -8287,10 +8297,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H75" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>
@@ -8319,30 +8329,30 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G1" s="93" t="s">
         <v>545</v>
-      </c>
-      <c r="G1" s="93" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="G2" s="94" t="s">
         <v>547</v>
-      </c>
-      <c r="G2" s="94" t="s">
-        <v>548</v>
       </c>
       <c r="H2" s="95">
         <v>10</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J2" s="95">
         <v>244</v>
       </c>
       <c r="K2" s="94" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L2" s="96">
         <f>B25</f>
@@ -8355,21 +8365,21 @@
         <v/>
       </c>
       <c r="G3" s="94" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H3" s="98">
         <f>$J$2-$L$2</f>
         <v>4</v>
       </c>
       <c r="I3" s="94" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J3" s="98">
         <f>ROUND($L$2*7/$H$2,1)</f>
         <v>168</v>
       </c>
       <c r="K3" s="94" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L3" s="98" t="str">
         <f>IF($H$3&lt;0,"INVALID","VALID")</f>
@@ -8381,19 +8391,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>557</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>558</v>
       </c>
       <c r="J4" s="99" t="str">
         <f>"주당 환산 (×7/"&amp;$H$2&amp;")"</f>
@@ -8421,10 +8431,10 @@
         <v>유지</v>
       </c>
       <c r="F5" s="53" t="s">
+        <v>558</v>
+      </c>
+      <c r="G5" s="117" t="s">
         <v>559</v>
-      </c>
-      <c r="G5" s="117" t="s">
-        <v>560</v>
       </c>
       <c r="H5" s="56">
         <f ca="1">SUM(D5:D6)</f>
@@ -8464,7 +8474,7 @@
         <v>성장</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G6" s="118"/>
       <c r="J6" s="55">
@@ -8497,10 +8507,10 @@
         <v>성장</v>
       </c>
       <c r="F7" s="53" t="s">
+        <v>561</v>
+      </c>
+      <c r="G7" s="117" t="s">
         <v>562</v>
-      </c>
-      <c r="G7" s="117" t="s">
-        <v>563</v>
       </c>
       <c r="H7" s="56">
         <f ca="1">SUM(D7:D10)</f>
@@ -8536,7 +8546,7 @@
         <v>유지 미만</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G8" s="118"/>
       <c r="J8" s="55">
@@ -8569,7 +8579,7 @@
         <v>유지</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G9" s="118"/>
       <c r="J9" s="55">
@@ -8602,7 +8612,7 @@
         <v>성장</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G10" s="118"/>
       <c r="J10" s="55">
@@ -8635,7 +8645,7 @@
         <v>유지</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G11" s="57"/>
       <c r="J11" s="55">
@@ -8668,7 +8678,7 @@
         <v>성장</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G12" s="57"/>
       <c r="J12" s="55">
@@ -8701,7 +8711,7 @@
         <v>성장</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G13" s="57"/>
       <c r="J13" s="55">
@@ -8734,7 +8744,7 @@
         <v>성장</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="56"/>
@@ -8771,7 +8781,7 @@
         <v>324</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H15" s="56">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -8807,7 +8817,7 @@
         <v>유지</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G16" s="57"/>
       <c r="J16" s="55">
@@ -8840,7 +8850,7 @@
         <v>성장</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G17" s="117" t="s">
         <v>321</v>
@@ -8879,7 +8889,7 @@
         <v>유지</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G18" s="118"/>
       <c r="J18" s="55">
@@ -8912,7 +8922,7 @@
         <v>유지</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G19" s="57"/>
       <c r="J19" s="55">
@@ -8945,7 +8955,7 @@
         <v>성장</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G20" s="57"/>
       <c r="J20" s="55">
@@ -8978,7 +8988,7 @@
         <v>성장</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G21" s="57"/>
       <c r="J21" s="55">
@@ -9011,7 +9021,7 @@
         <v>성장</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G22" s="57"/>
       <c r="J22" s="55">
@@ -9044,7 +9054,7 @@
         <v>유지</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G23" s="57"/>
       <c r="J23" s="55">
@@ -9077,7 +9087,7 @@
         <v>유지</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G24" s="57"/>
       <c r="J24" s="55">
@@ -9091,7 +9101,7 @@
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
@@ -9115,22 +9125,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="48" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="48" customHeight="1">
@@ -9138,22 +9148,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
@@ -9161,124 +9171,124 @@
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="77.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="39" customHeight="1">
       <c r="A39" s="63" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="48" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48" customHeight="1">
       <c r="A44" s="90" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51.75" customHeight="1">
       <c r="A45" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="90" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="48" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="93" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="100" t="s">
+        <v>609</v>
+      </c>
+      <c r="B58" s="100" t="s">
         <v>610</v>
       </c>
-      <c r="B58" s="100" t="s">
+      <c r="C58" s="100" t="s">
         <v>611</v>
       </c>
-      <c r="C58" s="100" t="s">
+      <c r="D58" s="100" t="s">
         <v>612</v>
       </c>
-      <c r="D58" s="100" t="s">
+      <c r="E58" s="100" t="s">
         <v>613</v>
-      </c>
-      <c r="E58" s="100" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -9292,7 +9302,7 @@
         <v>239</v>
       </c>
       <c r="D59" s="102" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E59" s="102" t="s">
         <v>149</v>
@@ -9309,10 +9319,10 @@
         <v>239</v>
       </c>
       <c r="D60" s="107" t="s">
+        <v>615</v>
+      </c>
+      <c r="E60" s="107" t="s">
         <v>616</v>
-      </c>
-      <c r="E60" s="107" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -9326,45 +9336,45 @@
         <v>244</v>
       </c>
       <c r="D61" s="111" t="s">
+        <v>617</v>
+      </c>
+      <c r="E61" s="111" t="s">
         <v>618</v>
-      </c>
-      <c r="E61" s="111" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="104" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -9414,50 +9424,50 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="64" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -9466,13 +9476,13 @@
     </row>
     <row r="8" spans="1:13" ht="84" customHeight="1">
       <c r="A8" s="64" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9480,40 +9490,40 @@
         <v>127</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>641</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L9" s="100" t="s">
+        <v>641</v>
+      </c>
+      <c r="M9" s="100" t="s">
         <v>642</v>
-      </c>
-      <c r="M9" s="100" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9662,7 +9672,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="65" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="L14" s="103"/>
       <c r="M14" s="103"/>
@@ -9872,17 +9882,17 @@
     </row>
     <row r="23" spans="1:13" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="120" customHeight="1">
@@ -9890,52 +9900,52 @@
     </row>
     <row r="27" spans="1:13" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -9956,45 +9966,45 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>660</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="C5" s="53" t="s">
         <v>662</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>664</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>662</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -10002,80 +10012,80 @@
         <v>271</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="C7" s="53" t="s">
         <v>666</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="67" t="s">
+        <v>667</v>
+      </c>
+      <c r="B8" s="67" t="s">
         <v>668</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="C8" s="68" t="s">
         <v>669</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="67" t="s">
+        <v>670</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>668</v>
+      </c>
+      <c r="C9" s="68" t="s">
         <v>671</v>
-      </c>
-      <c r="B9" s="67" t="s">
-        <v>669</v>
-      </c>
-      <c r="C9" s="68" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="69" t="s">
         <v>674</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="53" t="s">
         <v>677</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="53" t="s">
         <v>680</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -10083,47 +10093,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -10149,31 +10159,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="70" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>699</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>700</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>7</v>
@@ -10182,111 +10192,111 @@
         <v>147</v>
       </c>
       <c r="G5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="71" t="s">
+        <v>701</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>702</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="C6" s="72" t="s">
         <v>703</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="D6" s="71" t="s">
         <v>704</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>705</v>
       </c>
       <c r="E6" s="71">
         <f>복귀_평일A_가슴!$E$27</f>
         <v>28</v>
       </c>
       <c r="F6" s="73" t="s">
+        <v>705</v>
+      </c>
+      <c r="G6" t="s">
         <v>706</v>
-      </c>
-      <c r="G6" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="D7" s="67" t="s">
         <v>708</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>709</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$21</f>
         <v>35</v>
       </c>
       <c r="F7" s="69" t="s">
+        <v>709</v>
+      </c>
+      <c r="G7" t="s">
         <v>710</v>
-      </c>
-      <c r="G7" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
+        <v>711</v>
+      </c>
+      <c r="B8" s="72" t="s">
         <v>712</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="C8" s="72" t="s">
+        <v>698</v>
+      </c>
+      <c r="D8" s="71" t="s">
         <v>713</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>699</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>714</v>
       </c>
       <c r="E8" s="71">
         <f>복귀_토_하체!$E$34</f>
         <v>37</v>
       </c>
       <c r="F8" s="73" t="s">
+        <v>714</v>
+      </c>
+      <c r="G8" t="s">
         <v>715</v>
-      </c>
-      <c r="G8" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
+        <v>716</v>
+      </c>
+      <c r="B9" s="72" t="s">
         <v>717</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="C9" s="72" t="s">
+        <v>698</v>
+      </c>
+      <c r="D9" s="71" t="s">
         <v>718</v>
       </c>
-      <c r="C9" s="72" t="s">
-        <v>699</v>
-      </c>
-      <c r="D9" s="71" t="s">
+      <c r="E9" s="71">
+        <f>복귀_일_등!$E$27</f>
+        <v>35</v>
+      </c>
+      <c r="F9" s="73" t="s">
         <v>719</v>
       </c>
-      <c r="E9" s="71">
-        <f>복귀_일_등!$E$26</f>
-        <v>33</v>
-      </c>
-      <c r="F9" s="73" t="s">
+      <c r="G9" t="s">
         <v>720</v>
-      </c>
-      <c r="G9" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="71" t="s">
+        <v>721</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>722</v>
-      </c>
-      <c r="B10" s="72" t="s">
-        <v>723</v>
       </c>
       <c r="C10" s="72" t="s">
         <v>149</v>
@@ -10301,7 +10311,7 @@
         <v>149</v>
       </c>
       <c r="G10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -10313,10 +10323,10 @@
       <c r="D11" s="67"/>
       <c r="E11" s="7">
         <f>SUM(E6:E10)</f>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -10337,32 +10347,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -10370,22 +10380,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -10393,32 +10403,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -10426,47 +10436,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="74" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -10476,27 +10486,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -10527,28 +10537,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="19" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10613,23 +10623,23 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="31" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="19" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -10694,7 +10704,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="31" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -10743,7 +10753,7 @@
         <v>16</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="29.25" customHeight="1">
@@ -10777,10 +10787,10 @@
         <v>17.5</v>
       </c>
       <c r="J24" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="K24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L24" s="68" t="s">
         <v>293</v>
@@ -10791,7 +10801,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C25" s="67" t="s">
         <v>27</v>
@@ -10817,10 +10827,10 @@
         <v>10.5</v>
       </c>
       <c r="J25" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="K25" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L25" s="68" t="s">
         <v>409</v>
@@ -10856,10 +10866,10 @@
         <v>13</v>
       </c>
       <c r="J26" t="s">
+        <v>759</v>
+      </c>
+      <c r="K26" t="s">
         <v>760</v>
-      </c>
-      <c r="K26" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
@@ -10867,7 +10877,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>315</v>
@@ -10892,10 +10902,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J27" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="K27" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N27">
         <v>75</v>
@@ -10906,7 +10916,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>330</v>
@@ -10931,10 +10941,10 @@
         <v>9</v>
       </c>
       <c r="J28" t="s">
+        <v>762</v>
+      </c>
+      <c r="K28" t="s">
         <v>763</v>
-      </c>
-      <c r="K28" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
@@ -10948,7 +10958,7 @@
         <v>333</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E29" s="7">
         <v>4</v>
@@ -10967,10 +10977,10 @@
         <v>3.3</v>
       </c>
       <c r="J29" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="K29" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M29" t="s">
         <v>336</v>
@@ -11006,7 +11016,7 @@
         <v>13.3</v>
       </c>
       <c r="J30" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="K30" t="s">
         <v>339</v>
@@ -11045,10 +11055,10 @@
         <v>5.8</v>
       </c>
       <c r="J31" t="s">
+        <v>766</v>
+      </c>
+      <c r="K31" t="s">
         <v>767</v>
-      </c>
-      <c r="K31" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
@@ -11056,13 +11066,13 @@
         <v>9</v>
       </c>
       <c r="B32" s="87" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="76" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E32" s="28">
         <v>3</v>
@@ -11081,10 +11091,10 @@
         <v>6</v>
       </c>
       <c r="J32" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="K32" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="N32">
         <v>60</v>
@@ -11120,10 +11130,10 @@
         <v>7.7</v>
       </c>
       <c r="J33" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="K33" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="N33">
         <v>60</v>
@@ -11149,97 +11159,97 @@
     </row>
     <row r="36" spans="1:14" ht="293.25" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="276" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="C58" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -11251,7 +11261,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11270,28 +11280,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="19" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -11356,7 +11366,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="31" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -11405,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="29.25" customHeight="1">
@@ -11435,53 +11445,51 @@
         <v>180</v>
       </c>
       <c r="I15">
-        <f t="shared" ref="I15:I25" si="0">IF(E15=0,0,ROUND((E15*(G15+H15)+N15)/60,1))</f>
+        <f t="shared" ref="I15:I26" si="0">IF(E15=0,0,ROUND((E15*(G15+H15)+N15)/60,1))</f>
         <v>3.5</v>
       </c>
       <c r="J15" t="s">
-        <v>1179</v>
+        <v>1218</v>
       </c>
       <c r="K15" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1">
-      <c r="A16" s="7">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A16" s="67">
         <v>2</v>
       </c>
-      <c r="B16" s="89" t="s">
-        <v>789</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>790</v>
-      </c>
-      <c r="E16" s="7">
-        <v>4</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G16" s="53">
-        <v>40</v>
-      </c>
-      <c r="H16" s="53">
+      <c r="B16" s="68" t="s">
+        <v>444</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" s="78">
+        <f>INDEX(증량기록!$E$10:$E$21,MAX(1,시작중량_설정!$C$4-1))</f>
+        <v>62</v>
+      </c>
+      <c r="E16" s="67">
+        <v>2</v>
+      </c>
+      <c r="F16" s="59">
+        <v>5</v>
+      </c>
+      <c r="G16" s="68">
+        <v>30</v>
+      </c>
+      <c r="H16" s="68">
         <v>150</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
-        <v>12.7</v>
+        <f>IF(E16=0,0,ROUND((E16*(G16+H16)+N16)/60,1))</f>
+        <v>6</v>
       </c>
       <c r="J16" t="s">
-        <v>791</v>
+        <v>1216</v>
       </c>
       <c r="K16" t="s">
-        <v>792</v>
-      </c>
-      <c r="L16" s="53" t="s">
-        <v>793</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1">
@@ -11489,19 +11497,19 @@
         <v>3</v>
       </c>
       <c r="B17" s="89" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>149</v>
+        <v>245</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>789</v>
       </c>
       <c r="E17" s="7">
         <v>4</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="G17" s="53">
         <v>40</v>
@@ -11511,108 +11519,108 @@
       </c>
       <c r="I17">
         <f t="shared" si="0"/>
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="J17" t="s">
-        <v>1169</v>
+        <v>790</v>
       </c>
       <c r="K17" t="s">
-        <v>795</v>
-      </c>
-      <c r="N17">
-        <v>60</v>
+        <v>791</v>
+      </c>
+      <c r="L17" s="53" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">
       <c r="A18" s="7">
         <v>4</v>
       </c>
-      <c r="B18" s="53" t="s">
-        <v>236</v>
+      <c r="B18" s="89" t="s">
+        <v>793</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>237</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>246</v>
+        <v>149</v>
       </c>
       <c r="E18" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>238</v>
+        <v>40</v>
       </c>
       <c r="G18" s="53">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H18" s="53">
         <v>150</v>
       </c>
       <c r="I18">
         <f t="shared" si="0"/>
-        <v>9.3000000000000007</v>
+        <v>13.7</v>
       </c>
       <c r="J18" t="s">
-        <v>796</v>
+        <v>1165</v>
       </c>
       <c r="K18" t="s">
-        <v>797</v>
-      </c>
-      <c r="L18" s="53" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="29.25" customHeight="1">
+        <v>794</v>
+      </c>
+      <c r="N18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1">
       <c r="A19" s="7">
         <v>5</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>387</v>
+        <v>236</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>799</v>
+        <v>237</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="E19" s="7">
         <v>3</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="G19" s="53">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H19" s="53">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="I19">
         <f t="shared" si="0"/>
-        <v>6.8</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J19" t="s">
-        <v>1162</v>
+        <v>795</v>
       </c>
       <c r="K19" t="s">
-        <v>800</v>
-      </c>
-      <c r="N19">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1">
+        <v>796</v>
+      </c>
+      <c r="L19" s="53" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="29.25" customHeight="1">
       <c r="A20" s="7">
         <v>6</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>34</v>
+        <v>245</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>770</v>
+        <v>798</v>
       </c>
       <c r="E20" s="7">
         <v>3</v>
@@ -11628,13 +11636,16 @@
       </c>
       <c r="I20">
         <f t="shared" si="0"/>
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="s">
-        <v>801</v>
+        <v>1158</v>
       </c>
       <c r="K20" t="s">
-        <v>802</v>
+        <v>799</v>
+      </c>
+      <c r="N20">
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1">
@@ -11642,38 +11653,35 @@
         <v>7</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>294</v>
+        <v>398</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>246</v>
+        <v>769</v>
       </c>
       <c r="E21" s="7">
         <v>3</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G21" s="53">
         <v>40</v>
       </c>
       <c r="H21" s="53">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="I21">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="J21" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="K21" t="s">
-        <v>804</v>
-      </c>
-      <c r="L21" s="53" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
@@ -11681,127 +11689,130 @@
         <v>8</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>357</v>
+        <v>294</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>52</v>
+      <c r="D22" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="E22" s="7">
         <v>3</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>19</v>
+      <c r="F22" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="G22" s="53">
         <v>40</v>
       </c>
       <c r="H22" s="53">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
-        <v>8.3000000000000007</v>
+        <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>1163</v>
+        <v>802</v>
       </c>
       <c r="K22" t="s">
-        <v>806</v>
-      </c>
-      <c r="N22">
-        <v>60</v>
+        <v>803</v>
+      </c>
+      <c r="L22" s="53" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1">
-      <c r="A23">
+      <c r="A23" s="7">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>392</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="76" t="s">
-        <v>363</v>
-      </c>
-      <c r="E23" s="28">
+      <c r="B23" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="7">
         <v>3</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="53">
         <v>40</v>
       </c>
-      <c r="G23">
-        <v>40</v>
-      </c>
-      <c r="H23">
-        <v>75</v>
+      <c r="H23" s="53">
+        <v>105</v>
       </c>
       <c r="I23">
         <f t="shared" si="0"/>
-        <v>6.8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J23" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="K23" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="N23">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" ht="15" customHeight="1">
       <c r="A24">
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>808</v>
+        <v>392</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24">
-        <v>12</v>
-      </c>
-      <c r="E24">
+        <v>44</v>
+      </c>
+      <c r="D24" s="76" t="s">
+        <v>363</v>
+      </c>
+      <c r="E24" s="28">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G24">
         <v>40</v>
       </c>
       <c r="H24">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I24">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="s">
-        <v>809</v>
+        <v>1160</v>
       </c>
       <c r="K24" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A25" s="12">
+        <v>806</v>
+      </c>
+      <c r="N24">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25">
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>366</v>
+        <v>807</v>
       </c>
       <c r="C25" t="s">
         <v>45</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -11820,158 +11831,194 @@
         <v>5</v>
       </c>
       <c r="J25" t="s">
+        <v>808</v>
+      </c>
+      <c r="K25" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="17.25" customHeight="1">
+      <c r="A26" s="12">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>366</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26">
+        <v>40</v>
+      </c>
+      <c r="H26">
+        <v>60</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J26" t="s">
+        <v>810</v>
+      </c>
+      <c r="K26" t="s">
         <v>811</v>
       </c>
-      <c r="K25" t="s">
+    </row>
+    <row r="27" spans="1:14" ht="23.25" customHeight="1">
+      <c r="A27" s="11"/>
+      <c r="C27" s="88"/>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27">
+        <f>SUM(E15:E26)</f>
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <f>ROUND(SUM(I15:I26),0)</f>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="240" customHeight="1">
+      <c r="A28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" ht="278.25" customHeight="1">
+      <c r="A29" s="11" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A26" s="11"/>
-      <c r="C26" s="88"/>
-      <c r="D26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26">
-        <f>SUM(E15:E25)</f>
-        <v>33</v>
-      </c>
-      <c r="I26">
-        <f>ROUND(SUM(I15:I25),0)</f>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="240" customHeight="1">
-      <c r="A27" s="11"/>
-    </row>
-    <row r="28" spans="1:14" ht="278.25" customHeight="1">
-      <c r="A28" s="11" t="s">
+    <row r="30" spans="1:14" ht="15" customHeight="1">
+      <c r="A30" s="63" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="95.25" customHeight="1">
+      <c r="A31" s="12" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="252.75" customHeight="1">
+      <c r="A32" s="11" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1">
-      <c r="A29" s="63" t="s">
+    <row r="33" spans="1:1" ht="237.75" customHeight="1">
+      <c r="A33" s="11" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="95.25" customHeight="1">
-      <c r="A30" s="12" t="s">
+    <row r="34" spans="1:1" ht="265.5" customHeight="1">
+      <c r="A34" s="11" t="s">
         <v>815</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="252.75" customHeight="1">
-      <c r="A31" s="11" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="237.75" customHeight="1">
-      <c r="A32" s="11" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="265.5" customHeight="1">
-      <c r="A33" s="11" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>824</v>
+        <v>819</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>830</v>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>1150</v>
+        <v>829</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1170</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="C58" t="s">
-        <v>834</v>
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="C59" t="s">
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -12002,32 +12049,32 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="31" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="31" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="31" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -12076,7 +12123,7 @@
         <v>16</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
@@ -12109,7 +12156,7 @@
         <v>10.7</v>
       </c>
       <c r="J11" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="K11" t="s">
         <v>32</v>
@@ -12145,10 +12192,10 @@
         <v>7.7</v>
       </c>
       <c r="J12" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="K12" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="N12">
         <v>60</v>
@@ -12159,13 +12206,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E13" s="7">
         <v>4</v>
@@ -12184,10 +12231,10 @@
         <v>8</v>
       </c>
       <c r="J13" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="K13" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -12220,10 +12267,10 @@
         <v>6.7</v>
       </c>
       <c r="J14" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="K14" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -12237,7 +12284,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E15" s="7">
         <v>3</v>
@@ -12256,10 +12303,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="K15" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -12292,10 +12339,10 @@
         <v>5.8</v>
       </c>
       <c r="J16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="K16" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1">
@@ -12303,13 +12350,13 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C17" t="s">
         <v>321</v>
       </c>
       <c r="D17" s="76" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E17" s="28">
         <v>3</v>
@@ -12328,10 +12375,10 @@
         <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="K17" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -12364,10 +12411,10 @@
         <v>6.8</v>
       </c>
       <c r="J18" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="K18" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1">
@@ -12400,10 +12447,10 @@
         <v>11.9</v>
       </c>
       <c r="J19" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="K19" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N19">
         <v>75</v>
@@ -12439,10 +12486,10 @@
         <v>5</v>
       </c>
       <c r="J20" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="K20" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="25.5" customHeight="1">
@@ -12461,97 +12508,97 @@
     </row>
     <row r="22" spans="1:14" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -12582,28 +12629,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="19" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -12668,7 +12715,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="31" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -12737,7 +12784,7 @@
         <v>16</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1">
@@ -12771,10 +12818,10 @@
         <v>17.5</v>
       </c>
       <c r="J20" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="K20" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="L20" s="68" t="s">
         <v>293</v>
@@ -12791,7 +12838,7 @@
         <v>299</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E21" s="7">
         <v>5</v>
@@ -12810,10 +12857,10 @@
         <v>15.8</v>
       </c>
       <c r="J21" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="K21" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
@@ -12821,7 +12868,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>299</v>
@@ -12846,10 +12893,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J22" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="K22" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1">
@@ -12882,10 +12929,10 @@
         <v>12.7</v>
       </c>
       <c r="J23" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="K23" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1">
@@ -12893,7 +12940,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="89" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>237</v>
@@ -12918,10 +12965,10 @@
         <v>11.7</v>
       </c>
       <c r="J24" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="K24" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="N24">
         <v>60</v>
@@ -12957,10 +13004,10 @@
         <v>5.8</v>
       </c>
       <c r="J25" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="K25" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
@@ -12993,10 +13040,10 @@
         <v>6.5</v>
       </c>
       <c r="J26" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="K26" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="N26">
         <v>60</v>
@@ -13031,77 +13078,77 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="C53" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>
@@ -13185,7 +13232,7 @@
         <v>152</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="E6" s="20">
         <f>INDEX(D2_밀기A!$E:$E,MATCH("세트 합계",D2_밀기A!$D:$D,0))</f>
@@ -13229,7 +13276,7 @@
         <v>149</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="E8" s="20">
         <f>INDEX(D4_어깨팔A!$E:$E,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))</f>
@@ -13271,7 +13318,7 @@
         <v>149</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="E10" s="20">
         <f>INDEX(D6_당기기B!$E:$E,MATCH("세트 합계",D6_당기기B!$D:$D,0))</f>
@@ -13293,7 +13340,7 @@
         <v>160</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="E11" s="20">
         <f>INDEX(D7_밀기B!$E:$E,MATCH("세트 합계",D7_밀기B!$D:$D,0))</f>
@@ -13337,7 +13384,7 @@
         <v>149</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="E13" s="20">
         <f>INDEX(D9_어깨팔B!$E:$E,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))</f>
@@ -13475,32 +13522,32 @@
     </row>
     <row r="35" spans="1:1" ht="90" customHeight="1">
       <c r="A35" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="90" customHeight="1">
       <c r="A36" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="90" customHeight="1">
       <c r="A37" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="90" customHeight="1">
       <c r="A38" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="90" customHeight="1">
       <c r="A39" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="90" customHeight="1">
       <c r="A40" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="51.75" customHeight="1">
@@ -13767,22 +13814,22 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -13804,166 +13851,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="D5" s="69" t="s">
         <v>894</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>895</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>896</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D7" s="53" t="s">
         <v>901</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>902</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="D8" s="53" t="s">
         <v>905</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>906</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="D10" s="53" t="s">
         <v>911</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>912</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>913</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>149</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="D12" s="53" t="s">
         <v>918</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>919</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>920</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="79" t="s">
+        <v>919</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>920</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>921</v>
+      </c>
+      <c r="D13" s="79" t="s">
         <v>922</v>
-      </c>
-      <c r="B13" s="80" t="s">
-        <v>923</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>924</v>
-      </c>
-      <c r="D13" s="79" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>923</v>
+      </c>
+      <c r="B14" t="s">
+        <v>924</v>
+      </c>
+      <c r="C14" t="s">
+        <v>925</v>
+      </c>
+      <c r="D14" t="s">
         <v>926</v>
-      </c>
-      <c r="B14" t="s">
-        <v>927</v>
-      </c>
-      <c r="C14" t="s">
-        <v>928</v>
-      </c>
-      <c r="D14" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -13971,37 +14018,37 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="39" customHeight="1">
@@ -14009,22 +14056,22 @@
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="39" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="51.75" customHeight="1">
@@ -14032,137 +14079,137 @@
     </row>
     <row r="29" spans="1:1" ht="39" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" customHeight="1">
       <c r="A30" s="63" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="51.75" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="39" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -14188,17 +14235,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -14207,38 +14254,38 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C6" t="s">
         <v>463</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>464</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>465</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>466</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>467</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>468</v>
-      </c>
-      <c r="H6" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B7" t="s">
         <v>381</v>
@@ -14258,18 +14305,18 @@
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H7" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B8" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -14286,18 +14333,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H8" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -14314,18 +14361,18 @@
         <v>0.8</v>
       </c>
       <c r="G9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H9" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -14342,15 +14389,15 @@
         <v>1.32</v>
       </c>
       <c r="G10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H10" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B11" t="s">
         <v>236</v>
@@ -14370,15 +14417,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H11" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -14398,15 +14445,15 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H12" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B13" t="s">
         <v>418</v>
@@ -14426,15 +14473,15 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H13" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -14454,18 +14501,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H15" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B16" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -14482,15 +14529,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H16" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B17" t="s">
         <v>294</v>
@@ -14510,15 +14557,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H17" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B18" t="s">
         <v>103</v>
@@ -14538,15 +14585,15 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H18" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B19" t="s">
         <v>418</v>
@@ -14566,15 +14613,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H19" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B20" t="s">
         <v>294</v>
@@ -14594,18 +14641,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H20" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B21" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -14622,15 +14669,15 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H21" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B22" t="s">
         <v>381</v>
@@ -14650,18 +14697,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H22" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B23" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C23" t="s">
         <v>237</v>
@@ -14678,18 +14725,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H23" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B24" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C24" t="s">
         <v>245</v>
@@ -14706,15 +14753,15 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H24" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B25" t="s">
         <v>350</v>
@@ -14734,15 +14781,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H25" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B26" t="s">
         <v>421</v>
@@ -14762,18 +14809,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H26" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B27" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C27" t="s">
         <v>245</v>
@@ -14790,18 +14837,18 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H27" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B28" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C28" t="s">
         <v>347</v>
@@ -14818,18 +14865,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H28" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B29" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C29" t="s">
         <v>347</v>
@@ -14846,15 +14893,15 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H29" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -14874,15 +14921,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H30" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B31" t="s">
         <v>236</v>
@@ -14902,18 +14949,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H31" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B32" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
@@ -14930,15 +14977,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H32" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B33" t="s">
         <v>99</v>
@@ -14958,18 +15005,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H33" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B34" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C34" t="s">
         <v>271</v>
@@ -14986,15 +15033,15 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H34" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B35" t="s">
         <v>398</v>
@@ -15014,15 +15061,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H35" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B36" t="s">
         <v>99</v>
@@ -15042,15 +15089,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B37" t="s">
         <v>101</v>
@@ -15070,15 +15117,15 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H37" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B38" t="s">
         <v>320</v>
@@ -15098,18 +15145,18 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H38" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B39" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C39" t="s">
         <v>330</v>
@@ -15126,15 +15173,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H39" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B40" t="s">
         <v>101</v>
@@ -15154,15 +15201,15 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H40" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B41" t="s">
         <v>99</v>
@@ -15182,15 +15229,15 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H41" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B42" t="s">
         <v>320</v>
@@ -15210,15 +15257,15 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H42" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -15238,15 +15285,15 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H43" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B44" t="s">
         <v>392</v>
@@ -15266,15 +15313,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H44" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -15294,15 +15341,15 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H45" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B46" t="s">
         <v>418</v>
@@ -15322,15 +15369,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H46" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B47" t="s">
         <v>101</v>
@@ -15350,15 +15397,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H47" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -15378,15 +15425,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H48" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -15406,18 +15453,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H49" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B50" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C50" t="s">
         <v>288</v>
@@ -15434,18 +15481,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H50" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B51" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -15462,10 +15509,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H51" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
     </row>
   </sheetData>
@@ -15491,34 +15538,34 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="G2" s="94" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2" s="95">
         <v>7</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J2" s="95">
         <v>136</v>
       </c>
       <c r="K2" s="94" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L2" s="96">
         <f>B25</f>
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -15527,21 +15574,21 @@
         <v/>
       </c>
       <c r="G3" s="94" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H3" s="98">
         <f>$J$2-$L$2</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" s="94" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J3" s="98">
         <f>ROUND($L$2*7/$H$2,1)</f>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K3" s="94" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L3" s="98" t="str">
         <f>IF($H$3&lt;0,"INVALID","VALID")</f>
@@ -15553,22 +15600,22 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C4" t="s">
         <v>554</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>555</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>556</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>557</v>
       </c>
-      <c r="F4" t="s">
-        <v>558</v>
-      </c>
       <c r="G4" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -15592,13 +15639,13 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="G5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I5">
         <f ca="1">SUM(D5:D6)</f>
@@ -15626,10 +15673,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="G6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -15653,13 +15700,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="G7" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="H7" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -15687,10 +15734,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G8" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -15714,10 +15761,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="G9" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -15741,10 +15788,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="G10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -15753,7 +15800,7 @@
       </c>
       <c r="B11">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A11)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A11)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A11)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A11)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$51,복귀_간접계수맵!$C$7:$C$51,$A11),0.5)</f>
@@ -15761,17 +15808,17 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1011</v>
+        <v>1221</v>
       </c>
       <c r="G11" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -15795,10 +15842,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="G12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -15822,10 +15869,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -15849,10 +15896,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G14" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -15876,13 +15923,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G15" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="H15" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -15910,10 +15957,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G16" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -15937,10 +15984,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G17" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -15964,10 +16011,10 @@
         <v>하한</v>
       </c>
       <c r="F18" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="G18" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -15991,10 +16038,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G19" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -16018,10 +16065,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="G20" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -16045,10 +16092,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="G21" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -16072,10 +16119,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="G22" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -16099,10 +16146,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="G23" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -16126,110 +16173,110 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="G24" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B25">
         <f>SUM(B5:B24)</f>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D25">
         <f ca="1">SUM(D5:D24)</f>
-        <v>186.5</v>
+        <v>188.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
+        <v>609</v>
+      </c>
+      <c r="B44" t="s">
         <v>610</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>611</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>612</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>613</v>
-      </c>
-      <c r="E44" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -16243,7 +16290,7 @@
         <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="E45" t="s">
         <v>149</v>
@@ -16251,32 +16298,32 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
     </row>
   </sheetData>
@@ -16380,7 +16427,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -16459,7 +16506,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>243</v>
@@ -16471,7 +16518,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>237</v>
@@ -16483,7 +16530,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -16499,10 +16546,10 @@
         <v>44</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="O8" s="26">
         <v>120</v>
@@ -16845,27 +16892,27 @@
     <row r="18" spans="1:12" ht="15" customHeight="1"/>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -16916,7 +16963,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -17069,7 +17116,7 @@
         <v>16</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.5" customHeight="1">
@@ -17228,7 +17275,7 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="L23" s="21" t="s">
         <v>308</v>
@@ -17268,7 +17315,7 @@
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="L24" s="86" t="s">
         <v>310</v>
@@ -17308,7 +17355,7 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="L25" s="21" t="s">
         <v>362</v>
@@ -17332,17 +17379,17 @@
     </row>
     <row r="27" spans="1:15" ht="16.5" customHeight="1">
       <c r="A27" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -17515,7 +17562,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1">
@@ -17673,7 +17720,7 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="L18" s="21" t="s">
         <v>331</v>
@@ -17817,17 +17864,17 @@
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1">
       <c r="A23" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -17867,7 +17914,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
@@ -17924,7 +17971,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -17958,7 +18005,7 @@
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="L6" s="21" t="s">
         <v>345</v>
@@ -18118,7 +18165,7 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="L10" s="21" t="s">
         <v>400</v>
@@ -18158,7 +18205,7 @@
         <v>301</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="L11" s="36" t="s">
         <v>302</v>
@@ -18199,7 +18246,7 @@
         <v>27</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="L12" s="21" t="s">
         <v>360</v>
@@ -18279,7 +18326,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>50</v>
@@ -18319,7 +18366,7 @@
         <v>53</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="L15" s="21" t="s">
         <v>54</v>
@@ -18357,7 +18404,7 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="L16" s="21" t="s">
         <v>401</v>
@@ -18379,7 +18426,7 @@
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1">
       <c r="F18" s="87" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.5" customHeight="1">
@@ -18409,7 +18456,7 @@
     </row>
     <row r="24" spans="1:9" ht="16.5" customHeight="1">
       <c r="A24" s="109" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5" customHeight="1">
@@ -18424,7 +18471,7 @@
     </row>
     <row r="27" spans="1:9" ht="16.5" customHeight="1">
       <c r="A27" s="108" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.5" customHeight="1">
@@ -18435,43 +18482,43 @@
     <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="30" spans="1:9" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.5" customHeight="1">
       <c r="A31" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" customHeight="1">
       <c r="A32" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
@@ -18512,7 +18559,7 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -18569,7 +18616,7 @@
         <v>16</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="16.5" customHeight="1">
@@ -18645,7 +18692,7 @@
         <v>382</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>386</v>
@@ -18657,7 +18704,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>237</v>
@@ -18669,7 +18716,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="G8" s="26">
         <v>80</v>
@@ -18685,10 +18732,10 @@
         <v>382</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="O8" s="26">
         <v>120</v>
@@ -18727,7 +18774,7 @@
         <v>388</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="L9" s="21" t="s">
         <v>389</v>
@@ -18809,7 +18856,7 @@
         <v>45</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="L11" s="22" t="s">
         <v>393</v>
@@ -18889,7 +18936,7 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>58</v>
@@ -18927,7 +18974,7 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="L14" s="21" t="s">
         <v>62</v>
@@ -18987,43 +19034,43 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B22" s="83"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
     </row>
   </sheetData>
@@ -19063,7 +19110,7 @@
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
@@ -19216,7 +19263,7 @@
         <v>16</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="16.5" customHeight="1">
@@ -19454,10 +19501,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="O25" s="26">
         <v>60</v>
@@ -19610,7 +19657,7 @@
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="L29" s="21" t="s">
         <v>403</v>
@@ -19682,32 +19729,32 @@
     <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -19880,7 +19927,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="35" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="16.5" customHeight="1">
@@ -19958,7 +20005,7 @@
         <v>441</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>445</v>
+        <v>1222</v>
       </c>
       <c r="L16" s="39" t="s">
         <v>443</v>
@@ -19970,7 +20017,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>321</v>
@@ -19998,10 +20045,10 @@
         <v>330</v>
       </c>
       <c r="K17" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="L17" s="21" t="s">
         <v>447</v>
-      </c>
-      <c r="L17" s="21" t="s">
-        <v>448</v>
       </c>
       <c r="O17" s="26"/>
     </row>
@@ -20010,7 +20057,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>330</v>
@@ -20038,10 +20085,10 @@
         <v>316</v>
       </c>
       <c r="K18" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="L18" s="21" t="s">
         <v>450</v>
-      </c>
-      <c r="L18" s="21" t="s">
-        <v>451</v>
       </c>
       <c r="O18" s="26"/>
     </row>
@@ -20050,7 +20097,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>330</v>
@@ -20076,10 +20123,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="L19" s="21" t="s">
         <v>453</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>454</v>
       </c>
       <c r="O19" s="26"/>
     </row>
@@ -20088,10 +20135,10 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D20" s="26">
         <v>120</v>
@@ -20100,7 +20147,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="G20" s="26">
         <v>45</v>
@@ -20116,10 +20163,10 @@
         <v>321</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="O20" s="26"/>
     </row>
@@ -20128,10 +20175,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D21" s="26">
         <v>42</v>
@@ -20140,7 +20187,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -20154,10 +20201,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="O21" s="26">
         <v>75</v>
@@ -20194,10 +20241,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="L22" s="21" t="s">
         <v>456</v>
-      </c>
-      <c r="L22" s="21" t="s">
-        <v>457</v>
       </c>
       <c r="O22" s="26"/>
     </row>
@@ -20216,17 +20263,17 @@
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
       <c r="A24" s="112" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="33" spans="2:2">

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1039" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAA239DB-EB37-4545-B0BF-1D3FEBFBA271}"/>
+  <xr:revisionPtr revIDLastSave="1064" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E7A1BE-E202-43FA-83C7-3F42001AD592}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" firstSheet="2" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="1228">
   <si>
     <t>9일차 — 어깨·팔 B</t>
   </si>
@@ -3811,34 +3811,7 @@
     <phoneticPr fontId="32" type="noConversion"/>
   </si>
   <si>
-    <t>복귀 운용 — 날짜로 자동 계산 (2026-09-13 신설)</t>
-  </si>
-  <si>
-    <t>복귀 시작일</t>
-  </si>
-  <si>
-    <t>← 복귀 1주차가 시작된 월요일. 주차는 월요일에 넘어간다</t>
-  </si>
-  <si>
-    <t>복귀 시작 사이클</t>
-  </si>
-  <si>
-    <t>← 그 주에 쓰고 있던 사이클 번호</t>
-  </si>
-  <si>
     <t>사이클 전진(주)</t>
-  </si>
-  <si>
-    <t>← 몇 주마다 사이클을 한 칸 올릴지. 복귀는 2주</t>
-  </si>
-  <si>
-    <t>· 앱 '복귀 → 달력'이 이 세 칸으로 오늘의 주차 · 사이클 · 네 리프트 중량을 계산한다. 손으로 셀 필요가 없고, 어디쯤인지 까먹어도 달력이 알려준다.</t>
-  </si>
-  <si>
-    <t>· 디로드 주나 통째로 쉰 주가 있으면 앱 달력에서 '한 주 미루기'를 누른다 — 그 폰에만 저장되고 사이클이 그만큼 늦게 올라간다. 영구히 맞추려면 위 '복귀 시작일'을 그만큼 뒤로 미룬다.</t>
-  </si>
-  <si>
-    <t>· 중량 자체는 증량기록 표(사이클 단위)가 그대로 정한다. 이 칸들이 정하는 것은 '오늘이 몇 번째 칸인가'뿐이다 — 표가 두 벌로 갈리지 않게 하려고 그렇게 뒀다.</t>
   </si>
   <si>
     <t>· 재택으로 돌아가면 이 칸들은 무시된다. 재택은 일차 회전을 증량기록 '날짜 (1일차)'로 따라간다.</t>
@@ -3868,6 +3841,58 @@
   <si>
     <t>백오프 = 톱세트 − 5kg = 직전 사이클의 톱세트 중량. 즉 모든 중량을 두 번 만난다 — 한 사이클은 톱으로 5회, 다음 사이클은 백오프로 10회. 중량 하나당 노출이 5 → 15회다. 여기는 기록이 아니라 폼 연습 자리다. 여유 있게 5회, 매 렙 셋업을 새로 잡을 것 — 무겁게 느껴지면 톱세트가 과했던 것이다. [2026-09-13 정정] 현장 복귀판에도 같은 구조를 넣었다 — 복귀_일_등에 톱 1 + 백오프 2. 복귀에서 상한인 것은 톱세트뿐이고, 백오프는 직전 사이클 중량이라 톱엔드 노출을 안 늘린다.</t>
     <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>복귀 운용 — 날짜로 자동 계산 (2026-09-13 신설 · 09-13 기준 정정)</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그램 시작일</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>← 1주차가 시작된 월요일. 주차는 월요일에 넘어간다. 주차는 세는 숫자일 뿐 중량과 무관하다</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이클 기준일</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>← 아래 '기준 사이클'이 시작된 월요일. 여기서부터 2주마다 한 칸씩 올라간다</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>기준 사이클</t>
+  </si>
+  <si>
+    <t>← 사이클 기준일에 시작된 사이클 번호. '현재 사이클'(C4)과 같은 번호로 둔다</t>
+  </si>
+  <si>
+    <t>← 몇 주마다 사이클을 한 칸 올릴지. 복귀는 2주</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 앱 '복귀 → 달력'이 이 칸들로 오늘의 주차 · 사이클 · 네 리프트 중량을 계산한다. 손으로 셀 필요가 없고, 어디쯤인지 까먹어도 달력이 알려준다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 주차와 사이클은 기준이 다르다. 주차는 '프로그램 시작일'에서 세고, 사이클은 '사이클 기준일'에서 2주마다 오른다. 하나로 묶어 두면 주차를 맞추려다 중량까지 따라 움직인다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 디로드 주나 통째로 쉰 주가 있으면 앱 달력에서 '한 주 미루기'를 누른다 — 사이클만 한 주 늦게 올라가고 주차 표시는 그대로다. 영구히 맞추려면 '사이클 기준일'을 한 주 뒤로 옮긴다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 중량 자체는 증량기록 표(사이클 단위)가 그대로 정한다. 이 칸들이 정하는 것은 '오늘이 몇 번째 칸인가'뿐이다 — 표가 두 벌로 갈리지 않게 하려고 그렇게 뒀다.</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 디로드 주에는 사이클을 올리지 않는다. 그 주에 앱 복귀 달력에서 '한 주 미루기'를 누르면 사이클이 한 주 늦게 올라간다. 안 누르면 세트가 절반인 주에 새 중량을 맞이하게 되고, 데드는 디로드에 건너뛰므로 그 중량을 한 번도 안 들고 다음 칸으로 넘어간다.</t>
+  </si>
+  <si>
+    <t>· 즉 디로드는 '한 주 쉬는 것'이 아니라 '한 주 멈추는 것'이다 — 볼륨도 진행도 같이 멈춘다. 중량만 그대로 두는 이유는 강도를 놓으면 근력이 먼저 빠지기 때문이다.</t>
   </si>
 </sst>
 </file>
@@ -5020,7 +5045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5573,60 +5598,76 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="C59" s="113">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="D59" t="s">
-        <v>1207</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C60">
-        <v>5</v>
+        <v>1217</v>
+      </c>
+      <c r="C60" s="113">
+        <v>46279</v>
       </c>
       <c r="D60" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>1211</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>1212</v>
+        <v>1205</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>1215</v>
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -11449,7 +11490,7 @@
         <v>3.5</v>
       </c>
       <c r="J15" t="s">
-        <v>1218</v>
+        <v>1209</v>
       </c>
       <c r="K15" t="s">
         <v>787</v>
@@ -11486,10 +11527,10 @@
         <v>6</v>
       </c>
       <c r="J16" t="s">
-        <v>1216</v>
+        <v>1207</v>
       </c>
       <c r="K16" t="s">
-        <v>1217</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1">
@@ -11898,12 +11939,12 @@
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="63" t="s">
-        <v>1219</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="95.25" customHeight="1">
       <c r="A31" s="12" t="s">
-        <v>1220</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="252.75" customHeight="1">
@@ -13841,7 +13882,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -14174,41 +14215,51 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>947</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>948</v>
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>947</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
         <v>954</v>
       </c>
     </row>
@@ -15815,7 +15866,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="G11" t="s">
         <v>1002</v>
@@ -20005,7 +20056,7 @@
         <v>441</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>1222</v>
+        <v>1213</v>
       </c>
       <c r="L16" s="39" t="s">
         <v>443</v>

--- a/운동프로그램_10일주기_v19.xlsx
+++ b/운동프로그램_10일주기_v19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1785" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40995B9D-56C0-4BDF-9311-63320D14914C}"/>
+  <xr:revisionPtr revIDLastSave="1796" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{177FC5C0-44DB-4791-AFB9-60D7074769CD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="E6" s="71">
         <f>복귀_평일A_가슴!$E$28</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F6" s="73" t="s">
         <v>1253</v>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$21</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7" s="69" t="s">
         <v>1253</v>
@@ -11561,7 +11561,7 @@
       <c r="D11" s="67"/>
       <c r="E11" s="7">
         <f>SUM(E6:E10)</f>
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>1304</v>
@@ -13639,7 +13639,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>19</v>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="J12" t="s">
         <v>1054</v>
@@ -13678,7 +13678,7 @@
         <v>763</v>
       </c>
       <c r="E13" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>19</v>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J13" t="s">
         <v>764</v>
@@ -13962,11 +13962,11 @@
       </c>
       <c r="E21">
         <f>SUM(E11:E20)</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I21">
         <f>ROUND(SUM(I11:I20),0)</f>
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="237.75" customHeight="1">
@@ -14343,7 +14343,7 @@
         <v>1325</v>
       </c>
       <c r="E22" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>279</v>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
-        <v>9.6999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="s">
         <v>795</v>
@@ -14415,7 +14415,7 @@
         <v>125</v>
       </c>
       <c r="E24" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>40</v>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="I24">
         <f>IF(E24=0,0,ROUND((E24*(G24+H24)+N24)/60,1))</f>
-        <v>13.3</v>
+        <v>8</v>
       </c>
       <c r="J24" t="s">
         <v>1308</v>
@@ -14451,7 +14451,7 @@
         <v>125</v>
       </c>
       <c r="E25" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>40</v>
@@ -14464,7 +14464,7 @@
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
-        <v>11.7</v>
+        <v>9</v>
       </c>
       <c r="J25" t="s">
         <v>1310</v>
@@ -14557,11 +14557,11 @@
       </c>
       <c r="E28">
         <f>SUM(E20:E27)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I28">
         <f>ROUND(SUM(I20:I27),0)</f>
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="32.25" customHeight="1">
@@ -15887,11 +15887,11 @@
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="s">
         <v>457</v>
@@ -16559,11 +16559,11 @@
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G32" t="s">
         <v>457</v>
@@ -17063,11 +17063,11 @@
       </c>
       <c r="E50">
         <f ca="1">IFERROR(INDEX(INDIRECT("'"&amp;$A50&amp;"'!$E$1:$E$45"),MATCH($B50,INDIRECT("'"&amp;$A50&amp;"'!$B$1:$B$45"),0)),"?")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F50">
         <f ca="1">IF(ISNUMBER(E50),$D50*E50,0)</f>
-        <v>1</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G50" t="s">
         <v>457</v>
@@ -17091,11 +17091,11 @@
       </c>
       <c r="E51">
         <f ca="1">IFERROR(INDEX(INDIRECT("'"&amp;$A51&amp;"'!$E$1:$E$45"),MATCH($B51,INDIRECT("'"&amp;$A51&amp;"'!$B$1:$B$45"),0)),"?")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F51">
         <f ca="1">IF(ISNUMBER(E51),$D51*E51,0)</f>
-        <v>1</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G51" t="s">
         <v>457</v>
@@ -17119,11 +17119,11 @@
       </c>
       <c r="E52">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G52" t="s">
         <v>457</v>
@@ -17287,11 +17287,11 @@
       </c>
       <c r="E58">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G58" t="s">
         <v>457</v>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="B5">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A5)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A5)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A5)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A5)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$58,복귀_간접계수맵!$C$7:$C$58,$A5),0.5)</f>
@@ -17383,11 +17383,11 @@
       </c>
       <c r="D5">
         <f t="shared" ref="D5:D24" ca="1" si="0">B5+C5</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E24" ca="1" si="1">IF(D5&gt;20,"과다 점검",IF(D5&gt;=10,"충분",IF(D5&gt;=8,"하한",IF(D5&gt;=1,"보완 필요","미배치"))))</f>
-        <v>충분</v>
+        <v>하한</v>
       </c>
       <c r="F5" t="s">
         <v>1240</v>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="I5">
         <f ca="1">SUM(D5:D6)</f>
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="B7">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A7)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A7)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A7)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A7)</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$58,복귀_간접계수맵!$C$7:$C$58,$A7),0.5)</f>
@@ -17444,11 +17444,11 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>과다 점검</v>
+        <v>충분</v>
       </c>
       <c r="F7" t="s">
         <v>1321</v>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
-        <v>45.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -17501,11 +17501,11 @@
       </c>
       <c r="C9">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$58,복귀_간접계수맵!$C$7:$C$58,$A9),0.5)</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="B13">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A13)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A13)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A13)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A13)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$58,복귀_간접계수맵!$C$7:$C$58,$A13),0.5)</f>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17805,11 +17805,11 @@
       </c>
       <c r="C20">
         <f ca="1">MROUND(SUMIFS(복귀_간접계수맵!$F$7:$F$58,복귀_간접계수맵!$C$7:$C$58,$A20),0.5)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17936,11 +17936,11 @@
       </c>
       <c r="B25">
         <f>SUM(B5:B24)</f>
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D25">
         <f ca="1">SUM(D5:D24)</f>
-        <v>204.5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:7">
